--- a/research/traditional_assets/database/data/mexico/mexico_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_beverage_alcoholic.xlsx
@@ -650,10 +650,10 @@
         <v>0.0692604341606021</v>
       </c>
       <c r="X2">
-        <v>0.1055780369084618</v>
+        <v>0.1055645455086359</v>
       </c>
       <c r="Y2">
-        <v>-0.03631760274785967</v>
+        <v>-0.03630411134803375</v>
       </c>
       <c r="Z2">
         <v>0.5318262098198517</v>
@@ -662,10 +662,10 @@
         <v>0.06959953679257996</v>
       </c>
       <c r="AB2">
-        <v>0.09195895690412979</v>
+        <v>0.09194910264747379</v>
       </c>
       <c r="AC2">
-        <v>-0.02235942011154983</v>
+        <v>-0.02234956585489382</v>
       </c>
       <c r="AD2">
         <v>1490.4</v>
@@ -787,10 +787,10 @@
         <v>0.0692604341606021</v>
       </c>
       <c r="X3">
-        <v>0.1055780369084618</v>
+        <v>0.1055645455086359</v>
       </c>
       <c r="Y3">
-        <v>-0.03631760274785967</v>
+        <v>-0.03630411134803375</v>
       </c>
       <c r="Z3">
         <v>0.5318262098198517</v>
@@ -799,10 +799,10 @@
         <v>0.06959953679257996</v>
       </c>
       <c r="AB3">
-        <v>0.09195895690412979</v>
+        <v>0.09194910264747379</v>
       </c>
       <c r="AC3">
-        <v>-0.02235942011154983</v>
+        <v>-0.02234956585489382</v>
       </c>
       <c r="AD3">
         <v>1490.4</v>
@@ -1139,49 +1139,49 @@
         <v>5.78765060240964</v>
       </c>
       <c r="F2">
-        <v>4.62964414743503</v>
+        <v>4.56377321188649</v>
       </c>
       <c r="G2">
         <v>3.53091684434968</v>
       </c>
       <c r="H2">
-        <v>2.61947405828003</v>
+        <v>2.75044776119403</v>
       </c>
       <c r="I2">
         <v>0.269589754721077</v>
       </c>
       <c r="J2">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="K2">
         <v>4038</v>
       </c>
       <c r="L2">
-        <v>4413.81524343913</v>
+        <v>4407.71657391719</v>
       </c>
       <c r="M2">
         <v>5062.8</v>
       </c>
       <c r="N2">
-        <v>5053.89524343913</v>
+        <v>5103.08057391719</v>
       </c>
       <c r="O2">
         <v>1490.4</v>
       </c>
       <c r="P2">
-        <v>1105.68</v>
+        <v>1160.964</v>
       </c>
       <c r="Q2">
-        <v>0.09195895690412979</v>
+        <v>0.0919491026474738</v>
       </c>
       <c r="R2">
-        <v>0.0920402870968892</v>
+        <v>0.0915848300647705</v>
       </c>
       <c r="S2">
         <v>0.055060241755517</v>
       </c>
       <c r="T2">
-        <v>0.053730241755517</v>
+        <v>0.051910241755517</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.105578036908462</v>
+        <v>0.105564545508636</v>
       </c>
       <c r="X2">
-        <v>0.101617798432232</v>
+        <v>0.102131239615332</v>
       </c>
       <c r="Y2">
         <v>0.869646958034577</v>
       </c>
       <c r="Z2">
-        <v>0.812033668571453</v>
+        <v>0.819688173931001</v>
       </c>
       <c r="AA2">
         <v>1490.4</v>
@@ -1236,7 +1236,7 @@
         <v>4038</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524602</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09330450930402745</v>
+        <v>0.09329378793608531</v>
       </c>
       <c r="C2">
-        <v>5384.997556947624</v>
+        <v>5385.05761829012</v>
       </c>
       <c r="D2">
-        <v>4919.397556947623</v>
+        <v>4919.45761829012</v>
       </c>
       <c r="E2">
         <v>-1490.4</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09330450930402745</v>
+        <v>0.09329378793608531</v>
       </c>
       <c r="T2">
         <v>0.6910924838905985</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09319789819367055</v>
+        <v>0.09317740898983222</v>
       </c>
       <c r="C3">
-        <v>5340.778655946112</v>
+        <v>5341.857886002528</v>
       </c>
       <c r="D3">
-        <v>4930.462655946111</v>
+        <v>4931.541886002527</v>
       </c>
       <c r="E3">
         <v>-1435.116</v>
@@ -1539,37 +1539,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M3">
-        <v>3.900700178874287</v>
+        <v>3.823302578874287</v>
       </c>
       <c r="N3">
-        <v>389.0135855354114</v>
+        <v>389.0909831354114</v>
       </c>
       <c r="O3">
-        <v>116.7040756606234</v>
+        <v>116.7272949406234</v>
       </c>
       <c r="P3">
-        <v>272.309509874788</v>
+        <v>272.363688194788</v>
       </c>
       <c r="Q3">
-        <v>310.109509874788</v>
+        <v>310.163688194788</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09364039977385391</v>
+        <v>0.09362960259825964</v>
       </c>
       <c r="T3">
         <v>0.6959789964029562</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>100.729168532937</v>
+        <v>102.7682945852466</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09309128708331361</v>
+        <v>0.09306103004357914</v>
       </c>
       <c r="C4">
-        <v>5296.609644155204</v>
+        <v>5298.717668048045</v>
       </c>
       <c r="D4">
-        <v>4941.577644155203</v>
+        <v>4943.685668048045</v>
       </c>
       <c r="E4">
         <v>-1379.832</v>
@@ -1621,37 +1621,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M4">
-        <v>7.801400357748574</v>
+        <v>7.646605157748574</v>
       </c>
       <c r="N4">
-        <v>385.1128853565372</v>
+        <v>385.2676805565371</v>
       </c>
       <c r="O4">
-        <v>115.5338656069611</v>
+        <v>115.5803041669611</v>
       </c>
       <c r="P4">
-        <v>269.579019749576</v>
+        <v>269.687376389576</v>
       </c>
       <c r="Q4">
-        <v>307.379019749576</v>
+        <v>307.487376389576</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09398314515122784</v>
+        <v>0.09397227062088653</v>
       </c>
       <c r="T4">
         <v>0.7009652336604641</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>50.36458426646853</v>
+        <v>51.38414729262329</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09298467597295672</v>
+        <v>0.09294465109732605</v>
       </c>
       <c r="C5">
-        <v>5252.490859740454</v>
+        <v>5255.637405169064</v>
       </c>
       <c r="D5">
-        <v>4952.742859740453</v>
+        <v>4955.889405169063</v>
       </c>
       <c r="E5">
         <v>-1324.548</v>
@@ -1703,37 +1703,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M5">
-        <v>11.70210053662286</v>
+        <v>11.46990773662286</v>
       </c>
       <c r="N5">
-        <v>381.2121851776628</v>
+        <v>381.4443779776628</v>
       </c>
       <c r="O5">
-        <v>114.3636555532988</v>
+        <v>114.4333133932988</v>
       </c>
       <c r="P5">
-        <v>266.848529624364</v>
+        <v>267.011064584364</v>
       </c>
       <c r="Q5">
-        <v>304.648529624364</v>
+        <v>304.811064584364</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09433295744359918</v>
+        <v>0.09432200396356757</v>
       </c>
       <c r="T5">
         <v>0.7060542799335908</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.57638951097901</v>
+        <v>34.2560981950822</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09287806486259979</v>
+        <v>0.09282827215107296</v>
       </c>
       <c r="C6">
-        <v>5208.422643930612</v>
+        <v>5212.61754247072</v>
       </c>
       <c r="D6">
-        <v>4963.958643930612</v>
+        <v>4968.15354247072</v>
       </c>
       <c r="E6">
         <v>-1269.264</v>
@@ -1785,37 +1785,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M6">
-        <v>15.60280071549715</v>
+        <v>15.29321031549715</v>
       </c>
       <c r="N6">
-        <v>377.3114849987886</v>
+        <v>377.6210753987885</v>
       </c>
       <c r="O6">
-        <v>113.1934454996366</v>
+        <v>113.2863226196366</v>
       </c>
       <c r="P6">
-        <v>264.118039499152</v>
+        <v>264.334752779152</v>
       </c>
       <c r="Q6">
-        <v>301.918039499152</v>
+        <v>302.134752779152</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09469005749206158</v>
+        <v>0.09467902341755446</v>
       </c>
       <c r="T6">
         <v>0.7112493480040742</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.18229213323426</v>
+        <v>25.69207364631164</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09277145375224288</v>
+        <v>0.09271189320481987</v>
       </c>
       <c r="C7">
-        <v>5164.405341052371</v>
+        <v>5169.658529475016</v>
       </c>
       <c r="D7">
-        <v>4975.225341052371</v>
+        <v>4980.478529475015</v>
       </c>
       <c r="E7">
         <v>-1213.98</v>
@@ -1867,37 +1867,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M7">
-        <v>19.50350089437144</v>
+        <v>19.11651289437144</v>
       </c>
       <c r="N7">
-        <v>373.4107848199143</v>
+        <v>373.7977728199143</v>
       </c>
       <c r="O7">
-        <v>112.0232354459743</v>
+        <v>112.1393318459743</v>
       </c>
       <c r="P7">
-        <v>261.38754937394</v>
+        <v>261.65844097394</v>
       </c>
       <c r="Q7">
-        <v>299.18754937394</v>
+        <v>299.45844097394</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0950546754362811</v>
+        <v>0.09504355907057266</v>
       </c>
       <c r="T7">
         <v>0.7165537859286731</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.14583370658741</v>
+        <v>20.55365891704932</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09266484264188597</v>
+        <v>0.09259551425856678</v>
       </c>
       <c r="C8">
-        <v>5120.43929856561</v>
+        <v>5126.760820175739</v>
       </c>
       <c r="D8">
-        <v>4986.543298565609</v>
+        <v>4992.864820175739</v>
       </c>
       <c r="E8">
         <v>-1158.696</v>
@@ -1949,37 +1949,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M8">
-        <v>23.40420107324572</v>
+        <v>22.93981547324572</v>
       </c>
       <c r="N8">
-        <v>369.51008464104</v>
+        <v>369.97447024104</v>
       </c>
       <c r="O8">
-        <v>110.853025392312</v>
+        <v>110.992341072312</v>
       </c>
       <c r="P8">
-        <v>258.657059248728</v>
+        <v>258.982129168728</v>
       </c>
       <c r="Q8">
-        <v>296.457059248728</v>
+        <v>296.782129168728</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09542705120910101</v>
+        <v>0.09541585080131465</v>
       </c>
       <c r="T8">
         <v>0.7219710842346465</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.78819475548951</v>
+        <v>17.1280490975411</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09255823153152906</v>
+        <v>0.09247913531231371</v>
       </c>
       <c r="C9">
-        <v>5076.524867099107</v>
+        <v>5083.924873094209</v>
       </c>
       <c r="D9">
-        <v>4997.912867099107</v>
+        <v>5005.312873094209</v>
       </c>
       <c r="E9">
         <v>-1103.412</v>
@@ -2031,37 +2031,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M9">
-        <v>27.30490125212001</v>
+        <v>26.76311805212001</v>
       </c>
       <c r="N9">
-        <v>365.6093844621657</v>
+        <v>366.1511676621657</v>
       </c>
       <c r="O9">
-        <v>109.6828153386497</v>
+        <v>109.8453502986497</v>
       </c>
       <c r="P9">
-        <v>255.926569123516</v>
+        <v>256.305817363516</v>
       </c>
       <c r="Q9">
-        <v>293.726569123516</v>
+        <v>294.105817363516</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09580743506305686</v>
+        <v>0.09579614880583605</v>
       </c>
       <c r="T9">
         <v>0.7275048835794581</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.38988121899101</v>
+        <v>14.68118494074951</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09251322042117216</v>
+        <v>0.09236275636606062</v>
       </c>
       <c r="C10">
-        <v>5026.056668826903</v>
+        <v>5041.151151335863</v>
       </c>
       <c r="D10">
-        <v>5002.728668826902</v>
+        <v>5017.823151335862</v>
       </c>
       <c r="E10">
         <v>-1048.128</v>
@@ -2113,45 +2113,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M10">
-        <v>31.69210063099429</v>
+        <v>30.5864206309943</v>
       </c>
       <c r="N10">
-        <v>361.2221850832914</v>
+        <v>362.3278650832914</v>
       </c>
       <c r="O10">
-        <v>108.3666555249874</v>
+        <v>108.6983595249874</v>
       </c>
       <c r="P10">
-        <v>252.855529558304</v>
+        <v>253.629505558304</v>
       </c>
       <c r="Q10">
-        <v>290.655529558304</v>
+        <v>291.429505558304</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09619608813122912</v>
+        <v>0.09618471415828181</v>
       </c>
       <c r="T10">
         <v>0.7331589829100263</v>
       </c>
       <c r="U10">
-        <v>0.07165748822216711</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.05016024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>12.39786186119903</v>
+        <v>12.84603682315582</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09241430931081523</v>
+        <v>0.09234087741980754</v>
       </c>
       <c r="C11">
-        <v>4981.387981051068</v>
+        <v>4988.226038600606</v>
       </c>
       <c r="D11">
-        <v>5013.343981051067</v>
+        <v>5020.182038600605</v>
       </c>
       <c r="E11">
         <v>-992.8440000000002</v>
@@ -2195,37 +2195,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M11">
-        <v>35.65361320986857</v>
+        <v>35.15605720986857</v>
       </c>
       <c r="N11">
-        <v>357.2606725044171</v>
+        <v>357.7582285044172</v>
       </c>
       <c r="O11">
-        <v>107.1782017513251</v>
+        <v>107.3274685513251</v>
       </c>
       <c r="P11">
-        <v>250.082470753092</v>
+        <v>250.430759953092</v>
       </c>
       <c r="Q11">
-        <v>287.882470753092</v>
+        <v>288.230759953092</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.0965932830250755</v>
+        <v>0.09658181940858353</v>
       </c>
       <c r="T11">
         <v>0.7389373481599476</v>
       </c>
       <c r="U11">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.02032165439913</v>
+        <v>11.17628986005836</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09231539820045831</v>
+        <v>0.09223499847355444</v>
       </c>
       <c r="C12">
-        <v>4936.764438425419</v>
+        <v>4944.388826620819</v>
       </c>
       <c r="D12">
-        <v>5024.004438425419</v>
+        <v>5031.628826620818</v>
       </c>
       <c r="E12">
         <v>-937.5600000000001</v>
@@ -2277,37 +2277,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M12">
-        <v>39.61512578874287</v>
+        <v>39.06228578874287</v>
       </c>
       <c r="N12">
-        <v>353.2991599255428</v>
+        <v>353.8519999255428</v>
       </c>
       <c r="O12">
-        <v>105.9897479776628</v>
+        <v>106.1555999776628</v>
       </c>
       <c r="P12">
-        <v>247.30941194788</v>
+        <v>247.69639994788</v>
       </c>
       <c r="Q12">
-        <v>285.10941194788</v>
+        <v>285.49639994788</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09699930447211846</v>
+        <v>0.09698774922000306</v>
       </c>
       <c r="T12">
         <v>0.7448441215265339</v>
       </c>
       <c r="U12">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.918289488959219</v>
+        <v>10.05866087405252</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09238588709010141</v>
+        <v>0.09226001952730135</v>
       </c>
       <c r="C13">
-        <v>4873.878640616103</v>
+        <v>4886.39504180828</v>
       </c>
       <c r="D13">
-        <v>5016.402640616102</v>
+        <v>5028.919041808279</v>
       </c>
       <c r="E13">
         <v>-882.2760000000002</v>
@@ -2359,37 +2359,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M13">
-        <v>44.91451116761715</v>
+        <v>44.00232516761715</v>
       </c>
       <c r="N13">
-        <v>347.9997745466686</v>
+        <v>348.9119605466686</v>
       </c>
       <c r="O13">
-        <v>104.3999323640006</v>
+        <v>104.6735881640006</v>
       </c>
       <c r="P13">
-        <v>243.599842182668</v>
+        <v>244.238372382668</v>
       </c>
       <c r="Q13">
-        <v>281.399842182668</v>
+        <v>282.038372382668</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09741444999662309</v>
+        <v>0.09740280104965673</v>
       </c>
       <c r="T13">
         <v>0.7508836313732683</v>
       </c>
       <c r="U13">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.748047691044947</v>
+        <v>8.929398258332155</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0923023759797445</v>
+        <v>0.09216604058104827</v>
       </c>
       <c r="C14">
-        <v>4827.603327714105</v>
+        <v>4841.304116446927</v>
       </c>
       <c r="D14">
-        <v>5025.411327714104</v>
+        <v>5039.112116446927</v>
       </c>
       <c r="E14">
         <v>-826.9920000000002</v>
@@ -2441,37 +2441,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M14">
-        <v>48.99764854649143</v>
+        <v>48.00253654649143</v>
       </c>
       <c r="N14">
-        <v>343.9166371677943</v>
+        <v>344.9117491677943</v>
       </c>
       <c r="O14">
-        <v>103.1749911503383</v>
+        <v>103.4735247503383</v>
       </c>
       <c r="P14">
-        <v>240.741646017456</v>
+        <v>241.438224417456</v>
       </c>
       <c r="Q14">
-        <v>278.5416460174561</v>
+        <v>279.238224417456</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09783903064668462</v>
+        <v>0.0978272858754389</v>
       </c>
       <c r="T14">
         <v>0.7570604028074284</v>
       </c>
       <c r="U14">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.019043716791202</v>
+        <v>8.185281736804475</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09235536486938759</v>
+        <v>0.09214486163479518</v>
       </c>
       <c r="C15">
-        <v>4766.599450595701</v>
+        <v>4788.322919409606</v>
       </c>
       <c r="D15">
-        <v>5019.691450595701</v>
+        <v>5041.414919409605</v>
       </c>
       <c r="E15">
         <v>-771.7080000000001</v>
@@ -2523,37 +2523,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M15">
-        <v>54.15882392536573</v>
+        <v>52.57770152536573</v>
       </c>
       <c r="N15">
-        <v>338.75546178892</v>
+        <v>340.33658418892</v>
       </c>
       <c r="O15">
-        <v>101.626638536676</v>
+        <v>102.100975256676</v>
       </c>
       <c r="P15">
-        <v>237.128823252244</v>
+        <v>238.235608932244</v>
       </c>
       <c r="Q15">
-        <v>274.928823252244</v>
+        <v>276.035608932244</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.0982733717714602</v>
+        <v>0.09826152897307815</v>
       </c>
       <c r="T15">
         <v>0.7633791689872014</v>
       </c>
       <c r="U15">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.254852621167445</v>
+        <v>7.473021343938496</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09228235375903068</v>
+        <v>0.09205648268854211</v>
       </c>
       <c r="C16">
-        <v>4719.200017895304</v>
+        <v>4742.671189575974</v>
       </c>
       <c r="D16">
-        <v>5027.576017895303</v>
+        <v>5051.047189575973</v>
       </c>
       <c r="E16">
         <v>-716.4240000000001</v>
@@ -2605,37 +2605,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M16">
-        <v>58.32488730424001</v>
+        <v>56.62214010424001</v>
       </c>
       <c r="N16">
-        <v>334.5893984100457</v>
+        <v>336.2921456100457</v>
       </c>
       <c r="O16">
-        <v>100.3768195230137</v>
+        <v>100.8876436830137</v>
       </c>
       <c r="P16">
-        <v>234.212578887032</v>
+        <v>235.404501927032</v>
       </c>
       <c r="Q16">
-        <v>272.012578887032</v>
+        <v>273.204501927032</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09871781385262593</v>
+        <v>0.09870587074740667</v>
       </c>
       <c r="T16">
         <v>0.7698448832176666</v>
       </c>
       <c r="U16">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.736648862512628</v>
+        <v>6.939234105085746</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09220934264867377</v>
+        <v>0.09196810374228903</v>
       </c>
       <c r="C17">
-        <v>4671.825393174526</v>
+        <v>4697.056337578697</v>
       </c>
       <c r="D17">
-        <v>5035.485393174526</v>
+        <v>5060.716337578697</v>
       </c>
       <c r="E17">
         <v>-661.1400000000002</v>
@@ -2687,37 +2687,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M17">
-        <v>62.49095068311429</v>
+        <v>60.66657868311429</v>
       </c>
       <c r="N17">
-        <v>330.4233350311714</v>
+        <v>332.2477070311714</v>
       </c>
       <c r="O17">
-        <v>99.12700050935142</v>
+        <v>99.67431210935143</v>
       </c>
       <c r="P17">
-        <v>231.29633452182</v>
+        <v>232.57339492182</v>
       </c>
       <c r="Q17">
-        <v>269.09633452182</v>
+        <v>270.37339492182</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09917271339452496</v>
+        <v>0.09916066762230763</v>
       </c>
       <c r="T17">
         <v>0.7764627319006137</v>
       </c>
       <c r="U17">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.28753893834512</v>
+        <v>6.476618498080032</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09229313153831685</v>
+        <v>0.09199172479603591</v>
       </c>
       <c r="C18">
-        <v>4607.466553172399</v>
+        <v>4639.1844400032</v>
       </c>
       <c r="D18">
-        <v>5026.410553172399</v>
+        <v>5058.128440003199</v>
       </c>
       <c r="E18">
         <v>-605.8560000000001</v>
@@ -2769,37 +2769,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M18">
-        <v>67.8953756619886</v>
+        <v>65.59556126198858</v>
       </c>
       <c r="N18">
-        <v>325.0189100522971</v>
+        <v>327.3187244522971</v>
       </c>
       <c r="O18">
-        <v>97.50567301568913</v>
+        <v>98.19561733568914</v>
       </c>
       <c r="P18">
-        <v>227.513237036608</v>
+        <v>229.123107116608</v>
       </c>
       <c r="Q18">
-        <v>265.313237036608</v>
+        <v>266.923107116608</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09963844387789778</v>
+        <v>0.09962629299423001</v>
       </c>
       <c r="T18">
         <v>0.7832381484093449</v>
       </c>
       <c r="U18">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.787055184293792</v>
+        <v>5.989952340601015</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09222992042795994</v>
+        <v>0.09191034584978286</v>
       </c>
       <c r="C19">
-        <v>4559.025661867119</v>
+        <v>4592.827398907413</v>
       </c>
       <c r="D19">
-        <v>5033.253661867118</v>
+        <v>5067.055398907413</v>
       </c>
       <c r="E19">
         <v>-550.5720000000001</v>
@@ -2851,37 +2851,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M19">
-        <v>72.13883664086288</v>
+        <v>69.69528384086287</v>
       </c>
       <c r="N19">
-        <v>320.7754490734228</v>
+        <v>323.2190018734228</v>
       </c>
       <c r="O19">
-        <v>96.23263472202684</v>
+        <v>96.96570056202684</v>
       </c>
       <c r="P19">
-        <v>224.542814351396</v>
+        <v>226.253301311396</v>
       </c>
       <c r="Q19">
-        <v>262.342814351396</v>
+        <v>264.053301311396</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1001153967825567</v>
+        <v>0.1001031382546325</v>
       </c>
       <c r="T19">
         <v>0.7901768279664796</v>
       </c>
       <c r="U19">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.446640173452981</v>
+        <v>5.637602202918601</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09216670931760303</v>
+        <v>0.09182896690352978</v>
       </c>
       <c r="C20">
-        <v>4510.603428797684</v>
+        <v>4546.50192343466</v>
       </c>
       <c r="D20">
-        <v>5040.115428797683</v>
+        <v>5076.01392343466</v>
       </c>
       <c r="E20">
         <v>-495.2880000000002</v>
@@ -2933,37 +2933,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M20">
-        <v>76.38229761973716</v>
+        <v>73.79500641973715</v>
       </c>
       <c r="N20">
-        <v>316.5319880945485</v>
+        <v>319.1192792945486</v>
       </c>
       <c r="O20">
-        <v>94.95959642836455</v>
+        <v>95.73578378836457</v>
       </c>
       <c r="P20">
-        <v>221.572391666184</v>
+        <v>223.383495506184</v>
       </c>
       <c r="Q20">
-        <v>259.372391666184</v>
+        <v>261.183495506184</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1006039826848902</v>
+        <v>0.1005916138872399</v>
       </c>
       <c r="T20">
         <v>0.7972847436103734</v>
       </c>
       <c r="U20">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.144049052705594</v>
+        <v>5.324402080534235</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09210349820724613</v>
+        <v>0.09174758795727668</v>
       </c>
       <c r="C21">
-        <v>4462.199930377829</v>
+        <v>4500.20818130498</v>
       </c>
       <c r="D21">
-        <v>5046.995930377829</v>
+        <v>5085.004181304979</v>
       </c>
       <c r="E21">
         <v>-440.0040000000001</v>
@@ -3015,37 +3015,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M21">
-        <v>80.62575859861144</v>
+        <v>77.89472899861144</v>
       </c>
       <c r="N21">
-        <v>312.2885271156742</v>
+        <v>315.0195567156743</v>
       </c>
       <c r="O21">
-        <v>93.68655813470227</v>
+        <v>94.50586701470229</v>
       </c>
       <c r="P21">
-        <v>218.601968980972</v>
+        <v>220.513689700972</v>
       </c>
       <c r="Q21">
-        <v>256.401968980972</v>
+        <v>258.313689700972</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1011046324366641</v>
+        <v>0.1010921506465783</v>
       </c>
       <c r="T21">
         <v>0.80456816334424</v>
       </c>
       <c r="U21">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.873309628878984</v>
+        <v>5.044170392085065</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09204028709688922</v>
+        <v>0.0916662090110236</v>
       </c>
       <c r="C22">
-        <v>4413.815243439132</v>
+        <v>4453.946341428737</v>
       </c>
       <c r="D22">
-        <v>5053.895243439132</v>
+        <v>5094.026341428736</v>
       </c>
       <c r="E22">
         <v>-384.72</v>
@@ -3097,37 +3097,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M22">
-        <v>84.86921957748574</v>
+        <v>81.99445157748573</v>
       </c>
       <c r="N22">
-        <v>308.0450661368</v>
+        <v>310.9198341368</v>
       </c>
       <c r="O22">
-        <v>92.41351984103999</v>
+        <v>93.27595024103999</v>
       </c>
       <c r="P22">
-        <v>215.63154629576</v>
+        <v>217.64388389576</v>
       </c>
       <c r="Q22">
-        <v>253.43154629576</v>
+        <v>255.44388389576</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1016177984322323</v>
+        <v>0.1016052008249002</v>
       </c>
       <c r="T22">
         <v>0.8120336685714533</v>
       </c>
       <c r="U22">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.629644147435035</v>
+        <v>4.791961872480811</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09235927598653229</v>
+        <v>0.0915848300647705</v>
       </c>
       <c r="C23">
-        <v>4323.905781639783</v>
+        <v>4407.716573917194</v>
       </c>
       <c r="D23">
-        <v>5019.269781639782</v>
+        <v>5103.080573917194</v>
       </c>
       <c r="E23">
         <v>-329.4360000000001</v>
@@ -3179,45 +3179,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M23">
-        <v>92.13118695636003</v>
+        <v>86.09417415636001</v>
       </c>
       <c r="N23">
-        <v>300.7830987579257</v>
+        <v>306.8201115579257</v>
       </c>
       <c r="O23">
-        <v>90.23492962737771</v>
+        <v>92.04603346737771</v>
       </c>
       <c r="P23">
-        <v>210.548169130548</v>
+        <v>214.774078090548</v>
       </c>
       <c r="Q23">
-        <v>248.348169130548</v>
+        <v>252.574078090548</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1021439559719921</v>
+        <v>0.1021312396153316</v>
       </c>
       <c r="T23">
         <v>0.8196881739310009</v>
       </c>
       <c r="U23">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05555024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.264726187674086</v>
+        <v>4.563773211886487</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09231426487617538</v>
+        <v>0.09188845111851743</v>
       </c>
       <c r="C24">
-        <v>4273.478848749281</v>
+        <v>4318.8145489325</v>
       </c>
       <c r="D24">
-        <v>5024.12684874928</v>
+        <v>5069.462548932499</v>
       </c>
       <c r="E24">
         <v>-274.1520000000003</v>
@@ -3261,37 +3261,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M24">
-        <v>96.5183863352343</v>
+        <v>93.23451673523429</v>
       </c>
       <c r="N24">
-        <v>296.3958993790514</v>
+        <v>299.6797689790514</v>
       </c>
       <c r="O24">
-        <v>88.91876981371541</v>
+        <v>89.90393069371542</v>
       </c>
       <c r="P24">
-        <v>207.477129565336</v>
+        <v>209.775838285336</v>
       </c>
       <c r="Q24">
-        <v>245.277129565336</v>
+        <v>247.575838285336</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1026836047307201</v>
+        <v>0.1026707665798765</v>
       </c>
       <c r="T24">
         <v>0.8275389486587423</v>
       </c>
       <c r="U24">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.070874997325264</v>
+        <v>4.214257760675444</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09270395376581846</v>
+        <v>0.09182457217226433</v>
       </c>
       <c r="C25">
-        <v>4176.453241572831</v>
+        <v>4270.566614894899</v>
       </c>
       <c r="D25">
-        <v>4982.385241572831</v>
+        <v>5076.498614894899</v>
       </c>
       <c r="E25">
         <v>-218.8680000000002</v>
@@ -3343,45 +3343,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M25">
-        <v>104.3387221141086</v>
+        <v>97.47244931410859</v>
       </c>
       <c r="N25">
-        <v>288.5755636001771</v>
+        <v>295.4418364001771</v>
       </c>
       <c r="O25">
-        <v>86.57266908005313</v>
+        <v>88.63255092005313</v>
       </c>
       <c r="P25">
-        <v>202.002894520124</v>
+        <v>206.809285480124</v>
       </c>
       <c r="Q25">
-        <v>239.802894520124</v>
+        <v>244.609285480124</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1032372703403241</v>
+        <v>0.1032243072318122</v>
       </c>
       <c r="T25">
         <v>0.8355936396131781</v>
       </c>
       <c r="U25">
-        <v>0.08205748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05744024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.765757120204908</v>
+        <v>4.031029162385208</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09267784265546156</v>
+        <v>0.09234869322601125</v>
       </c>
       <c r="C26">
-        <v>4123.94444630739</v>
+        <v>4158.123119772991</v>
       </c>
       <c r="D26">
-        <v>4985.160446307389</v>
+        <v>5019.339119772991</v>
       </c>
       <c r="E26">
         <v>-163.5840000000003</v>
@@ -3425,37 +3425,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M26">
-        <v>108.8751882929829</v>
+        <v>106.3542378929829</v>
       </c>
       <c r="N26">
-        <v>284.0390974213028</v>
+        <v>286.5600478213029</v>
       </c>
       <c r="O26">
-        <v>85.21172922639084</v>
+        <v>85.96801434639086</v>
       </c>
       <c r="P26">
-        <v>198.827368194912</v>
+        <v>200.592033474912</v>
       </c>
       <c r="Q26">
-        <v>236.627368194912</v>
+        <v>238.392033474912</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1038055060975493</v>
+        <v>0.1037924147430094</v>
       </c>
       <c r="T26">
         <v>0.8438602961190467</v>
       </c>
       <c r="U26">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.05744024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.608850573529704</v>
+        <v>3.694392376819521</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09347423154510465</v>
+        <v>0.09230931427975815</v>
       </c>
       <c r="C27">
-        <v>3985.384297665722</v>
+        <v>4107.088941308408</v>
       </c>
       <c r="D27">
-        <v>4901.884297665722</v>
+        <v>5023.588941308408</v>
       </c>
       <c r="E27">
         <v>-108.3000000000002</v>
@@ -3507,45 +3507,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M27">
-        <v>119.9075244718572</v>
+        <v>110.7856644718572</v>
       </c>
       <c r="N27">
-        <v>273.0067612424285</v>
+        <v>282.1286212424286</v>
       </c>
       <c r="O27">
-        <v>81.90202837272855</v>
+        <v>84.63858637272857</v>
       </c>
       <c r="P27">
-        <v>191.1047328697</v>
+        <v>197.4900348697</v>
       </c>
       <c r="Q27">
-        <v>228.9047328697</v>
+        <v>235.2900348697</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1043888948083005</v>
+        <v>0.1043756717878385</v>
       </c>
       <c r="T27">
         <v>0.8523473967984049</v>
       </c>
       <c r="U27">
-        <v>0.08675748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.06073024175551697</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.276810921123674</v>
+        <v>3.54661668174674</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09348102043474772</v>
+        <v>0.09277953533350507</v>
       </c>
       <c r="C28">
-        <v>3929.402360599012</v>
+        <v>4001.523531141102</v>
       </c>
       <c r="D28">
-        <v>4901.186360599012</v>
+        <v>4973.307531141102</v>
       </c>
       <c r="E28">
         <v>-53.01600000000008</v>
@@ -3589,37 +3589,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M28">
-        <v>124.7038254507315</v>
+        <v>119.2417662507315</v>
       </c>
       <c r="N28">
-        <v>268.2104602635542</v>
+        <v>273.6725194635542</v>
       </c>
       <c r="O28">
-        <v>80.46313807906627</v>
+        <v>82.10175583906627</v>
       </c>
       <c r="P28">
-        <v>187.747322184488</v>
+        <v>191.570763624488</v>
       </c>
       <c r="Q28">
-        <v>225.547322184488</v>
+        <v>229.370763624488</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1049880507815045</v>
+        <v>0.104974692536582</v>
       </c>
       <c r="T28">
         <v>0.8610638785772051</v>
       </c>
       <c r="U28">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.150779731849686</v>
+        <v>3.295106220484012</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09348780932439081</v>
+        <v>0.09275975638725199</v>
       </c>
       <c r="C29">
-        <v>3873.420622250497</v>
+        <v>3948.3342349881</v>
       </c>
       <c r="D29">
-        <v>4900.488622250497</v>
+        <v>4975.4022349881</v>
       </c>
       <c r="E29">
         <v>2.267999999999802</v>
@@ -3671,37 +3671,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M29">
-        <v>129.5001264296057</v>
+        <v>123.8279880296057</v>
       </c>
       <c r="N29">
-        <v>263.41415928468</v>
+        <v>269.0862976846799</v>
       </c>
       <c r="O29">
-        <v>79.02424778540399</v>
+        <v>80.72588930540398</v>
       </c>
       <c r="P29">
-        <v>184.389911499276</v>
+        <v>188.360408379276</v>
       </c>
       <c r="Q29">
-        <v>222.189911499276</v>
+        <v>226.160408379276</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.105603621986851</v>
+        <v>0.1055901248126882</v>
       </c>
       <c r="T29">
         <v>0.8700191680759727</v>
       </c>
       <c r="U29">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.034084186225624</v>
+        <v>3.173065249354974</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.0953173982140339</v>
+        <v>0.09273997744099889</v>
       </c>
       <c r="C30">
-        <v>3637.071383355315</v>
+        <v>3895.146704112251</v>
       </c>
       <c r="D30">
-        <v>4719.423383355315</v>
+        <v>4977.49870411225</v>
       </c>
       <c r="E30">
         <v>57.55199999999991</v>
@@ -3753,45 +3753,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M30">
-        <v>148.69238100848</v>
+        <v>128.41420980848</v>
       </c>
       <c r="N30">
-        <v>244.2219047058057</v>
+        <v>264.5000759058057</v>
       </c>
       <c r="O30">
-        <v>73.26657141174171</v>
+        <v>79.35002277174171</v>
       </c>
       <c r="P30">
-        <v>170.955333294064</v>
+        <v>185.150053134064</v>
       </c>
       <c r="Q30">
-        <v>208.755333294064</v>
+        <v>222.950053134064</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.106236292392346</v>
+        <v>0.1062226524297974</v>
       </c>
       <c r="T30">
         <v>0.8792232156163725</v>
       </c>
       <c r="U30">
-        <v>0.09605748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.06724024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.642464146780174</v>
+        <v>3.05974149044944</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09538928710367699</v>
+        <v>0.09430359849474582</v>
       </c>
       <c r="C31">
-        <v>3574.945701883353</v>
+        <v>3679.401995829111</v>
       </c>
       <c r="D31">
-        <v>4712.581701883352</v>
+        <v>4817.037995829111</v>
       </c>
       <c r="E31">
         <v>112.8359999999998</v>
@@ -3835,37 +3835,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M31">
-        <v>154.0028231873543</v>
+        <v>145.5056723873543</v>
       </c>
       <c r="N31">
-        <v>238.9114625269314</v>
+        <v>247.4086133269314</v>
       </c>
       <c r="O31">
-        <v>71.67343875807943</v>
+        <v>74.22258399807941</v>
       </c>
       <c r="P31">
-        <v>167.238023768852</v>
+        <v>173.186029328852</v>
       </c>
       <c r="Q31">
-        <v>205.038023768852</v>
+        <v>210.986029328852</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1068867844994043</v>
+        <v>0.1068729977262618</v>
       </c>
       <c r="T31">
         <v>0.8886865321015726</v>
       </c>
       <c r="U31">
-        <v>0.09605748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.06724024175551697</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.551344693442927</v>
+        <v>2.700336552298103</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09644817599332006</v>
+        <v>0.09433841954849273</v>
       </c>
       <c r="C32">
-        <v>3421.136921715205</v>
+        <v>3620.662293304927</v>
       </c>
       <c r="D32">
-        <v>4614.056921715204</v>
+        <v>4813.582293304926</v>
       </c>
       <c r="E32">
         <v>168.1199999999997</v>
@@ -3917,45 +3917,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M32">
-        <v>167.1083093662286</v>
+        <v>150.5231093662286</v>
       </c>
       <c r="N32">
-        <v>225.8059763480571</v>
+        <v>242.3911763480571</v>
       </c>
       <c r="O32">
-        <v>67.74179290441714</v>
+        <v>72.71735290441713</v>
       </c>
       <c r="P32">
-        <v>158.06418344364</v>
+        <v>169.67382344364</v>
       </c>
       <c r="Q32">
-        <v>195.86418344364</v>
+        <v>207.47382344364</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1075558620952357</v>
+        <v>0.1075419243169109</v>
       </c>
       <c r="T32">
         <v>0.8984202290577781</v>
       </c>
       <c r="U32">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.351255226053355</v>
+        <v>2.610325333888167</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09655296488296315</v>
+        <v>0.09437324060223963</v>
       </c>
       <c r="C33">
-        <v>3356.326347204898</v>
+        <v>3561.927545410156</v>
       </c>
       <c r="D33">
-        <v>4604.530347204897</v>
+        <v>4810.131545410156</v>
       </c>
       <c r="E33">
         <v>223.4039999999998</v>
@@ -3999,45 +3999,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M33">
-        <v>172.6785863451029</v>
+        <v>155.5405463451029</v>
       </c>
       <c r="N33">
-        <v>220.2356993691828</v>
+        <v>237.3737393691828</v>
       </c>
       <c r="O33">
-        <v>66.07070981075483</v>
+        <v>71.21212181075485</v>
       </c>
       <c r="P33">
-        <v>154.164989558428</v>
+        <v>166.161617558428</v>
       </c>
       <c r="Q33">
-        <v>191.964989558428</v>
+        <v>203.961617558428</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1082443332445694</v>
+        <v>0.1082302400841005</v>
       </c>
       <c r="T33">
         <v>0.9084360621576417</v>
       </c>
       <c r="U33">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.275408283277439</v>
+        <v>2.526121290859516</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09665775377260624</v>
+        <v>0.09528166165598655</v>
       </c>
       <c r="C34">
-        <v>3291.555030392424</v>
+        <v>3418.335581996925</v>
       </c>
       <c r="D34">
-        <v>4595.043030392423</v>
+        <v>4721.823581996924</v>
       </c>
       <c r="E34">
         <v>278.6879999999999</v>
@@ -4081,37 +4081,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M34">
-        <v>178.2488633239772</v>
+        <v>167.4574265239772</v>
       </c>
       <c r="N34">
-        <v>214.6654223903085</v>
+        <v>225.4568591903085</v>
       </c>
       <c r="O34">
-        <v>64.39962671709256</v>
+        <v>67.63705775709256</v>
       </c>
       <c r="P34">
-        <v>150.265795673216</v>
+        <v>157.819801433216</v>
       </c>
       <c r="Q34">
-        <v>188.065795673216</v>
+        <v>195.619801433216</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1089530535453541</v>
+        <v>0.1089388004326781</v>
       </c>
       <c r="T34">
         <v>0.9187464785839721</v>
       </c>
       <c r="U34">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.204301774425019</v>
+        <v>2.346353302270693</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09676254266224932</v>
+        <v>0.09534378270973345</v>
       </c>
       <c r="C35">
-        <v>3226.82272911342</v>
+        <v>3357.131068049914</v>
       </c>
       <c r="D35">
-        <v>4585.59472911342</v>
+        <v>4715.903068049914</v>
       </c>
       <c r="E35">
         <v>333.972</v>
@@ -4163,37 +4163,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M35">
-        <v>183.8191403028515</v>
+        <v>172.6904711028515</v>
       </c>
       <c r="N35">
-        <v>209.0951454114342</v>
+        <v>220.2238146114342</v>
       </c>
       <c r="O35">
-        <v>62.72854362343027</v>
+        <v>66.06714438343027</v>
       </c>
       <c r="P35">
-        <v>146.3666017880039</v>
+        <v>154.156670228004</v>
       </c>
       <c r="Q35">
-        <v>184.166601788004</v>
+        <v>191.956670228004</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.109682929676013</v>
+        <v>0.1096685118364371</v>
       </c>
       <c r="T35">
         <v>0.9293646686349691</v>
       </c>
       <c r="U35">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.137504750957595</v>
+        <v>2.275251687050369</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09686733155189241</v>
+        <v>0.09540590376348038</v>
       </c>
       <c r="C36">
-        <v>3162.129203191184</v>
+        <v>3295.941382521989</v>
       </c>
       <c r="D36">
-        <v>4576.185203191184</v>
+        <v>4709.997382521989</v>
       </c>
       <c r="E36">
         <v>389.2559999999999</v>
@@ -4245,37 +4245,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M36">
-        <v>189.3894172817258</v>
+        <v>177.9235156817257</v>
       </c>
       <c r="N36">
-        <v>203.5248684325599</v>
+        <v>214.99077003256</v>
       </c>
       <c r="O36">
-        <v>61.05746052976798</v>
+        <v>64.49723100976799</v>
       </c>
       <c r="P36">
-        <v>142.467407902792</v>
+        <v>150.493539022792</v>
       </c>
       <c r="Q36">
-        <v>180.267407902792</v>
+        <v>188.293539022792</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1104349232651767</v>
+        <v>0.1104203357069767</v>
       </c>
       <c r="T36">
         <v>0.9403046220208446</v>
       </c>
       <c r="U36">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.074636964164724</v>
+        <v>2.208332519784181</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09697212044153551</v>
+        <v>0.09546802481722727</v>
       </c>
       <c r="C37">
-        <v>3097.47421441632</v>
+        <v>3234.76646977432</v>
       </c>
       <c r="D37">
-        <v>4566.814214416319</v>
+        <v>4704.10646977432</v>
       </c>
       <c r="E37">
         <v>444.54</v>
@@ -4327,37 +4327,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M37">
-        <v>194.9596942606001</v>
+        <v>183.1565602606</v>
       </c>
       <c r="N37">
-        <v>197.9545914536857</v>
+        <v>209.7577254536857</v>
       </c>
       <c r="O37">
-        <v>59.38637743610569</v>
+        <v>62.9273176361057</v>
       </c>
       <c r="P37">
-        <v>138.56821401758</v>
+        <v>146.83040781758</v>
       </c>
       <c r="Q37">
-        <v>176.36821401758</v>
+        <v>184.63040781758</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1112100551186224</v>
+        <v>0.1111952926196867</v>
       </c>
       <c r="T37">
         <v>0.9515811893570548</v>
       </c>
       <c r="U37">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.015361622331446</v>
+        <v>2.145237304933205</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1011845093311786</v>
+        <v>0.09553014587097422</v>
       </c>
       <c r="C38">
-        <v>2694.851261879246</v>
+        <v>3173.60627444607</v>
       </c>
       <c r="D38">
-        <v>4219.475261879245</v>
+        <v>4698.230274446069</v>
       </c>
       <c r="E38">
         <v>499.8239999999996</v>
@@ -4409,45 +4409,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M38">
-        <v>232.9706224394743</v>
+        <v>188.3896048394743</v>
       </c>
       <c r="N38">
-        <v>159.9436632748114</v>
+        <v>204.5246808748114</v>
       </c>
       <c r="O38">
-        <v>47.98309898244342</v>
+        <v>61.35740426244342</v>
       </c>
       <c r="P38">
-        <v>111.960564292368</v>
+        <v>143.167276612368</v>
       </c>
       <c r="Q38">
-        <v>149.760564292368</v>
+        <v>180.967276612368</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1120094098424883</v>
+        <v>0.1119944669359189</v>
       </c>
       <c r="T38">
         <v>0.9632101494225217</v>
       </c>
       <c r="U38">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>1.686540052131958</v>
+        <v>2.085647379796172</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1014033982208217</v>
+        <v>0.09559226692472111</v>
       </c>
       <c r="C39">
-        <v>2622.956833658991</v>
+        <v>3112.460741452695</v>
       </c>
       <c r="D39">
-        <v>4202.86483365899</v>
+        <v>4692.368741452695</v>
       </c>
       <c r="E39">
         <v>555.1079999999997</v>
@@ -4491,45 +4491,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M39">
-        <v>239.4420286183486</v>
+        <v>193.6226494183486</v>
       </c>
       <c r="N39">
-        <v>153.4722570959371</v>
+        <v>199.2916362959371</v>
       </c>
       <c r="O39">
-        <v>46.04167712878112</v>
+        <v>59.78749088878113</v>
       </c>
       <c r="P39">
-        <v>107.430579967156</v>
+        <v>139.504145407156</v>
       </c>
       <c r="Q39">
-        <v>145.230579967156</v>
+        <v>177.304145407156</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1128341409067943</v>
+        <v>0.1128190118653648</v>
       </c>
       <c r="T39">
         <v>0.9752082828234</v>
       </c>
       <c r="U39">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.640957888560824</v>
+        <v>2.029278531693572</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1016222871104648</v>
+        <v>0.09943158797846804</v>
       </c>
       <c r="C40">
-        <v>2551.192670190604</v>
+        <v>2721.26444088393</v>
       </c>
       <c r="D40">
-        <v>4186.384670190603</v>
+        <v>4356.45644088393</v>
       </c>
       <c r="E40">
         <v>610.3919999999998</v>
@@ -4573,37 +4573,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M40">
-        <v>245.9134347972229</v>
+        <v>228.6869403972229</v>
       </c>
       <c r="N40">
-        <v>147.0008509170628</v>
+        <v>164.2273453170628</v>
       </c>
       <c r="O40">
-        <v>44.10025527511883</v>
+        <v>49.26820359511884</v>
       </c>
       <c r="P40">
-        <v>102.900595641944</v>
+        <v>114.959141721944</v>
       </c>
       <c r="Q40">
-        <v>140.700595641944</v>
+        <v>152.759141721944</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1136854761989812</v>
+        <v>0.1136701550183413</v>
       </c>
       <c r="T40">
         <v>0.9875934527855972</v>
       </c>
       <c r="U40">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.597774786230276</v>
+        <v>1.718131717673971</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1018411760001079</v>
+        <v>0.09959310903221497</v>
       </c>
       <c r="C41">
-        <v>2479.557245087121</v>
+        <v>2652.899593771846</v>
       </c>
       <c r="D41">
-        <v>4170.033245087121</v>
+        <v>4343.375593771845</v>
       </c>
       <c r="E41">
         <v>665.6759999999999</v>
@@ -4655,37 +4655,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M41">
-        <v>252.3848409760972</v>
+        <v>234.7050177760972</v>
       </c>
       <c r="N41">
-        <v>140.5294447381885</v>
+        <v>158.2092679381885</v>
       </c>
       <c r="O41">
-        <v>42.15883342145654</v>
+        <v>47.46278038145655</v>
       </c>
       <c r="P41">
-        <v>98.37061131673195</v>
+        <v>110.7464875567319</v>
       </c>
       <c r="Q41">
-        <v>136.170611316732</v>
+        <v>148.546487556732</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1145647241236988</v>
+        <v>0.1145492045042022</v>
       </c>
       <c r="T41">
         <v>1.000384693894096</v>
       </c>
       <c r="U41">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.556806201967961</v>
+        <v>1.674077058246433</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1020600648897509</v>
+        <v>0.09975463008596187</v>
       </c>
       <c r="C42">
-        <v>2408.049055716196</v>
+        <v>2584.613065506766</v>
       </c>
       <c r="D42">
-        <v>4153.809055716196</v>
+        <v>4330.373065506766</v>
       </c>
       <c r="E42">
         <v>720.96</v>
@@ -4737,37 +4737,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M42">
-        <v>258.8562471549715</v>
+        <v>240.7230951549715</v>
       </c>
       <c r="N42">
-        <v>134.0580385593142</v>
+        <v>152.1911905593142</v>
       </c>
       <c r="O42">
-        <v>40.21741156779425</v>
+        <v>45.65735716779426</v>
       </c>
       <c r="P42">
-        <v>93.84062699151994</v>
+        <v>106.5338333915199</v>
       </c>
       <c r="Q42">
-        <v>131.64062699152</v>
+        <v>144.33383339152</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1154732803125736</v>
+        <v>0.1154575556395918</v>
       </c>
       <c r="T42">
         <v>1.013602309706211</v>
       </c>
       <c r="U42">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V42">
         <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.517886046918762</v>
+        <v>1.632225131790273</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1224612128747473</v>
+        <v>0.09991615113970878</v>
       </c>
       <c r="C43">
-        <v>1247.349812866591</v>
+        <v>2516.404154811396</v>
       </c>
       <c r="D43">
-        <v>3048.393812866591</v>
+        <v>4317.448154811395</v>
       </c>
       <c r="E43">
         <v>776.2440000000001</v>
@@ -4819,45 +4819,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M43">
-        <v>413.5661709338458</v>
+        <v>246.7411725338458</v>
       </c>
       <c r="N43">
-        <v>-20.65188521956009</v>
+        <v>146.1731131804399</v>
       </c>
       <c r="O43">
-        <v>-6.195565565868026</v>
+        <v>43.85193395413197</v>
       </c>
       <c r="P43">
-        <v>-14.45631965369206</v>
+        <v>102.3211792263079</v>
       </c>
       <c r="Q43">
-        <v>23.34368034630795</v>
+        <v>140.121179226308</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1169071763912423</v>
+        <v>0.1163966983388929</v>
       </c>
       <c r="T43">
-        <v>1.034462535759827</v>
+        <v>1.027267980291618</v>
       </c>
       <c r="U43">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V43">
-        <v>0.2850191674239742</v>
+        <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.1304536068388155</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.9500638914132472</v>
+        <v>1.592414762722217</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.123827787756969</v>
+        <v>0.1000776721934557</v>
       </c>
       <c r="C44">
-        <v>1138.676391795745</v>
+        <v>2448.272168755964</v>
       </c>
       <c r="D44">
-        <v>2995.004391795745</v>
+        <v>4304.600168755964</v>
       </c>
       <c r="E44">
         <v>831.5279999999998</v>
@@ -4901,45 +4901,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M44">
-        <v>423.65315071272</v>
+        <v>252.75924991272</v>
       </c>
       <c r="N44">
-        <v>-30.73886499843434</v>
+        <v>140.1550358015657</v>
       </c>
       <c r="O44">
-        <v>-9.221659499530301</v>
+        <v>42.0465107404697</v>
       </c>
       <c r="P44">
-        <v>-21.51720549890404</v>
+        <v>98.10852506109597</v>
       </c>
       <c r="Q44">
-        <v>16.28279450109597</v>
+        <v>135.908525061096</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1181331621910913</v>
+        <v>0.1173682252692044</v>
       </c>
       <c r="T44">
-        <v>1.052298096721203</v>
+        <v>1.041404880897212</v>
       </c>
       <c r="U44">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V44">
-        <v>0.2782329967710224</v>
+        <v>0.3</v>
       </c>
       <c r="W44">
-        <v>0.1316917944908</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.9274433225700748</v>
+        <v>1.554500125514546</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1251943626391906</v>
+        <v>0.1002391932472026</v>
       </c>
       <c r="C45">
-        <v>1031.840900758882</v>
+        <v>2380.216422634389</v>
       </c>
       <c r="D45">
-        <v>2943.452900758882</v>
+        <v>4291.828422634389</v>
       </c>
       <c r="E45">
         <v>886.8119999999999</v>
@@ -4983,45 +4983,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M45">
-        <v>433.7401304915944</v>
+        <v>258.7773272915944</v>
       </c>
       <c r="N45">
-        <v>-40.82584477730865</v>
+        <v>134.1369584226914</v>
       </c>
       <c r="O45">
-        <v>-12.24775343319259</v>
+        <v>40.24108752680741</v>
       </c>
       <c r="P45">
-        <v>-28.57809134411605</v>
+        <v>93.89587089588395</v>
       </c>
       <c r="Q45">
-        <v>9.221908655883958</v>
+        <v>131.695870895884</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.119402165036549</v>
+        <v>0.1183738408637374</v>
       </c>
       <c r="T45">
-        <v>1.070759466839119</v>
+        <v>1.056037813103002</v>
       </c>
       <c r="U45">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V45">
-        <v>0.271762461962394</v>
+        <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.1328723920194365</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.90587487320798</v>
+        <v>1.518348959804905</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1265609375214123</v>
+        <v>0.1185966186773166</v>
       </c>
       <c r="C46">
-        <v>926.7500396125133</v>
+        <v>1242.644238665419</v>
       </c>
       <c r="D46">
-        <v>2893.646039612513</v>
+        <v>3209.540238665419</v>
       </c>
       <c r="E46">
         <v>942.0959999999995</v>
@@ -5065,37 +5065,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M46">
-        <v>443.8271102704686</v>
+        <v>402.9611774704686</v>
       </c>
       <c r="N46">
-        <v>-50.91282455618284</v>
+        <v>-10.0468917561829</v>
       </c>
       <c r="O46">
-        <v>-15.27384736685485</v>
+        <v>-3.01406752685487</v>
       </c>
       <c r="P46">
-        <v>-35.63897718932799</v>
+        <v>-7.032824229328032</v>
       </c>
       <c r="Q46">
-        <v>2.161022810672023</v>
+        <v>30.76717577067198</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1207164894122017</v>
+        <v>0.1196944914763165</v>
       </c>
       <c r="T46">
-        <v>1.089880171604104</v>
+        <v>1.075254888679859</v>
       </c>
       <c r="U46">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V46">
-        <v>0.2655860423723396</v>
+        <v>0.2925202036936281</v>
       </c>
       <c r="W46">
-        <v>0.133999326024044</v>
+        <v>0.117199326024044</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8852868079077988</v>
+        <v>0.9750673456454271</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.127927512403634</v>
+        <v>0.1197951935595383</v>
       </c>
       <c r="C47">
-        <v>823.3167181483486</v>
+        <v>1135.372073914573</v>
       </c>
       <c r="D47">
-        <v>2845.496718148348</v>
+        <v>3157.552073914573</v>
       </c>
       <c r="E47">
         <v>997.3799999999997</v>
@@ -5147,37 +5147,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M47">
-        <v>453.9140900493429</v>
+        <v>412.1193860493429</v>
       </c>
       <c r="N47">
-        <v>-60.99980433505715</v>
+        <v>-19.20510033505718</v>
       </c>
       <c r="O47">
-        <v>-18.29994130051714</v>
+        <v>-5.761530100517154</v>
       </c>
       <c r="P47">
-        <v>-42.69986303454</v>
+        <v>-13.44357023454003</v>
       </c>
       <c r="Q47">
-        <v>-4.89986303453999</v>
+        <v>24.35642976545999</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1220786074015144</v>
+        <v>0.1210380276849768</v>
       </c>
       <c r="T47">
-        <v>1.109696174724178</v>
+        <v>1.094804977564947</v>
       </c>
       <c r="U47">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V47">
-        <v>0.259684130319621</v>
+        <v>0.2860197547226586</v>
       </c>
       <c r="W47">
-        <v>0.1350761740728912</v>
+        <v>0.1182761740728912</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8656137677320699</v>
+        <v>0.9533991824088621</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1292940872858556</v>
+        <v>0.1209937684417599</v>
       </c>
       <c r="C48">
-        <v>721.459547893161</v>
+        <v>1029.757272791974</v>
       </c>
       <c r="D48">
-        <v>2798.923547893161</v>
+        <v>3107.221272791974</v>
       </c>
       <c r="E48">
         <v>1052.664</v>
@@ -5229,37 +5229,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M48">
-        <v>464.0010698282172</v>
+        <v>421.2775946282172</v>
       </c>
       <c r="N48">
-        <v>-71.08678411393146</v>
+        <v>-28.36330891393152</v>
       </c>
       <c r="O48">
-        <v>-21.32603523417944</v>
+        <v>-8.508992674179455</v>
       </c>
       <c r="P48">
-        <v>-49.76074887975202</v>
+        <v>-19.85431623975207</v>
       </c>
       <c r="Q48">
-        <v>-11.96074887975201</v>
+        <v>17.94568376024795</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1234911742052462</v>
+        <v>0.1224313244939578</v>
       </c>
       <c r="T48">
-        <v>1.130246103885737</v>
+        <v>1.11507914381615</v>
       </c>
       <c r="U48">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V48">
-        <v>0.2540388231387596</v>
+        <v>0.2798019339678182</v>
       </c>
       <c r="W48">
-        <v>0.1361062026413537</v>
+        <v>0.1193062026413537</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8467960771291987</v>
+        <v>0.9326731132260606</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1306606621680773</v>
+        <v>0.1221923433239816</v>
       </c>
       <c r="C49">
-        <v>621.1023830121958</v>
+        <v>925.7218245574468</v>
       </c>
       <c r="D49">
-        <v>2753.850383012196</v>
+        <v>3058.469824557447</v>
       </c>
       <c r="E49">
         <v>1107.948</v>
@@ -5311,37 +5311,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M49">
-        <v>474.0880496070915</v>
+        <v>430.4358032070915</v>
       </c>
       <c r="N49">
-        <v>-81.17376389280577</v>
+        <v>-37.5215174928058</v>
       </c>
       <c r="O49">
-        <v>-24.35212916784173</v>
+        <v>-11.25645524784174</v>
       </c>
       <c r="P49">
-        <v>-56.82163472496404</v>
+        <v>-26.26506224496406</v>
       </c>
       <c r="Q49">
-        <v>-19.02163472496403</v>
+        <v>11.53493775503595</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1249570454166659</v>
+        <v>0.1238771985410136</v>
       </c>
       <c r="T49">
-        <v>1.15157150207226</v>
+        <v>1.136118372944756</v>
       </c>
       <c r="U49">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V49">
-        <v>0.2486337417953817</v>
+        <v>0.2738487013302051</v>
       </c>
       <c r="W49">
-        <v>0.1370924002069029</v>
+        <v>0.1202924002069029</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8287791393179391</v>
+        <v>0.9128290044340168</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.132027237050299</v>
+        <v>0.1233909182062033</v>
       </c>
       <c r="C50">
-        <v>522.1739048686413</v>
+        <v>823.1925387109086</v>
       </c>
       <c r="D50">
-        <v>2710.205904868641</v>
+        <v>3011.224538710908</v>
       </c>
       <c r="E50">
         <v>1163.232</v>
@@ -5393,37 +5393,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M50">
-        <v>484.1750293859657</v>
+        <v>439.5940117859657</v>
       </c>
       <c r="N50">
-        <v>-91.26074367168002</v>
+        <v>-46.67972607168002</v>
       </c>
       <c r="O50">
-        <v>-27.37822310150401</v>
+        <v>-14.00391782150401</v>
       </c>
       <c r="P50">
-        <v>-63.88252057017601</v>
+        <v>-32.67580825017602</v>
       </c>
       <c r="Q50">
-        <v>-26.082520570176</v>
+        <v>5.124191749823993</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1264792962900633</v>
+        <v>0.1253786831283408</v>
       </c>
       <c r="T50">
-        <v>1.173717107881342</v>
+        <v>1.157966803193694</v>
       </c>
       <c r="U50">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V50">
-        <v>0.2434538721746446</v>
+        <v>0.2681435200524925</v>
       </c>
       <c r="W50">
-        <v>0.1380375062072209</v>
+        <v>0.1212375062072209</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8115129072488154</v>
+        <v>0.8938117335083082</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1602067035584738</v>
+        <v>0.1245894930884249</v>
       </c>
       <c r="C51">
-        <v>-200.6597591898931</v>
+        <v>722.1006783560019</v>
       </c>
       <c r="D51">
-        <v>2042.656240810107</v>
+        <v>2965.416678356002</v>
       </c>
       <c r="E51">
         <v>1218.516</v>
@@ -5475,45 +5475,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M51">
-        <v>635.66742436484</v>
+        <v>448.7522203648401</v>
       </c>
       <c r="N51">
-        <v>-242.7531386505543</v>
+        <v>-55.83793465055436</v>
       </c>
       <c r="O51">
-        <v>-72.8259415951663</v>
+        <v>-16.75138039516631</v>
       </c>
       <c r="P51">
-        <v>-169.927197055388</v>
+        <v>-39.08655425538805</v>
       </c>
       <c r="Q51">
-        <v>-132.127197055388</v>
+        <v>-1.28655425538804</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1304825994054629</v>
+        <v>0.1269390494641906</v>
       </c>
       <c r="T51">
-        <v>1.231956898889012</v>
+        <v>1.180672034628864</v>
       </c>
       <c r="U51">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V51">
-        <v>0.1854338938825847</v>
+        <v>0.2626712033167273</v>
       </c>
       <c r="W51">
-        <v>0.1911440364524239</v>
+        <v>0.1221440364524239</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.6181129796086158</v>
+        <v>0.8755706777224243</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1620952784406955</v>
+        <v>0.1257880679706466</v>
       </c>
       <c r="C52">
-        <v>-289.1154349546546</v>
+        <v>622.3816265267333</v>
       </c>
       <c r="D52">
-        <v>2009.484565045345</v>
+        <v>2920.981626526733</v>
       </c>
       <c r="E52">
         <v>1273.8</v>
@@ -5557,45 +5557,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M52">
-        <v>648.6402289437144</v>
+        <v>457.9104289437144</v>
       </c>
       <c r="N52">
-        <v>-255.7259432294287</v>
+        <v>-64.99614322942864</v>
       </c>
       <c r="O52">
-        <v>-76.71778296882862</v>
+        <v>-19.49884296882859</v>
       </c>
       <c r="P52">
-        <v>-179.0081602606001</v>
+        <v>-45.49730026060005</v>
       </c>
       <c r="Q52">
-        <v>-141.2081602606001</v>
+        <v>-7.697300260600038</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1321762513935722</v>
+        <v>0.1285618304534745</v>
       </c>
       <c r="T52">
-        <v>1.256596036866792</v>
+        <v>1.204285475321441</v>
       </c>
       <c r="U52">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V52">
-        <v>0.181725216004933</v>
+        <v>0.2574177792503927</v>
       </c>
       <c r="W52">
-        <v>0.1920143054878188</v>
+        <v>0.1230143054878188</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.6057507200164434</v>
+        <v>0.8580592641679758</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1639838533229172</v>
+        <v>0.1269866428528683</v>
       </c>
       <c r="C53">
-        <v>-376.5109456987448</v>
+        <v>523.9745820706298</v>
       </c>
       <c r="D53">
-        <v>1977.373054301255</v>
+        <v>2877.85858207063</v>
       </c>
       <c r="E53">
         <v>1329.084</v>
@@ -5639,45 +5639,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M53">
-        <v>661.6130335225887</v>
+        <v>467.0686375225887</v>
       </c>
       <c r="N53">
-        <v>-268.698747808303</v>
+        <v>-74.15435180830298</v>
       </c>
       <c r="O53">
-        <v>-80.60962434249089</v>
+        <v>-22.24630554249089</v>
       </c>
       <c r="P53">
-        <v>-188.0891234658121</v>
+        <v>-51.90804626581209</v>
       </c>
       <c r="Q53">
-        <v>-150.2891234658121</v>
+        <v>-14.10804626581208</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1339390320342573</v>
+        <v>0.1302508474015046</v>
       </c>
       <c r="T53">
-        <v>1.282240853945707</v>
+        <v>1.228862729919838</v>
       </c>
       <c r="U53">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V53">
-        <v>0.1781619764754245</v>
+        <v>0.2523703718141105</v>
       </c>
       <c r="W53">
-        <v>0.1928504463257472</v>
+        <v>0.1238504463257472</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.5938732549180818</v>
+        <v>0.8412345727137017</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1658724282051388</v>
+        <v>0.12818521773509</v>
       </c>
       <c r="C54">
-        <v>-462.8963162544828</v>
+        <v>426.8222820784254</v>
       </c>
       <c r="D54">
-        <v>1946.271683745517</v>
+        <v>2835.990282078425</v>
       </c>
       <c r="E54">
         <v>1384.368</v>
@@ -5721,45 +5721,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M54">
-        <v>674.585838101463</v>
+        <v>476.226846101463</v>
       </c>
       <c r="N54">
-        <v>-281.6715523871773</v>
+        <v>-83.31256038717726</v>
       </c>
       <c r="O54">
-        <v>-84.50146571615318</v>
+        <v>-24.99376811615318</v>
       </c>
       <c r="P54">
-        <v>-197.1700866710241</v>
+        <v>-58.31879227102408</v>
       </c>
       <c r="Q54">
-        <v>-159.3700866710241</v>
+        <v>-20.51879227102407</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1357752618683043</v>
+        <v>0.1320102400557026</v>
       </c>
       <c r="T54">
-        <v>1.308954205069575</v>
+        <v>1.254464036793168</v>
       </c>
       <c r="U54">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V54">
-        <v>0.1747357846201279</v>
+        <v>0.2475170954330699</v>
       </c>
       <c r="W54">
-        <v>0.1936544279006784</v>
+        <v>0.1246544279006783</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.5824526154004264</v>
+        <v>0.8250569847768998</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1677610030873605</v>
+        <v>0.1293837926173116</v>
       </c>
       <c r="C55">
-        <v>-548.3184729017198</v>
+        <v>330.8707481955466</v>
       </c>
       <c r="D55">
-        <v>1916.13352709828</v>
+        <v>2795.322748195547</v>
       </c>
       <c r="E55">
         <v>1439.652</v>
@@ -5803,45 +5803,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M55">
-        <v>687.5586426803374</v>
+        <v>485.3850546803373</v>
       </c>
       <c r="N55">
-        <v>-294.6443569660516</v>
+        <v>-92.47076896605159</v>
       </c>
       <c r="O55">
-        <v>-88.39330708981549</v>
+        <v>-27.74123068981548</v>
       </c>
       <c r="P55">
-        <v>-206.2510498762362</v>
+        <v>-64.72953827623611</v>
       </c>
       <c r="Q55">
-        <v>-168.4510498762361</v>
+        <v>-26.9295382762361</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.137689629142098</v>
+        <v>0.1338445004824196</v>
       </c>
       <c r="T55">
-        <v>1.336804294539141</v>
+        <v>1.281154760980257</v>
       </c>
       <c r="U55">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V55">
-        <v>0.1714388830235217</v>
+        <v>0.2428469615569742</v>
       </c>
       <c r="W55">
-        <v>0.1944280705482536</v>
+        <v>0.1254280705482536</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.5714629434117391</v>
+        <v>0.8094898718565808</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1696495779695822</v>
+        <v>0.1612451395150766</v>
       </c>
       <c r="C56">
-        <v>-632.8214796160537</v>
+        <v>-495.8857290830724</v>
       </c>
       <c r="D56">
-        <v>1886.914520383946</v>
+        <v>2023.850270916927</v>
       </c>
       <c r="E56">
         <v>1494.936</v>
@@ -5885,37 +5885,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M56">
-        <v>700.5314472592115</v>
+        <v>655.7514072592115</v>
       </c>
       <c r="N56">
-        <v>-307.6171615449258</v>
+        <v>-262.8371215449258</v>
       </c>
       <c r="O56">
-        <v>-92.28514846347774</v>
+        <v>-78.85113646347774</v>
       </c>
       <c r="P56">
-        <v>-215.3320130814481</v>
+        <v>-183.9859850814481</v>
       </c>
       <c r="Q56">
-        <v>-177.532013081448</v>
+        <v>-146.1859850814481</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1396872297756219</v>
+        <v>0.1390254070484359</v>
       </c>
       <c r="T56">
-        <v>1.365865257463905</v>
+        <v>1.356543264258447</v>
       </c>
       <c r="U56">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V56">
-        <v>0.1682640888934565</v>
+        <v>0.1797545295509999</v>
       </c>
       <c r="W56">
-        <v>0.1951730597644372</v>
+        <v>0.1801730597644372</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5608802963115218</v>
+        <v>0.5991817651699997</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1715381528518038</v>
+        <v>0.1629837143972983</v>
       </c>
       <c r="C57">
-        <v>-716.4467530264924</v>
+        <v>-581.1962158222127</v>
       </c>
       <c r="D57">
-        <v>1858.573246973507</v>
+        <v>1993.823784177787</v>
       </c>
       <c r="E57">
         <v>1550.22</v>
@@ -5967,37 +5967,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M57">
-        <v>713.5042518380858</v>
+        <v>667.8949518380858</v>
       </c>
       <c r="N57">
-        <v>-320.5899661238001</v>
+        <v>-274.9806661238001</v>
       </c>
       <c r="O57">
-        <v>-96.17698983714003</v>
+        <v>-82.49419983714003</v>
       </c>
       <c r="P57">
-        <v>-224.4129762866601</v>
+        <v>-192.4864662866601</v>
       </c>
       <c r="Q57">
-        <v>-186.6129762866601</v>
+        <v>-154.6864662866601</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1417736126595246</v>
+        <v>0.1410970827606233</v>
       </c>
       <c r="T57">
-        <v>1.39621781874088</v>
+        <v>1.386688670130857</v>
       </c>
       <c r="U57">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V57">
-        <v>0.1652047418226664</v>
+        <v>0.1764862653773454</v>
       </c>
       <c r="W57">
-        <v>0.1958909584636686</v>
+        <v>0.1808909584636686</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5506824727422213</v>
+        <v>0.5882875512578178</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1734267277340255</v>
+        <v>0.1647222892795199</v>
       </c>
       <c r="C58">
-        <v>-799.2332582879162</v>
+        <v>-665.6287629259446</v>
       </c>
       <c r="D58">
-        <v>1831.070741712084</v>
+        <v>1964.675237074056</v>
       </c>
       <c r="E58">
         <v>1605.504</v>
@@ -6049,37 +6049,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M58">
-        <v>726.4770564169602</v>
+        <v>680.0384964169601</v>
       </c>
       <c r="N58">
-        <v>-333.5627707026745</v>
+        <v>-287.1242107026744</v>
       </c>
       <c r="O58">
-        <v>-100.0688312108023</v>
+        <v>-86.13726321080232</v>
       </c>
       <c r="P58">
-        <v>-233.4939394918721</v>
+        <v>-200.9869474918721</v>
       </c>
       <c r="Q58">
-        <v>-195.6939394918721</v>
+        <v>-163.1869474918721</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1439548311290593</v>
+        <v>0.1432629255506375</v>
       </c>
       <c r="T58">
-        <v>1.427950041894082</v>
+        <v>1.418204321724741</v>
       </c>
       <c r="U58">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V58">
-        <v>0.1622546571472616</v>
+        <v>0.1733347249241785</v>
       </c>
       <c r="W58">
-        <v>0.1965832179236418</v>
+        <v>0.1815832179236418</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5408488571575387</v>
+        <v>0.5777824164139282</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1753153026162472</v>
+        <v>0.1664608641617416</v>
       </c>
       <c r="C59">
-        <v>-881.2176878164241</v>
+        <v>-749.2213204904019</v>
       </c>
       <c r="D59">
-        <v>1804.370312183576</v>
+        <v>1936.366679509598</v>
       </c>
       <c r="E59">
         <v>1660.788</v>
@@ -6131,37 +6131,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M59">
-        <v>739.4498609958345</v>
+        <v>692.1820409958344</v>
       </c>
       <c r="N59">
-        <v>-346.5355752815487</v>
+        <v>-299.2677552815487</v>
       </c>
       <c r="O59">
-        <v>-103.9606725844646</v>
+        <v>-89.78032658446462</v>
       </c>
       <c r="P59">
-        <v>-242.5749026970841</v>
+        <v>-209.4874286970841</v>
       </c>
       <c r="Q59">
-        <v>-204.7749026970841</v>
+        <v>-171.6874286970841</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1462375016204328</v>
+        <v>0.1455295052146058</v>
       </c>
       <c r="T59">
-        <v>1.461158182403247</v>
+        <v>1.451185817578805</v>
       </c>
       <c r="U59">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V59">
-        <v>0.1594080842148535</v>
+        <v>0.1702937648377894</v>
       </c>
       <c r="W59">
-        <v>0.1972511875780019</v>
+        <v>0.1822511875780019</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5313602807161784</v>
+        <v>0.5676458827926312</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1772038774984688</v>
+        <v>0.1681994390439632</v>
       </c>
       <c r="C60">
-        <v>-962.4346246116565</v>
+        <v>-832.0096824226248</v>
       </c>
       <c r="D60">
-        <v>1778.437375388343</v>
+        <v>1908.862317577375</v>
       </c>
       <c r="E60">
         <v>1716.072</v>
@@ -6213,37 +6213,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M60">
-        <v>752.4226655747086</v>
+        <v>704.3255855747086</v>
       </c>
       <c r="N60">
-        <v>-359.5083798604229</v>
+        <v>-311.4112998604229</v>
       </c>
       <c r="O60">
-        <v>-107.8525139581269</v>
+        <v>-93.42338995812686</v>
       </c>
       <c r="P60">
-        <v>-251.6558659022961</v>
+        <v>-217.9879099022961</v>
       </c>
       <c r="Q60">
-        <v>-213.855865902296</v>
+        <v>-180.187909902296</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1486288707066335</v>
+        <v>0.1479040172435249</v>
       </c>
       <c r="T60">
-        <v>1.495947662936657</v>
+        <v>1.48573786085449</v>
       </c>
       <c r="U60">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V60">
-        <v>0.1566596689697699</v>
+        <v>0.1673576654440344</v>
       </c>
       <c r="W60">
-        <v>0.1978961237960048</v>
+        <v>0.1828961237960048</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5221988965658996</v>
+        <v>0.557858884813448</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1790924523806905</v>
+        <v>0.1699380139261849</v>
       </c>
       <c r="C61">
-        <v>-1042.91669169478</v>
+        <v>-914.0276374296132</v>
       </c>
       <c r="D61">
-        <v>1753.239308305219</v>
+        <v>1882.128362570386</v>
       </c>
       <c r="E61">
         <v>1771.355999999999</v>
@@ -6295,37 +6295,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M61">
-        <v>765.3954701535829</v>
+        <v>716.4691301535828</v>
       </c>
       <c r="N61">
-        <v>-372.4811844392972</v>
+        <v>-323.5548444392971</v>
       </c>
       <c r="O61">
-        <v>-111.7443553317892</v>
+        <v>-97.06645333178912</v>
       </c>
       <c r="P61">
-        <v>-260.736829107508</v>
+        <v>-226.488391107508</v>
       </c>
       <c r="Q61">
-        <v>-222.936829107508</v>
+        <v>-188.688391107508</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1511368919433807</v>
+        <v>0.1503943591275134</v>
       </c>
       <c r="T61">
-        <v>1.532434191300966</v>
+        <v>1.521975369655819</v>
       </c>
       <c r="U61">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V61">
-        <v>0.1540044203431636</v>
+        <v>0.1645210948432881</v>
       </c>
       <c r="W61">
-        <v>0.1985191977693296</v>
+        <v>0.1835191977693295</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5133480678105453</v>
+        <v>0.548403649477627</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1809810272629122</v>
+        <v>0.1716765888084066</v>
       </c>
       <c r="C62">
-        <v>-1122.694689019931</v>
+        <v>-995.3071074948402</v>
       </c>
       <c r="D62">
-        <v>1728.745310980069</v>
+        <v>1856.132892505159</v>
       </c>
       <c r="E62">
         <v>1826.639999999999</v>
@@ -6377,37 +6377,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M62">
-        <v>778.3682747324572</v>
+        <v>728.6126747324571</v>
       </c>
       <c r="N62">
-        <v>-385.4539890181715</v>
+        <v>-335.6983890181714</v>
       </c>
       <c r="O62">
-        <v>-115.6361967054514</v>
+        <v>-100.7095167054514</v>
       </c>
       <c r="P62">
-        <v>-269.81779231272</v>
+        <v>-234.98887231272</v>
       </c>
       <c r="Q62">
-        <v>-232.01779231272</v>
+        <v>-197.18887231272</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1537703142419652</v>
+        <v>0.1530092181057012</v>
       </c>
       <c r="T62">
-        <v>1.57074504608349</v>
+        <v>1.560024753897214</v>
       </c>
       <c r="U62">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V62">
-        <v>0.1514376800041109</v>
+        <v>0.1617790765958999</v>
       </c>
       <c r="W62">
-        <v>0.1991215026102102</v>
+        <v>0.1841215026102102</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5047922666803696</v>
+        <v>0.5392635886529998</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2016588817384947</v>
+        <v>0.1734151636906283</v>
       </c>
       <c r="C63">
-        <v>-1407.331957611762</v>
+        <v>-1075.87827503551</v>
       </c>
       <c r="D63">
-        <v>1499.392042388237</v>
+        <v>1830.845724964489</v>
       </c>
       <c r="E63">
         <v>1881.924</v>
@@ -6459,45 +6459,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M63">
-        <v>892.5107993113314</v>
+        <v>740.7562193113315</v>
       </c>
       <c r="N63">
-        <v>-499.5965135970457</v>
+        <v>-347.8419335970458</v>
       </c>
       <c r="O63">
-        <v>-149.8789540791137</v>
+        <v>-104.3525800791137</v>
       </c>
       <c r="P63">
-        <v>-349.717559517932</v>
+        <v>-243.489353517932</v>
       </c>
       <c r="Q63">
-        <v>-311.917559517932</v>
+        <v>-205.689353517932</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1577933468978126</v>
+        <v>0.1557581724161038</v>
       </c>
       <c r="T63">
-        <v>1.629271861150852</v>
+        <v>1.600025388612528</v>
       </c>
       <c r="U63">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V63">
-        <v>0.1320704307502368</v>
+        <v>0.1591269605861311</v>
       </c>
       <c r="W63">
-        <v>0.2297040597513898</v>
+        <v>0.1847040597513898</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.4402347691674561</v>
+        <v>0.5304232019537702</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2038474566207163</v>
+        <v>0.1751537385728499</v>
       </c>
       <c r="C64">
-        <v>-1483.37890965628</v>
+        <v>-1155.769699805484</v>
       </c>
       <c r="D64">
-        <v>1478.629090343719</v>
+        <v>1806.238300194516</v>
       </c>
       <c r="E64">
         <v>1937.208</v>
@@ -6541,45 +6541,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M64">
-        <v>907.1421238902057</v>
+        <v>752.8997638902058</v>
       </c>
       <c r="N64">
-        <v>-514.2278381759199</v>
+        <v>-359.9854781759201</v>
       </c>
       <c r="O64">
-        <v>-154.268351452776</v>
+        <v>-107.995643452776</v>
       </c>
       <c r="P64">
-        <v>-359.959486723144</v>
+        <v>-251.9898347231441</v>
       </c>
       <c r="Q64">
-        <v>-322.159486723144</v>
+        <v>-214.1898347231441</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1607405402372287</v>
+        <v>0.1586518085323171</v>
       </c>
       <c r="T64">
-        <v>1.672147436444295</v>
+        <v>1.642131319891805</v>
       </c>
       <c r="U64">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V64">
-        <v>0.1299402625123298</v>
+        <v>0.1565603967057096</v>
       </c>
       <c r="W64">
-        <v>0.2302678247267249</v>
+        <v>0.1852678247267249</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.4331342083744326</v>
+        <v>0.5218679890190321</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.206036031502938</v>
+        <v>0.1768923134550716</v>
       </c>
       <c r="C65">
-        <v>-1558.858682460284</v>
+        <v>-1235.008426495857</v>
       </c>
       <c r="D65">
-        <v>1458.433317539715</v>
+        <v>1782.283573504142</v>
       </c>
       <c r="E65">
         <v>1992.492</v>
@@ -6623,45 +6623,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M65">
-        <v>921.77344846908</v>
+        <v>765.0433084690801</v>
       </c>
       <c r="N65">
-        <v>-528.8591627547943</v>
+        <v>-372.1290227547944</v>
       </c>
       <c r="O65">
-        <v>-158.6577488264383</v>
+        <v>-111.6387068264383</v>
       </c>
       <c r="P65">
-        <v>-370.201413928356</v>
+        <v>-260.4903159283561</v>
       </c>
       <c r="Q65">
-        <v>-332.401413928356</v>
+        <v>-222.6903159283561</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1638470413247214</v>
+        <v>0.1617018574115689</v>
       </c>
       <c r="T65">
-        <v>1.717340610402249</v>
+        <v>1.686513247456448</v>
       </c>
       <c r="U65">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V65">
-        <v>0.1278777186629277</v>
+        <v>0.1540753110437142</v>
       </c>
       <c r="W65">
-        <v>0.2308136924012557</v>
+        <v>0.1858136924012558</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4262590622097591</v>
+        <v>0.513584370145714</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2082246063851597</v>
+        <v>0.1786308883372933</v>
       </c>
       <c r="C66">
-        <v>-1633.794203231673</v>
+        <v>-1313.620083885472</v>
       </c>
       <c r="D66">
-        <v>1438.781796768327</v>
+        <v>1758.955916114528</v>
       </c>
       <c r="E66">
         <v>2047.776</v>
@@ -6705,45 +6705,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M66">
-        <v>936.4047730479543</v>
+        <v>777.1868530479544</v>
       </c>
       <c r="N66">
-        <v>-543.4904873336686</v>
+        <v>-384.2725673336687</v>
       </c>
       <c r="O66">
-        <v>-163.0471462001006</v>
+        <v>-115.2817702001006</v>
       </c>
       <c r="P66">
-        <v>-380.4433411335681</v>
+        <v>-268.9907971335681</v>
       </c>
       <c r="Q66">
-        <v>-342.6433411335681</v>
+        <v>-231.1907971335681</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1671261258059636</v>
+        <v>0.1649213534507792</v>
       </c>
       <c r="T66">
-        <v>1.765044516246756</v>
+        <v>1.733360837663572</v>
       </c>
       <c r="U66">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V66">
-        <v>0.1258796293088195</v>
+        <v>0.1516678843086562</v>
       </c>
       <c r="W66">
-        <v>0.2313425017109575</v>
+        <v>0.1863425017109575</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4195987643627316</v>
+        <v>0.5055596143621872</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2104131812673814</v>
+        <v>0.2037530731926974</v>
       </c>
       <c r="C67">
-        <v>-1708.207179885676</v>
+        <v>-1648.663222368502</v>
       </c>
       <c r="D67">
-        <v>1419.652820114324</v>
+        <v>1479.196777631498</v>
       </c>
       <c r="E67">
         <v>2103.06</v>
@@ -6787,37 +6787,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M67">
-        <v>951.0360976268287</v>
+        <v>915.1014976268286</v>
       </c>
       <c r="N67">
-        <v>-558.121811912543</v>
+        <v>-522.1872119125429</v>
       </c>
       <c r="O67">
-        <v>-167.4365435737629</v>
+        <v>-156.6561635737629</v>
       </c>
       <c r="P67">
-        <v>-390.6852683387801</v>
+        <v>-365.53104833878</v>
       </c>
       <c r="Q67">
-        <v>-352.8852683387801</v>
+        <v>-327.73104833878</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1705925865432769</v>
+        <v>0.1701351349013228</v>
       </c>
       <c r="T67">
-        <v>1.815474359568092</v>
+        <v>1.809227710568466</v>
       </c>
       <c r="U67">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V67">
-        <v>0.1239430196271453</v>
+        <v>0.1288100675389277</v>
       </c>
       <c r="W67">
-        <v>0.2318550399649761</v>
+        <v>0.221855039964976</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.413143398757151</v>
+        <v>0.4293668917964257</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.212601756149603</v>
+        <v>0.2058416480749191</v>
       </c>
       <c r="C68">
-        <v>-1782.118181035417</v>
+        <v>-1723.251030300911</v>
       </c>
       <c r="D68">
-        <v>1401.025818964583</v>
+        <v>1459.892969699089</v>
       </c>
       <c r="E68">
         <v>2158.344</v>
@@ -6869,37 +6869,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M68">
-        <v>965.667422205703</v>
+        <v>929.1799822057029</v>
       </c>
       <c r="N68">
-        <v>-572.7531364914173</v>
+        <v>-536.2656964914172</v>
       </c>
       <c r="O68">
-        <v>-171.8259409474252</v>
+        <v>-160.8797089474251</v>
       </c>
       <c r="P68">
-        <v>-400.9271955439921</v>
+        <v>-375.3859875439921</v>
       </c>
       <c r="Q68">
-        <v>-363.1271955439921</v>
+        <v>-337.5859875439921</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1742629567357262</v>
+        <v>0.1737920506337147</v>
       </c>
       <c r="T68">
-        <v>1.868870664261271</v>
+        <v>1.862440290291067</v>
       </c>
       <c r="U68">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V68">
-        <v>0.1220650950873401</v>
+        <v>0.126858399848944</v>
       </c>
       <c r="W68">
-        <v>0.2323520467567517</v>
+        <v>0.2223520467567517</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4068836502911336</v>
+        <v>0.4228613328298133</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2147903310318247</v>
+        <v>0.2079302229571408</v>
       </c>
       <c r="C69">
-        <v>-1855.546709766782</v>
+        <v>-1797.341491746729</v>
       </c>
       <c r="D69">
-        <v>1382.881290233217</v>
+        <v>1441.08650825327</v>
       </c>
       <c r="E69">
         <v>2213.628</v>
@@ -6951,37 +6951,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M69">
-        <v>980.2987467845771</v>
+        <v>943.2584667845771</v>
       </c>
       <c r="N69">
-        <v>-587.3844610702914</v>
+        <v>-550.3441810702914</v>
       </c>
       <c r="O69">
-        <v>-176.2153383210874</v>
+        <v>-165.1032543210874</v>
       </c>
       <c r="P69">
-        <v>-411.169122749204</v>
+        <v>-385.2409267492039</v>
       </c>
       <c r="Q69">
-        <v>-373.369122749204</v>
+        <v>-347.4409267492039</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1781557736065058</v>
+        <v>0.1776705976226151</v>
       </c>
       <c r="T69">
-        <v>1.925503108632825</v>
+        <v>1.918877874845342</v>
       </c>
       <c r="U69">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V69">
-        <v>0.1202432279964843</v>
+        <v>0.1249649908959747</v>
       </c>
       <c r="W69">
-        <v>0.2328342175248922</v>
+        <v>0.2228342175248922</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4008107599882809</v>
+        <v>0.416549969653249</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2169789059140464</v>
+        <v>0.2100187978393624</v>
       </c>
       <c r="C70">
-        <v>-1928.511271753892</v>
+        <v>-1870.953582829155</v>
       </c>
       <c r="D70">
-        <v>1365.200728246108</v>
+        <v>1422.758417170845</v>
       </c>
       <c r="E70">
         <v>2268.912</v>
@@ -7033,37 +7033,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M70">
-        <v>994.9300713634515</v>
+        <v>957.3369513634515</v>
       </c>
       <c r="N70">
-        <v>-602.0157856491658</v>
+        <v>-564.4226656491658</v>
       </c>
       <c r="O70">
-        <v>-180.6047356947497</v>
+        <v>-169.3267996947497</v>
       </c>
       <c r="P70">
-        <v>-421.4110499544161</v>
+        <v>-395.095865954416</v>
       </c>
       <c r="Q70">
-        <v>-383.611049954416</v>
+        <v>-357.295865954416</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1822918915317091</v>
+        <v>0.1817915537983218</v>
       </c>
       <c r="T70">
-        <v>1.985675080777601</v>
+        <v>1.978842808434259</v>
       </c>
       <c r="U70">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V70">
-        <v>0.1184749452318301</v>
+        <v>0.1231272704416221</v>
       </c>
       <c r="W70">
-        <v>0.2333022067998521</v>
+        <v>0.2233022067998521</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3949164841061003</v>
+        <v>0.410424234805407</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.219167480796268</v>
+        <v>0.2121073727215841</v>
       </c>
       <c r="C71">
-        <v>-2001.029438215256</v>
+        <v>-1944.105326423104</v>
       </c>
       <c r="D71">
-        <v>1347.966561784744</v>
+        <v>1404.890673576896</v>
       </c>
       <c r="E71">
         <v>2324.196</v>
@@ -7115,37 +7115,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M71">
-        <v>1009.561395942326</v>
+        <v>971.4154359423258</v>
       </c>
       <c r="N71">
-        <v>-616.6471102280401</v>
+        <v>-578.50115022804</v>
       </c>
       <c r="O71">
-        <v>-184.994133068412</v>
+        <v>-173.550345068412</v>
       </c>
       <c r="P71">
-        <v>-431.6529771596281</v>
+        <v>-404.950805159628</v>
       </c>
       <c r="Q71">
-        <v>-393.8529771596281</v>
+        <v>-367.150805159628</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1866948557746675</v>
+        <v>0.1861783781143968</v>
       </c>
       <c r="T71">
-        <v>2.049729115641395</v>
+        <v>2.04267644741601</v>
       </c>
       <c r="U71">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V71">
-        <v>0.1167579170400644</v>
+        <v>0.121342817246816</v>
       </c>
       <c r="W71">
-        <v>0.2337566311682915</v>
+        <v>0.2237566311682915</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3891930568002148</v>
+        <v>0.4044760574893866</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2213560556784897</v>
+        <v>0.2141959476038058</v>
       </c>
       <c r="C72">
-        <v>-2073.117904160877</v>
+        <v>-2016.813851269769</v>
       </c>
       <c r="D72">
-        <v>1331.162095839123</v>
+        <v>1387.466148730231</v>
       </c>
       <c r="E72">
         <v>2379.48</v>
@@ -7197,37 +7197,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M72">
-        <v>1024.1927205212</v>
+        <v>985.4939205212</v>
       </c>
       <c r="N72">
-        <v>-631.2784348069143</v>
+        <v>-592.5796348069143</v>
       </c>
       <c r="O72">
-        <v>-189.3835304420743</v>
+        <v>-177.7738904420743</v>
       </c>
       <c r="P72">
-        <v>-441.89490436484</v>
+        <v>-414.8057443648401</v>
       </c>
       <c r="Q72">
-        <v>-404.09490436484</v>
+        <v>-377.00574436484</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1913913509671564</v>
+        <v>0.1908576573848766</v>
       </c>
       <c r="T72">
-        <v>2.118053419496108</v>
+        <v>2.110765662329877</v>
       </c>
       <c r="U72">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V72">
-        <v>0.1150899467966349</v>
+        <v>0.1196093484290043</v>
       </c>
       <c r="W72">
-        <v>0.2341980719833469</v>
+        <v>0.2241980719833469</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3836331559887831</v>
+        <v>0.3986978280966811</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2235446305607114</v>
+        <v>0.2162845224860275</v>
       </c>
       <c r="C73">
-        <v>-2144.792542336154</v>
+        <v>-2089.09544674597</v>
       </c>
       <c r="D73">
-        <v>1314.771457663846</v>
+        <v>1370.46855325403</v>
       </c>
       <c r="E73">
         <v>2434.764</v>
@@ -7279,37 +7279,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M73">
-        <v>1038.824045100074</v>
+        <v>999.5724051000742</v>
       </c>
       <c r="N73">
-        <v>-645.9097593857886</v>
+        <v>-606.6581193857885</v>
       </c>
       <c r="O73">
-        <v>-193.7729278157366</v>
+        <v>-181.9974358157365</v>
       </c>
       <c r="P73">
-        <v>-452.136831570052</v>
+        <v>-424.660683570052</v>
       </c>
       <c r="Q73">
-        <v>-414.336831570052</v>
+        <v>-386.8606835700519</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1964117423798169</v>
+        <v>0.195859645570562</v>
       </c>
       <c r="T73">
-        <v>2.191089744306318</v>
+        <v>2.183550685168837</v>
       </c>
       <c r="U73">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V73">
-        <v>0.1134689616304851</v>
+        <v>0.1179247097187367</v>
       </c>
       <c r="W73">
-        <v>0.2346270778458655</v>
+        <v>0.2246270778458654</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3782298721016172</v>
+        <v>0.3930823657291223</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.225733205442933</v>
+        <v>0.2183730973682491</v>
       </c>
       <c r="C74">
-        <v>-2216.068453228986</v>
+        <v>-2160.965613656407</v>
       </c>
       <c r="D74">
-        <v>1298.779546771013</v>
+        <v>1353.882386343593</v>
       </c>
       <c r="E74">
         <v>2490.047999999999</v>
@@ -7361,37 +7361,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M74">
-        <v>1053.455369678949</v>
+        <v>1013.650889678948</v>
       </c>
       <c r="N74">
-        <v>-660.5410839646628</v>
+        <v>-620.7366039646628</v>
       </c>
       <c r="O74">
-        <v>-198.1623251893988</v>
+        <v>-186.2209811893988</v>
       </c>
       <c r="P74">
-        <v>-462.3787587752639</v>
+        <v>-434.515622775264</v>
       </c>
       <c r="Q74">
-        <v>-424.5787587752639</v>
+        <v>-396.715622775264</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2017907331790961</v>
+        <v>0.2012189186266535</v>
       </c>
       <c r="T74">
-        <v>2.269342949460115</v>
+        <v>2.261534638210581</v>
       </c>
       <c r="U74">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V74">
-        <v>0.1118930038300617</v>
+        <v>0.1162868665281987</v>
       </c>
       <c r="W74">
-        <v>0.2350441668788696</v>
+        <v>0.2250441668788696</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3729766794335392</v>
+        <v>0.3876228884273288</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2279217803251547</v>
+        <v>0.2204616722504708</v>
       </c>
       <c r="C75">
-        <v>-2286.960011471231</v>
+        <v>-2232.439111381727</v>
       </c>
       <c r="D75">
-        <v>1283.171988528768</v>
+        <v>1337.692888618272</v>
       </c>
       <c r="E75">
         <v>2545.331999999999</v>
@@ -7443,37 +7443,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M75">
-        <v>1068.086694257823</v>
+        <v>1027.729374257823</v>
       </c>
       <c r="N75">
-        <v>-675.172408543537</v>
+        <v>-634.8150885435372</v>
       </c>
       <c r="O75">
-        <v>-202.5517225630611</v>
+        <v>-190.4445265630611</v>
       </c>
       <c r="P75">
-        <v>-472.6206859804759</v>
+        <v>-444.3705619804761</v>
       </c>
       <c r="Q75">
-        <v>-434.8206859804759</v>
+        <v>-406.570561980476</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2075681677412848</v>
+        <v>0.2069751748720851</v>
       </c>
       <c r="T75">
-        <v>2.353392688329008</v>
+        <v>2.345295180366529</v>
       </c>
       <c r="U75">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V75">
-        <v>0.1103602229556774</v>
+        <v>0.1146938957538398</v>
       </c>
       <c r="W75">
-        <v>0.2354498288150792</v>
+        <v>0.2254498288150792</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3678674098522579</v>
+        <v>0.3823129858461326</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2301103552073764</v>
+        <v>0.2225502471326925</v>
       </c>
       <c r="C76">
-        <v>-2357.480908934235</v>
+        <v>-2303.530001683823</v>
       </c>
       <c r="D76">
-        <v>1267.935091065764</v>
+        <v>1321.885998316177</v>
       </c>
       <c r="E76">
         <v>2600.616</v>
@@ -7525,37 +7525,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M76">
-        <v>1082.718018836697</v>
+        <v>1041.807858836697</v>
       </c>
       <c r="N76">
-        <v>-689.8037331224115</v>
+        <v>-648.8935731224113</v>
       </c>
       <c r="O76">
-        <v>-206.9411199367234</v>
+        <v>-194.6680719367234</v>
       </c>
       <c r="P76">
-        <v>-482.862613185688</v>
+        <v>-454.2255011856879</v>
       </c>
       <c r="Q76">
-        <v>-445.062613185688</v>
+        <v>-416.4255011856879</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2137900203467189</v>
+        <v>0.213174220059473</v>
       </c>
       <c r="T76">
-        <v>2.443907791726278</v>
+        <v>2.435498841149857</v>
       </c>
       <c r="U76">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V76">
-        <v>0.1088688685914114</v>
+        <v>0.1131439782436527</v>
       </c>
       <c r="W76">
-        <v>0.235844526915175</v>
+        <v>0.225844526915175</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3628962286380381</v>
+        <v>0.3771465941455092</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2322989300895981</v>
+        <v>0.2246388220149141</v>
       </c>
       <c r="C77">
-        <v>-2427.64419478998</v>
+        <v>-2374.251689441648</v>
       </c>
       <c r="D77">
-        <v>1253.055805210019</v>
+        <v>1306.448310558352</v>
       </c>
       <c r="E77">
         <v>2655.899999999999</v>
@@ -7607,37 +7607,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M77">
-        <v>1097.349343415571</v>
+        <v>1055.886343415571</v>
       </c>
       <c r="N77">
-        <v>-704.4350577012857</v>
+        <v>-662.9720577012855</v>
       </c>
       <c r="O77">
-        <v>-211.3305173103857</v>
+        <v>-198.8916173103856</v>
       </c>
       <c r="P77">
-        <v>-493.1045403909</v>
+        <v>-464.0804403908999</v>
       </c>
       <c r="Q77">
-        <v>-455.3045403908999</v>
+        <v>-426.2804403908999</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2205096211605876</v>
+        <v>0.2198691888618519</v>
       </c>
       <c r="T77">
-        <v>2.541664103395329</v>
+        <v>2.532918794795851</v>
       </c>
       <c r="U77">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V77">
-        <v>0.1074172836768593</v>
+        <v>0.1116353918670707</v>
       </c>
       <c r="W77">
-        <v>0.2362286997326015</v>
+        <v>0.2262286997326015</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3580576122561976</v>
+        <v>0.3721179728902357</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2344875049718197</v>
+        <v>0.2267273968971358</v>
       </c>
       <c r="C78">
-        <v>-2497.46231278425</v>
+        <v>-2444.616960565581</v>
       </c>
       <c r="D78">
-        <v>1238.52168721575</v>
+        <v>1291.367039434419</v>
       </c>
       <c r="E78">
         <v>2711.184</v>
@@ -7689,37 +7689,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M78">
-        <v>1111.980667994446</v>
+        <v>1069.964827994446</v>
       </c>
       <c r="N78">
-        <v>-719.0663822801599</v>
+        <v>-677.0505422801599</v>
       </c>
       <c r="O78">
-        <v>-215.719914684048</v>
+        <v>-203.115162684048</v>
       </c>
       <c r="P78">
-        <v>-503.3464675961119</v>
+        <v>-473.9353795961119</v>
       </c>
       <c r="Q78">
-        <v>-465.5464675961119</v>
+        <v>-436.1353795961119</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2277891887089455</v>
+        <v>0.2271220717310958</v>
       </c>
       <c r="T78">
-        <v>2.647566774370135</v>
+        <v>2.638457077912345</v>
       </c>
       <c r="U78">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V78">
-        <v>0.1060038983653217</v>
+        <v>0.1101665051319777</v>
       </c>
       <c r="W78">
-        <v>0.2366027627390432</v>
+        <v>0.2266027627390432</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3533463278844056</v>
+        <v>0.3672216837732589</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2366760798540414</v>
+        <v>0.2288159717793575</v>
       </c>
       <c r="C79">
-        <v>-2566.947135945538</v>
+        <v>-2514.638017315706</v>
       </c>
       <c r="D79">
-        <v>1224.320864054461</v>
+        <v>1276.629982684294</v>
       </c>
       <c r="E79">
         <v>2766.467999999999</v>
@@ -7771,37 +7771,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M79">
-        <v>1126.61199257332</v>
+        <v>1084.04331257332</v>
       </c>
       <c r="N79">
-        <v>-733.6977068590342</v>
+        <v>-691.1290268590343</v>
       </c>
       <c r="O79">
-        <v>-220.1093120577102</v>
+        <v>-207.3387080577103</v>
       </c>
       <c r="P79">
-        <v>-513.5883948013239</v>
+        <v>-483.790318801324</v>
       </c>
       <c r="Q79">
-        <v>-475.7883948013239</v>
+        <v>-445.990318801324</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2357017621310736</v>
+        <v>0.2350056400672304</v>
       </c>
       <c r="T79">
-        <v>2.762678373255792</v>
+        <v>2.753172603038969</v>
       </c>
       <c r="U79">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V79">
-        <v>0.1046272243605772</v>
+        <v>0.1087357712990948</v>
       </c>
       <c r="W79">
-        <v>0.2369671098232396</v>
+        <v>0.2269671098232396</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3487574145352574</v>
+        <v>0.3624525709969828</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2388646547362631</v>
+        <v>0.2309045466615791</v>
       </c>
       <c r="C80">
-        <v>-2636.109998933226</v>
+        <v>-2584.326511229086</v>
       </c>
       <c r="D80">
-        <v>1210.442001066774</v>
+        <v>1262.225488770915</v>
       </c>
       <c r="E80">
         <v>2821.752</v>
@@ -7853,37 +7853,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M80">
-        <v>1141.243317152194</v>
+        <v>1098.121797152194</v>
       </c>
       <c r="N80">
-        <v>-748.3290314379086</v>
+        <v>-705.2075114379087</v>
       </c>
       <c r="O80">
-        <v>-224.4987094313726</v>
+        <v>-211.5622534313726</v>
       </c>
       <c r="P80">
-        <v>-523.830322006536</v>
+        <v>-493.6452580065361</v>
       </c>
       <c r="Q80">
-        <v>-486.030322006536</v>
+        <v>-455.8452580065361</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2443336604097587</v>
+        <v>0.2436058964339227</v>
       </c>
       <c r="T80">
-        <v>2.888254662949238</v>
+        <v>2.878316812268013</v>
       </c>
       <c r="U80">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V80">
-        <v>0.1032858496892878</v>
+        <v>0.1073417229491064</v>
       </c>
       <c r="W80">
-        <v>0.2373221146745079</v>
+        <v>0.2273221146745079</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3442861656309593</v>
+        <v>0.3578057431636882</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2410532296184847</v>
+        <v>0.2329931215438008</v>
       </c>
       <c r="C81">
-        <v>-2704.961728210211</v>
+        <v>-2653.693573842741</v>
       </c>
       <c r="D81">
-        <v>1196.874271789789</v>
+        <v>1248.142426157259</v>
       </c>
       <c r="E81">
         <v>2877.036</v>
@@ -7935,37 +7935,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M81">
-        <v>1155.874641731069</v>
+        <v>1112.200281731069</v>
       </c>
       <c r="N81">
-        <v>-762.9603560167828</v>
+        <v>-719.2859960167829</v>
       </c>
       <c r="O81">
-        <v>-228.8881068050349</v>
+        <v>-215.7857988050349</v>
       </c>
       <c r="P81">
-        <v>-534.0722492117479</v>
+        <v>-503.500197211748</v>
       </c>
       <c r="Q81">
-        <v>-496.2722492117479</v>
+        <v>-465.700197211748</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2537876442387949</v>
+        <v>0.253025224835538</v>
       </c>
       <c r="T81">
-        <v>3.025790599280154</v>
+        <v>3.015379517614109</v>
       </c>
       <c r="U81">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V81">
-        <v>0.101978433870436</v>
+        <v>0.1059829669624089</v>
       </c>
       <c r="W81">
-        <v>0.2376681320611871</v>
+        <v>0.2276681320611871</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3399281129014534</v>
+        <v>0.353276556541363</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2432418045007064</v>
+        <v>0.2350816964260225</v>
       </c>
       <c r="C82">
-        <v>-2773.512670208846</v>
+        <v>-2722.749845382615</v>
       </c>
       <c r="D82">
-        <v>1183.607329791155</v>
+        <v>1234.370154617385</v>
       </c>
       <c r="E82">
         <v>2932.32</v>
@@ -8017,37 +8017,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M82">
-        <v>1170.505966309943</v>
+        <v>1126.278766309943</v>
       </c>
       <c r="N82">
-        <v>-777.5916805956573</v>
+        <v>-733.3644805956573</v>
       </c>
       <c r="O82">
-        <v>-233.2775041786972</v>
+        <v>-220.0093441786972</v>
       </c>
       <c r="P82">
-        <v>-544.3141764169601</v>
+        <v>-513.35513641696</v>
       </c>
       <c r="Q82">
-        <v>-506.5141764169601</v>
+        <v>-475.55513641696</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2641870264507346</v>
+        <v>0.263386486077315</v>
       </c>
       <c r="T82">
-        <v>3.177080129244161</v>
+        <v>3.166148493494815</v>
       </c>
       <c r="U82">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V82">
-        <v>0.1007037034470556</v>
+        <v>0.1046581798753788</v>
       </c>
       <c r="W82">
-        <v>0.2380054990131994</v>
+        <v>0.2280054990131994</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3356790114901852</v>
+        <v>0.3488605995845959</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2454303793829281</v>
+        <v>0.2371702713082442</v>
       </c>
       <c r="C83">
-        <v>-2841.772717644118</v>
+        <v>-2791.505501573903</v>
       </c>
       <c r="D83">
-        <v>1170.631282355882</v>
+        <v>1220.898498426097</v>
       </c>
       <c r="E83">
         <v>2987.604</v>
@@ -8099,37 +8099,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M83">
-        <v>1185.137290888817</v>
+        <v>1140.357250888817</v>
       </c>
       <c r="N83">
-        <v>-792.2230051745315</v>
+        <v>-747.4429651745314</v>
       </c>
       <c r="O83">
-        <v>-237.6669015523594</v>
+        <v>-224.2328895523594</v>
       </c>
       <c r="P83">
-        <v>-554.556103622172</v>
+        <v>-523.210075622172</v>
       </c>
       <c r="Q83">
-        <v>-516.7561036221721</v>
+        <v>-485.410075622172</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2756810804744575</v>
+        <v>0.2748384063971736</v>
       </c>
       <c r="T83">
-        <v>3.344294872888591</v>
+        <v>3.332787887889279</v>
       </c>
       <c r="U83">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V83">
-        <v>0.09946044784894377</v>
+        <v>0.103366103580621</v>
       </c>
       <c r="W83">
-        <v>0.2383345359170138</v>
+        <v>0.2283345359170138</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3315348261631459</v>
+        <v>0.3445536786020701</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2476189542651498</v>
+        <v>0.2392588461904658</v>
       </c>
       <c r="C84">
-        <v>-2909.751334114785</v>
+        <v>-2859.970278714713</v>
       </c>
       <c r="D84">
-        <v>1157.936665885215</v>
+        <v>1207.717721285287</v>
       </c>
       <c r="E84">
         <v>3042.888</v>
@@ -8181,37 +8181,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M84">
-        <v>1199.768615467692</v>
+        <v>1154.435735467692</v>
       </c>
       <c r="N84">
-        <v>-806.854329753406</v>
+        <v>-761.5214497534058</v>
       </c>
       <c r="O84">
-        <v>-242.0562989260218</v>
+        <v>-228.4564349260217</v>
       </c>
       <c r="P84">
-        <v>-564.7980308273842</v>
+        <v>-533.0650148273841</v>
       </c>
       <c r="Q84">
-        <v>-526.9980308273841</v>
+        <v>-495.2650148273841</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2884522516119273</v>
+        <v>0.2875627623081278</v>
       </c>
       <c r="T84">
-        <v>3.530089032493513</v>
+        <v>3.517942770549795</v>
       </c>
       <c r="U84">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V84">
-        <v>0.09824751555810297</v>
+        <v>0.102105541341833</v>
       </c>
       <c r="W84">
-        <v>0.2386555475304913</v>
+        <v>0.2286555475304913</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.32749171852701</v>
+        <v>0.3403518044727766</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2498075291473715</v>
+        <v>0.2413474210726875</v>
       </c>
       <c r="C85">
-        <v>-2977.457577120969</v>
+        <v>-2928.153497142926</v>
       </c>
       <c r="D85">
-        <v>1145.514422879031</v>
+        <v>1194.818502857074</v>
       </c>
       <c r="E85">
         <v>3098.172</v>
@@ -8263,37 +8263,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M85">
-        <v>1214.399940046566</v>
+        <v>1168.514220046566</v>
       </c>
       <c r="N85">
-        <v>-821.4856543322802</v>
+        <v>-775.59993433228</v>
       </c>
       <c r="O85">
-        <v>-246.445696299684</v>
+        <v>-232.679980299684</v>
       </c>
       <c r="P85">
-        <v>-575.0399580325961</v>
+        <v>-542.919954032596</v>
       </c>
       <c r="Q85">
-        <v>-537.2399580325962</v>
+        <v>-505.119954032596</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3027259134714526</v>
+        <v>0.3017841012674294</v>
       </c>
       <c r="T85">
-        <v>3.737741328522544</v>
+        <v>3.724880580582136</v>
       </c>
       <c r="U85">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V85">
-        <v>0.09706381055137885</v>
+        <v>0.1008753540967506</v>
       </c>
       <c r="W85">
-        <v>0.2389688239243669</v>
+        <v>0.2289688239243669</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3235460351712629</v>
+        <v>0.3362511803225021</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.251996104029593</v>
+        <v>0.2434359959549092</v>
       </c>
       <c r="C86">
-        <v>-3044.900119615912</v>
+        <v>-2996.064083215082</v>
       </c>
       <c r="D86">
-        <v>1133.355880384087</v>
+        <v>1182.191916784918</v>
       </c>
       <c r="E86">
         <v>3153.456</v>
@@ -8345,37 +8345,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M86">
-        <v>1229.03126462544</v>
+        <v>1182.59270462544</v>
       </c>
       <c r="N86">
-        <v>-836.1169789111542</v>
+        <v>-789.6784189111544</v>
       </c>
       <c r="O86">
-        <v>-250.8350936733463</v>
+        <v>-236.9035256733463</v>
       </c>
       <c r="P86">
-        <v>-585.281885237808</v>
+        <v>-552.7748932378081</v>
       </c>
       <c r="Q86">
-        <v>-547.481885237808</v>
+        <v>-514.9748932378081</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3187837830634181</v>
+        <v>0.3177831075966436</v>
       </c>
       <c r="T86">
-        <v>3.9713501615552</v>
+        <v>3.957685616868518</v>
       </c>
       <c r="U86">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V86">
-        <v>0.09590828899719579</v>
+        <v>0.09967445702417026</v>
       </c>
       <c r="W86">
-        <v>0.2392746413564835</v>
+        <v>0.2292746413564836</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3196942966573193</v>
+        <v>0.3322481900805676</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2541846789118148</v>
+        <v>0.2455245708371309</v>
       </c>
       <c r="C87">
-        <v>-3112.087270199629</v>
+        <v>-3063.710589906239</v>
       </c>
       <c r="D87">
-        <v>1121.45272980037</v>
+        <v>1169.829410093761</v>
       </c>
       <c r="E87">
         <v>3208.739999999999</v>
@@ -8427,37 +8427,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M87">
-        <v>1243.662589204314</v>
+        <v>1196.671189204314</v>
       </c>
       <c r="N87">
-        <v>-850.7483034900284</v>
+        <v>-803.7569034900285</v>
       </c>
       <c r="O87">
-        <v>-255.2244910470085</v>
+        <v>-241.1270710470085</v>
       </c>
       <c r="P87">
-        <v>-595.5238124430199</v>
+        <v>-562.62983244302</v>
       </c>
       <c r="Q87">
-        <v>-557.7238124430198</v>
+        <v>-524.82983244302</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3369827019343127</v>
+        <v>0.3359153147697532</v>
       </c>
       <c r="T87">
-        <v>4.236106838992215</v>
+        <v>4.221531324659752</v>
       </c>
       <c r="U87">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V87">
-        <v>0.09477995618546409</v>
+        <v>0.09850181635329769</v>
       </c>
       <c r="W87">
-        <v>0.2395732630843151</v>
+        <v>0.2295732630843151</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3159331872848803</v>
+        <v>0.3283393878443256</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2563732537940365</v>
+        <v>0.2476131457193525</v>
       </c>
       <c r="C88">
-        <v>-3179.026992053274</v>
+        <v>-3131.101216130697</v>
       </c>
       <c r="D88">
-        <v>1109.797007946726</v>
+        <v>1157.722783869303</v>
       </c>
       <c r="E88">
         <v>3264.024</v>
@@ -8509,37 +8509,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M88">
-        <v>1258.293913783189</v>
+        <v>1210.749673783189</v>
       </c>
       <c r="N88">
-        <v>-865.3796280689029</v>
+        <v>-817.8353880689029</v>
       </c>
       <c r="O88">
-        <v>-259.6138884206708</v>
+        <v>-245.3506164206709</v>
       </c>
       <c r="P88">
-        <v>-605.7657396482321</v>
+        <v>-572.484771648232</v>
       </c>
       <c r="Q88">
-        <v>-567.9657396482321</v>
+        <v>-534.6847716482321</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3577814663581922</v>
+        <v>0.3566378372533071</v>
       </c>
       <c r="T88">
-        <v>4.53868589892023</v>
+        <v>4.523069276421164</v>
       </c>
       <c r="U88">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V88">
-        <v>0.09367786367167961</v>
+        <v>0.09735644639570119</v>
       </c>
       <c r="W88">
-        <v>0.2398649401208018</v>
+        <v>0.2298649401208018</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3122595455722653</v>
+        <v>0.3245214879856706</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2585618286762582</v>
+        <v>0.2497017206015742</v>
       </c>
       <c r="C89">
-        <v>-3245.726920704896</v>
+        <v>-3198.243824875297</v>
       </c>
       <c r="D89">
-        <v>1098.381079295103</v>
+        <v>1145.864175124702</v>
       </c>
       <c r="E89">
         <v>3319.308</v>
@@ -8591,37 +8591,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M89">
-        <v>1272.925238362063</v>
+        <v>1224.828158362063</v>
       </c>
       <c r="N89">
-        <v>-880.0109526477771</v>
+        <v>-831.9138726477771</v>
       </c>
       <c r="O89">
-        <v>-264.0032857943331</v>
+        <v>-249.5741617943331</v>
       </c>
       <c r="P89">
-        <v>-616.007666853444</v>
+        <v>-582.339710853444</v>
       </c>
       <c r="Q89">
-        <v>-578.2076668534439</v>
+        <v>-544.5397108534439</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3817800406934378</v>
+        <v>0.380548440118946</v>
       </c>
       <c r="T89">
-        <v>4.887815583452555</v>
+        <v>4.870997682299714</v>
       </c>
       <c r="U89">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V89">
-        <v>0.09260110661798214</v>
+        <v>0.09623740678195751</v>
       </c>
       <c r="W89">
-        <v>0.2401499119380589</v>
+        <v>0.2301499119380589</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3086703553932738</v>
+        <v>0.3207913559398584</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2607504035584798</v>
+        <v>0.2517902954837959</v>
       </c>
       <c r="C90">
-        <v>-3312.194380709886</v>
+        <v>-3265.145960229598</v>
       </c>
       <c r="D90">
-        <v>1087.197619290113</v>
+        <v>1134.246039770402</v>
       </c>
       <c r="E90">
         <v>3374.591999999999</v>
@@ -8673,37 +8673,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M90">
-        <v>1287.556562940937</v>
+        <v>1238.906642940937</v>
       </c>
       <c r="N90">
-        <v>-894.6422772266513</v>
+        <v>-845.9923572266513</v>
       </c>
       <c r="O90">
-        <v>-268.3926831679954</v>
+        <v>-253.7977071679954</v>
       </c>
       <c r="P90">
-        <v>-626.2495940586559</v>
+        <v>-592.194650058656</v>
       </c>
       <c r="Q90">
-        <v>-588.449594058656</v>
+        <v>-554.394650058656</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4097783774178909</v>
+        <v>0.4084441434621915</v>
       </c>
       <c r="T90">
-        <v>5.295133548740268</v>
+        <v>5.276914155824691</v>
       </c>
       <c r="U90">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V90">
-        <v>0.09154882131550508</v>
+        <v>0.095143799886708</v>
       </c>
       <c r="W90">
-        <v>0.2404284071231055</v>
+        <v>0.2304284071231056</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3051627377183502</v>
+        <v>0.31714599962236</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2629389784407015</v>
+        <v>0.2538788703660175</v>
       </c>
       <c r="C91">
-        <v>-3378.436401322659</v>
+        <v>-3331.814863390389</v>
       </c>
       <c r="D91">
-        <v>1076.239598677341</v>
+        <v>1122.861136609611</v>
       </c>
       <c r="E91">
         <v>3429.876</v>
@@ -8755,37 +8755,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M91">
-        <v>1302.187887519812</v>
+        <v>1252.985127519811</v>
       </c>
       <c r="N91">
-        <v>-909.2736018055258</v>
+        <v>-860.0708418055257</v>
       </c>
       <c r="O91">
-        <v>-272.7820805416577</v>
+        <v>-258.0212525416577</v>
       </c>
       <c r="P91">
-        <v>-636.4915212638681</v>
+        <v>-602.049589263868</v>
       </c>
       <c r="Q91">
-        <v>-598.691521263868</v>
+        <v>-564.2495892638681</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4428673208195174</v>
+        <v>0.4414117928678453</v>
       </c>
       <c r="T91">
-        <v>5.776509325898475</v>
+        <v>5.756633624536026</v>
       </c>
       <c r="U91">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V91">
-        <v>0.09052018287375781</v>
+        <v>0.09407476842730678</v>
       </c>
       <c r="W91">
-        <v>0.2407006439893871</v>
+        <v>0.2307006439893871</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3017339429125261</v>
+        <v>0.3135825614243559</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2651275533229231</v>
+        <v>0.2559674452482392</v>
       </c>
       <c r="C92">
-        <v>-3444.459731230058</v>
+        <v>-3398.257487711942</v>
       </c>
       <c r="D92">
-        <v>1065.500268769941</v>
+        <v>1111.702512288058</v>
       </c>
       <c r="E92">
         <v>3485.159999999999</v>
@@ -8837,37 +8837,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M92">
-        <v>1316.819212098686</v>
+        <v>1267.063612098686</v>
       </c>
       <c r="N92">
-        <v>-923.9049263844</v>
+        <v>-874.1493263843998</v>
       </c>
       <c r="O92">
-        <v>-277.17147791532</v>
+        <v>-262.24479791532</v>
       </c>
       <c r="P92">
-        <v>-646.73344846908</v>
+        <v>-611.9045284690799</v>
       </c>
       <c r="Q92">
-        <v>-608.9334484690801</v>
+        <v>-574.1045284690799</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4825740529014693</v>
+        <v>0.48097297215463</v>
       </c>
       <c r="T92">
-        <v>6.354160258488324</v>
+        <v>6.33229698698963</v>
       </c>
       <c r="U92">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V92">
-        <v>0.0895144030640494</v>
+        <v>0.09302949322255893</v>
       </c>
       <c r="W92">
-        <v>0.2409668311475291</v>
+        <v>0.2309668311475291</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2983813435468313</v>
+        <v>0.3100983107418631</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2673161282051448</v>
+        <v>0.2580560201304609</v>
       </c>
       <c r="C93">
-        <v>-3510.270852411369</v>
+        <v>-3464.480512867698</v>
       </c>
       <c r="D93">
-        <v>1054.973147588631</v>
+        <v>1100.763487132302</v>
       </c>
       <c r="E93">
         <v>3540.444</v>
@@ -8919,37 +8919,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M93">
-        <v>1331.45053667756</v>
+        <v>1281.14209667756</v>
       </c>
       <c r="N93">
-        <v>-938.5362509632745</v>
+        <v>-888.2278109632745</v>
       </c>
       <c r="O93">
-        <v>-281.5608752889823</v>
+        <v>-266.4683432889823</v>
       </c>
       <c r="P93">
-        <v>-656.9753756742921</v>
+        <v>-621.7594676742922</v>
       </c>
       <c r="Q93">
-        <v>-619.1753756742921</v>
+        <v>-583.9594676742922</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5311045032238546</v>
+        <v>0.5293255246162555</v>
       </c>
       <c r="T93">
-        <v>7.060178064987026</v>
+        <v>7.03588554109959</v>
       </c>
       <c r="U93">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V93">
-        <v>0.08853072830510378</v>
+        <v>0.0920071910992341</v>
       </c>
       <c r="W93">
-        <v>0.2412271680384592</v>
+        <v>0.2312271680384592</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2951024276836793</v>
+        <v>0.3066906369974469</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2695047030873665</v>
+        <v>0.2601445950126826</v>
       </c>
       <c r="C94">
-        <v>-3575.875993184744</v>
+        <v>-3530.490358183999</v>
       </c>
       <c r="D94">
-        <v>1044.652006815255</v>
+        <v>1090.037641816001</v>
       </c>
       <c r="E94">
         <v>3595.728</v>
@@ -9001,37 +9001,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M94">
-        <v>1346.081861256434</v>
+        <v>1295.220581256434</v>
       </c>
       <c r="N94">
-        <v>-953.1675755421485</v>
+        <v>-902.3062955421486</v>
       </c>
       <c r="O94">
-        <v>-285.9502726626445</v>
+        <v>-270.6918886626446</v>
       </c>
       <c r="P94">
-        <v>-667.2173028795039</v>
+        <v>-631.614406879504</v>
       </c>
       <c r="Q94">
-        <v>-629.4173028795039</v>
+        <v>-593.8144068795041</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5917675661268367</v>
+        <v>0.5897662151932876</v>
       </c>
       <c r="T94">
-        <v>7.942700323110407</v>
+        <v>7.915371233737041</v>
       </c>
       <c r="U94">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V94">
-        <v>0.08756843778004833</v>
+        <v>0.09100711293511199</v>
       </c>
       <c r="W94">
-        <v>0.2414818454317604</v>
+        <v>0.2314818454317604</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2918947926001612</v>
+        <v>0.3033570431170399</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2716932779695881</v>
+        <v>0.2622331698949042</v>
       </c>
       <c r="C95">
-        <v>-3641.281140495228</v>
+        <v>-3596.293195201812</v>
       </c>
       <c r="D95">
-        <v>1034.530859504772</v>
+        <v>1079.518804798188</v>
       </c>
       <c r="E95">
         <v>3651.012</v>
@@ -9083,37 +9083,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M95">
-        <v>1360.713185835309</v>
+        <v>1309.299065835309</v>
       </c>
       <c r="N95">
-        <v>-967.7989001210229</v>
+        <v>-916.384780121023</v>
       </c>
       <c r="O95">
-        <v>-290.3396700363069</v>
+        <v>-274.9154340363069</v>
       </c>
       <c r="P95">
-        <v>-677.4592300847161</v>
+        <v>-641.4693460847161</v>
       </c>
       <c r="Q95">
-        <v>-639.659230084716</v>
+        <v>-603.6693460847162</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6697629327163849</v>
+        <v>0.6674756745066145</v>
       </c>
       <c r="T95">
-        <v>9.077371797840467</v>
+        <v>9.046138552842333</v>
       </c>
       <c r="U95">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V95">
-        <v>0.0866268416748865</v>
+        <v>0.09002854182828282</v>
       </c>
       <c r="W95">
-        <v>0.2417310458918723</v>
+        <v>0.2317310458918723</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2887561389162884</v>
+        <v>0.3000951394276093</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2738818528518099</v>
+        <v>0.2643217447771259</v>
       </c>
       <c r="C96">
-        <v>-3706.492051495318</v>
+        <v>-3661.894959518067</v>
       </c>
       <c r="D96">
-        <v>1024.603948504682</v>
+        <v>1069.201040481933</v>
       </c>
       <c r="E96">
         <v>3706.296</v>
@@ -9165,37 +9165,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M96">
-        <v>1375.344510414183</v>
+        <v>1323.377550414183</v>
       </c>
       <c r="N96">
-        <v>-982.4302246998972</v>
+        <v>-930.4632646998972</v>
       </c>
       <c r="O96">
-        <v>-294.7290674099692</v>
+        <v>-279.1389794099691</v>
       </c>
       <c r="P96">
-        <v>-687.701157289928</v>
+        <v>-651.3242852899281</v>
       </c>
       <c r="Q96">
-        <v>-649.9011572899281</v>
+        <v>-613.524285289928</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7737567548357825</v>
+        <v>0.7710882869243837</v>
       </c>
       <c r="T96">
-        <v>10.59026709748055</v>
+        <v>10.55382831164939</v>
       </c>
       <c r="U96">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V96">
-        <v>0.085705279529409</v>
+        <v>0.08907079138330108</v>
       </c>
       <c r="W96">
-        <v>0.241974944214535</v>
+        <v>0.231974944214535</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.28568426509803</v>
+        <v>0.296902637944337</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2760704277340315</v>
+        <v>0.2664103196593476</v>
       </c>
       <c r="C97">
-        <v>-3771.514264465125</v>
+        <v>-3727.301361954382</v>
       </c>
       <c r="D97">
-        <v>1014.865735534876</v>
+        <v>1059.078638045618</v>
       </c>
       <c r="E97">
         <v>3761.58</v>
@@ -9247,37 +9247,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M97">
-        <v>1389.975834993057</v>
+        <v>1337.456034993057</v>
       </c>
       <c r="N97">
-        <v>-997.0615492787716</v>
+        <v>-944.5417492787716</v>
       </c>
       <c r="O97">
-        <v>-299.1184647836315</v>
+        <v>-283.3625247836314</v>
       </c>
       <c r="P97">
-        <v>-697.9430844951402</v>
+        <v>-661.1792244951401</v>
       </c>
       <c r="Q97">
-        <v>-660.1430844951401</v>
+        <v>-623.3792244951401</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.9193481058029395</v>
+        <v>0.9161459443092608</v>
       </c>
       <c r="T97">
-        <v>12.70832051697666</v>
+        <v>12.66459397397927</v>
       </c>
       <c r="U97">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V97">
-        <v>0.0848031186922573</v>
+        <v>0.08813320410558212</v>
       </c>
       <c r="W97">
-        <v>0.242213707835668</v>
+        <v>0.232213707835668</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2826770623075244</v>
+        <v>0.2937773470186071</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2782590026162532</v>
+        <v>0.2684988945415693</v>
       </c>
       <c r="C98">
-        <v>-3836.353109115669</v>
+        <v>-3792.517899097294</v>
       </c>
       <c r="D98">
-        <v>1005.31089088433</v>
+        <v>1049.146100902706</v>
       </c>
       <c r="E98">
         <v>3816.863999999999</v>
@@ -9329,37 +9329,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M98">
-        <v>1404.607159571931</v>
+        <v>1351.534519571931</v>
       </c>
       <c r="N98">
-        <v>-1011.692873857646</v>
+        <v>-958.6202338576455</v>
       </c>
       <c r="O98">
-        <v>-303.5078621572937</v>
+        <v>-287.5860701572936</v>
       </c>
       <c r="P98">
-        <v>-708.1850117003519</v>
+        <v>-671.0341637003519</v>
       </c>
       <c r="Q98">
-        <v>-670.3850117003519</v>
+        <v>-633.2341637003519</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.137735132253672</v>
+        <v>1.133732430386574</v>
       </c>
       <c r="T98">
-        <v>15.88540064622079</v>
+        <v>15.83074246747406</v>
       </c>
       <c r="U98">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V98">
-        <v>0.08391975287254631</v>
+        <v>0.08721514989614899</v>
       </c>
       <c r="W98">
-        <v>0.242447497214694</v>
+        <v>0.232447497214694</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2797325095751544</v>
+        <v>0.2907171663204967</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2804475774984748</v>
+        <v>0.2705874694237909</v>
       </c>
       <c r="C99">
-        <v>-3901.013716315578</v>
+        <v>-3857.549863250914</v>
       </c>
       <c r="D99">
-        <v>995.9342836844216</v>
+        <v>1039.398136749085</v>
       </c>
       <c r="E99">
         <v>3872.148</v>
@@ -9411,37 +9411,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M99">
-        <v>1419.238484150806</v>
+        <v>1365.613004150806</v>
       </c>
       <c r="N99">
-        <v>-1026.32419843652</v>
+        <v>-972.6987184365199</v>
       </c>
       <c r="O99">
-        <v>-307.897259530956</v>
+        <v>-291.809615530956</v>
       </c>
       <c r="P99">
-        <v>-718.4269389055639</v>
+        <v>-680.889102905564</v>
       </c>
       <c r="Q99">
-        <v>-680.626938905564</v>
+        <v>-643.089102905564</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.501713509671563</v>
+        <v>1.496376573848765</v>
       </c>
       <c r="T99">
-        <v>21.18053419496106</v>
+        <v>21.10765662329875</v>
       </c>
       <c r="U99">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V99">
-        <v>0.08305460078107675</v>
+        <v>0.08631602463948766</v>
       </c>
       <c r="W99">
-        <v>0.2426764661941525</v>
+        <v>0.2326764661941525</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.276848669270256</v>
+        <v>0.2877200821316256</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2826361523806965</v>
+        <v>0.2726760443060126</v>
       </c>
       <c r="C100">
-        <v>-3965.501027278473</v>
+        <v>-3922.402351839837</v>
       </c>
       <c r="D100">
-        <v>986.7309727215267</v>
+        <v>1029.829648160163</v>
       </c>
       <c r="E100">
         <v>3927.431999999999</v>
@@ -9493,37 +9493,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M100">
-        <v>1433.86980872968</v>
+        <v>1379.69148872968</v>
       </c>
       <c r="N100">
-        <v>-1040.955523015394</v>
+        <v>-986.7772030153941</v>
       </c>
       <c r="O100">
-        <v>-312.2866569046183</v>
+        <v>-296.0331609046182</v>
       </c>
       <c r="P100">
-        <v>-728.668866110776</v>
+        <v>-690.7440421107758</v>
       </c>
       <c r="Q100">
-        <v>-690.868866110776</v>
+        <v>-652.9440421107759</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.229670264507344</v>
+        <v>2.221664860773148</v>
       </c>
       <c r="T100">
-        <v>31.77080129244159</v>
+        <v>31.66148493494812</v>
       </c>
       <c r="U100">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V100">
-        <v>0.08220710485473924</v>
+        <v>0.08543524887786025</v>
       </c>
       <c r="W100">
-        <v>0.2429007623372955</v>
+        <v>0.2329007623372955</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2740236828491309</v>
+        <v>0.2847841629262008</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2848247272629181</v>
+        <v>0.2747646191882342</v>
       </c>
       <c r="C101">
-        <v>-4029.819802245638</v>
+        <v>-3987.080276297425</v>
       </c>
       <c r="D101">
-        <v>977.6961977543616</v>
+        <v>1020.435723702575</v>
       </c>
       <c r="E101">
         <v>3982.716</v>
@@ -9575,37 +9575,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M101">
-        <v>1448.501133308554</v>
+        <v>1393.769973308554</v>
       </c>
       <c r="N101">
-        <v>-1055.586847594269</v>
+        <v>-1000.855687594269</v>
       </c>
       <c r="O101">
-        <v>-316.6760542782807</v>
+        <v>-300.2567062782806</v>
       </c>
       <c r="P101">
-        <v>-738.9107933159883</v>
+        <v>-700.5989813159881</v>
       </c>
       <c r="Q101">
-        <v>-701.1107933159883</v>
+        <v>-662.7989813159882</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.413540529014687</v>
+        <v>4.397529721546295</v>
       </c>
       <c r="T101">
-        <v>63.54160258488317</v>
+        <v>63.32296986989623</v>
       </c>
       <c r="U101">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V101">
-        <v>0.08137673005822672</v>
+        <v>0.08457226656596264</v>
       </c>
       <c r="W101">
-        <v>0.2431205272452235</v>
+        <v>0.2331205272452235</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2712557668607557</v>
+        <v>0.2819075552198755</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/mexico/mexico_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_beverage_alcoholic.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09329378793608531</v>
+        <v>0.09317740898983222</v>
       </c>
       <c r="C2">
-        <v>5385.05761829012</v>
+        <v>5341.857886002528</v>
       </c>
       <c r="D2">
-        <v>4919.45761829012</v>
+        <v>4931.541886002527</v>
       </c>
       <c r="E2">
-        <v>-1490.4</v>
+        <v>-1435.116</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>55.284</v>
       </c>
       <c r="G2">
         <v>465.6</v>
@@ -1457,28 +1457,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.823302578874287</v>
       </c>
       <c r="N2">
-        <v>392.9142857142857</v>
+        <v>389.0909831354114</v>
       </c>
       <c r="O2">
-        <v>117.8742857142857</v>
+        <v>116.7272949406234</v>
       </c>
       <c r="P2">
-        <v>275.04</v>
+        <v>272.363688194788</v>
       </c>
       <c r="Q2">
-        <v>312.84</v>
+        <v>310.163688194788</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09329378793608531</v>
+        <v>0.09362960259825964</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6959789964029562</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>102.7682945852466</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09317740898983222</v>
+        <v>0.09306103004357914</v>
       </c>
       <c r="C3">
-        <v>5341.857886002528</v>
+        <v>5298.717668048045</v>
       </c>
       <c r="D3">
-        <v>4931.541886002527</v>
+        <v>4943.685668048045</v>
       </c>
       <c r="E3">
-        <v>-1435.116</v>
+        <v>-1379.832</v>
       </c>
       <c r="F3">
-        <v>55.284</v>
+        <v>110.568</v>
       </c>
       <c r="G3">
         <v>465.6</v>
@@ -1539,28 +1539,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M3">
-        <v>3.823302578874287</v>
+        <v>7.646605157748574</v>
       </c>
       <c r="N3">
-        <v>389.0909831354114</v>
+        <v>385.2676805565371</v>
       </c>
       <c r="O3">
-        <v>116.7272949406234</v>
+        <v>115.5803041669611</v>
       </c>
       <c r="P3">
-        <v>272.363688194788</v>
+        <v>269.687376389576</v>
       </c>
       <c r="Q3">
-        <v>310.163688194788</v>
+        <v>307.487376389576</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09362960259825964</v>
+        <v>0.09397227062088653</v>
       </c>
       <c r="T3">
-        <v>0.6959789964029562</v>
+        <v>0.7009652336604641</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>102.7682945852466</v>
+        <v>51.38414729262329</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09306103004357914</v>
+        <v>0.09294465109732605</v>
       </c>
       <c r="C4">
-        <v>5298.717668048045</v>
+        <v>5255.637405169064</v>
       </c>
       <c r="D4">
-        <v>4943.685668048045</v>
+        <v>4955.889405169063</v>
       </c>
       <c r="E4">
-        <v>-1379.832</v>
+        <v>-1324.548</v>
       </c>
       <c r="F4">
-        <v>110.568</v>
+        <v>165.852</v>
       </c>
       <c r="G4">
         <v>465.6</v>
@@ -1621,28 +1621,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M4">
-        <v>7.646605157748574</v>
+        <v>11.46990773662286</v>
       </c>
       <c r="N4">
-        <v>385.2676805565371</v>
+        <v>381.4443779776628</v>
       </c>
       <c r="O4">
-        <v>115.5803041669611</v>
+        <v>114.4333133932988</v>
       </c>
       <c r="P4">
-        <v>269.687376389576</v>
+        <v>267.011064584364</v>
       </c>
       <c r="Q4">
-        <v>307.487376389576</v>
+        <v>304.811064584364</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09397227062088653</v>
+        <v>0.09432200396356757</v>
       </c>
       <c r="T4">
-        <v>0.7009652336604641</v>
+        <v>0.7060542799335908</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.38414729262329</v>
+        <v>34.2560981950822</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09294465109732605</v>
+        <v>0.09282827215107296</v>
       </c>
       <c r="C5">
-        <v>5255.637405169064</v>
+        <v>5212.61754247072</v>
       </c>
       <c r="D5">
-        <v>4955.889405169063</v>
+        <v>4968.15354247072</v>
       </c>
       <c r="E5">
-        <v>-1324.548</v>
+        <v>-1269.264</v>
       </c>
       <c r="F5">
-        <v>165.852</v>
+        <v>221.136</v>
       </c>
       <c r="G5">
         <v>465.6</v>
@@ -1703,28 +1703,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M5">
-        <v>11.46990773662286</v>
+        <v>15.29321031549715</v>
       </c>
       <c r="N5">
-        <v>381.4443779776628</v>
+        <v>377.6210753987885</v>
       </c>
       <c r="O5">
-        <v>114.4333133932988</v>
+        <v>113.2863226196366</v>
       </c>
       <c r="P5">
-        <v>267.011064584364</v>
+        <v>264.334752779152</v>
       </c>
       <c r="Q5">
-        <v>304.811064584364</v>
+        <v>302.134752779152</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09432200396356757</v>
+        <v>0.09467902341755446</v>
       </c>
       <c r="T5">
-        <v>0.7060542799335908</v>
+        <v>0.7112493480040742</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.2560981950822</v>
+        <v>25.69207364631164</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09282827215107296</v>
+        <v>0.09271189320481987</v>
       </c>
       <c r="C6">
-        <v>5212.61754247072</v>
+        <v>5169.658529475016</v>
       </c>
       <c r="D6">
-        <v>4968.15354247072</v>
+        <v>4980.478529475015</v>
       </c>
       <c r="E6">
-        <v>-1269.264</v>
+        <v>-1213.98</v>
       </c>
       <c r="F6">
-        <v>221.136</v>
+        <v>276.42</v>
       </c>
       <c r="G6">
         <v>465.6</v>
@@ -1785,28 +1785,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M6">
-        <v>15.29321031549715</v>
+        <v>19.11651289437144</v>
       </c>
       <c r="N6">
-        <v>377.6210753987885</v>
+        <v>373.7977728199143</v>
       </c>
       <c r="O6">
-        <v>113.2863226196366</v>
+        <v>112.1393318459743</v>
       </c>
       <c r="P6">
-        <v>264.334752779152</v>
+        <v>261.65844097394</v>
       </c>
       <c r="Q6">
-        <v>302.134752779152</v>
+        <v>299.45844097394</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09467902341755446</v>
+        <v>0.09504355907057266</v>
       </c>
       <c r="T6">
-        <v>0.7112493480040742</v>
+        <v>0.7165537859286731</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.69207364631164</v>
+        <v>20.55365891704932</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09271189320481987</v>
+        <v>0.09259551425856678</v>
       </c>
       <c r="C7">
-        <v>5169.658529475016</v>
+        <v>5126.760820175739</v>
       </c>
       <c r="D7">
-        <v>4980.478529475015</v>
+        <v>4992.864820175739</v>
       </c>
       <c r="E7">
-        <v>-1213.98</v>
+        <v>-1158.696</v>
       </c>
       <c r="F7">
-        <v>276.42</v>
+        <v>331.704</v>
       </c>
       <c r="G7">
         <v>465.6</v>
@@ -1867,28 +1867,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M7">
-        <v>19.11651289437144</v>
+        <v>22.93981547324572</v>
       </c>
       <c r="N7">
-        <v>373.7977728199143</v>
+        <v>369.97447024104</v>
       </c>
       <c r="O7">
-        <v>112.1393318459743</v>
+        <v>110.992341072312</v>
       </c>
       <c r="P7">
-        <v>261.65844097394</v>
+        <v>258.982129168728</v>
       </c>
       <c r="Q7">
-        <v>299.45844097394</v>
+        <v>296.782129168728</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09504355907057266</v>
+        <v>0.09541585080131465</v>
       </c>
       <c r="T7">
-        <v>0.7165537859286731</v>
+        <v>0.7219710842346465</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.55365891704932</v>
+        <v>17.1280490975411</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09259551425856678</v>
+        <v>0.09247913531231372</v>
       </c>
       <c r="C8">
-        <v>5126.760820175739</v>
+        <v>5083.924873094207</v>
       </c>
       <c r="D8">
-        <v>4992.864820175739</v>
+        <v>5005.312873094207</v>
       </c>
       <c r="E8">
-        <v>-1158.696</v>
+        <v>-1103.412</v>
       </c>
       <c r="F8">
-        <v>331.704</v>
+        <v>386.9879999999999</v>
       </c>
       <c r="G8">
         <v>465.6</v>
@@ -1949,28 +1949,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M8">
-        <v>22.93981547324572</v>
+        <v>26.76311805212001</v>
       </c>
       <c r="N8">
-        <v>369.97447024104</v>
+        <v>366.1511676621657</v>
       </c>
       <c r="O8">
-        <v>110.992341072312</v>
+        <v>109.8453502986497</v>
       </c>
       <c r="P8">
-        <v>258.982129168728</v>
+        <v>256.305817363516</v>
       </c>
       <c r="Q8">
-        <v>296.782129168728</v>
+        <v>294.105817363516</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09541585080131465</v>
+        <v>0.09579614880583605</v>
       </c>
       <c r="T8">
-        <v>0.7219710842346465</v>
+        <v>0.7275048835794581</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.1280490975411</v>
+        <v>14.68118494074951</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09247913531231371</v>
+        <v>0.09236275636606062</v>
       </c>
       <c r="C9">
-        <v>5083.924873094209</v>
+        <v>5041.151151335863</v>
       </c>
       <c r="D9">
-        <v>5005.312873094209</v>
+        <v>5017.823151335862</v>
       </c>
       <c r="E9">
-        <v>-1103.412</v>
+        <v>-1048.128</v>
       </c>
       <c r="F9">
-        <v>386.988</v>
+        <v>442.272</v>
       </c>
       <c r="G9">
         <v>465.6</v>
@@ -2031,28 +2031,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M9">
-        <v>26.76311805212001</v>
+        <v>30.5864206309943</v>
       </c>
       <c r="N9">
-        <v>366.1511676621657</v>
+        <v>362.3278650832914</v>
       </c>
       <c r="O9">
-        <v>109.8453502986497</v>
+        <v>108.6983595249874</v>
       </c>
       <c r="P9">
-        <v>256.305817363516</v>
+        <v>253.629505558304</v>
       </c>
       <c r="Q9">
-        <v>294.105817363516</v>
+        <v>291.429505558304</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09579614880583605</v>
+        <v>0.09618471415828181</v>
       </c>
       <c r="T9">
-        <v>0.7275048835794581</v>
+        <v>0.7331589829100263</v>
       </c>
       <c r="U9">
         <v>0.06915748822216712</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.68118494074951</v>
+        <v>12.84603682315582</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09236275636606062</v>
+        <v>0.09234087741980754</v>
       </c>
       <c r="C10">
-        <v>5041.151151335863</v>
+        <v>4988.226038600606</v>
       </c>
       <c r="D10">
-        <v>5017.823151335862</v>
+        <v>5020.182038600605</v>
       </c>
       <c r="E10">
-        <v>-1048.128</v>
+        <v>-992.8440000000002</v>
       </c>
       <c r="F10">
-        <v>442.272</v>
+        <v>497.5559999999999</v>
       </c>
       <c r="G10">
         <v>465.6</v>
@@ -2113,45 +2113,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M10">
-        <v>30.5864206309943</v>
+        <v>35.15605720986857</v>
       </c>
       <c r="N10">
-        <v>362.3278650832914</v>
+        <v>357.7582285044172</v>
       </c>
       <c r="O10">
-        <v>108.6983595249874</v>
+        <v>107.3274685513251</v>
       </c>
       <c r="P10">
-        <v>253.629505558304</v>
+        <v>250.430759953092</v>
       </c>
       <c r="Q10">
-        <v>291.429505558304</v>
+        <v>288.230759953092</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09618471415828181</v>
+        <v>0.09658181940858353</v>
       </c>
       <c r="T10">
-        <v>0.7331589829100263</v>
+        <v>0.7389373481599476</v>
       </c>
       <c r="U10">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.04841024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>12.84603682315582</v>
+        <v>11.17628986005836</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09234087741980754</v>
+        <v>0.09223499847355444</v>
       </c>
       <c r="C11">
-        <v>4988.226038600606</v>
+        <v>4944.388826620819</v>
       </c>
       <c r="D11">
-        <v>5020.182038600605</v>
+        <v>5031.628826620818</v>
       </c>
       <c r="E11">
-        <v>-992.8440000000002</v>
+        <v>-937.5600000000002</v>
       </c>
       <c r="F11">
-        <v>497.5559999999999</v>
+        <v>552.8399999999999</v>
       </c>
       <c r="G11">
         <v>465.6</v>
@@ -2195,28 +2195,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M11">
-        <v>35.15605720986857</v>
+        <v>39.06228578874286</v>
       </c>
       <c r="N11">
-        <v>357.7582285044172</v>
+        <v>353.8519999255428</v>
       </c>
       <c r="O11">
-        <v>107.3274685513251</v>
+        <v>106.1555999776628</v>
       </c>
       <c r="P11">
-        <v>250.430759953092</v>
+        <v>247.69639994788</v>
       </c>
       <c r="Q11">
-        <v>288.230759953092</v>
+        <v>285.49639994788</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09658181940858353</v>
+        <v>0.09698774922000306</v>
       </c>
       <c r="T11">
-        <v>0.7389373481599476</v>
+        <v>0.7448441215265339</v>
       </c>
       <c r="U11">
         <v>0.07065748822216711</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.17628986005836</v>
+        <v>10.05866087405252</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09223499847355444</v>
+        <v>0.09226001952730135</v>
       </c>
       <c r="C12">
-        <v>4944.388826620819</v>
+        <v>4886.39504180828</v>
       </c>
       <c r="D12">
-        <v>5031.628826620818</v>
+        <v>5028.919041808279</v>
       </c>
       <c r="E12">
-        <v>-937.5600000000001</v>
+        <v>-882.2760000000002</v>
       </c>
       <c r="F12">
-        <v>552.84</v>
+        <v>608.1239999999999</v>
       </c>
       <c r="G12">
         <v>465.6</v>
@@ -2277,45 +2277,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M12">
-        <v>39.06228578874287</v>
+        <v>44.00232516761715</v>
       </c>
       <c r="N12">
-        <v>353.8519999255428</v>
+        <v>348.9119605466686</v>
       </c>
       <c r="O12">
-        <v>106.1555999776628</v>
+        <v>104.6735881640006</v>
       </c>
       <c r="P12">
-        <v>247.69639994788</v>
+        <v>244.238372382668</v>
       </c>
       <c r="Q12">
-        <v>285.49639994788</v>
+        <v>282.038372382668</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09698774922000306</v>
+        <v>0.09740280104965673</v>
       </c>
       <c r="T12">
-        <v>0.7448441215265339</v>
+        <v>0.7508836313732683</v>
       </c>
       <c r="U12">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.04946024175551697</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.05866087405252</v>
+        <v>8.929398258332155</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09226001952730135</v>
+        <v>0.09216604058104827</v>
       </c>
       <c r="C13">
-        <v>4886.39504180828</v>
+        <v>4841.304116446927</v>
       </c>
       <c r="D13">
-        <v>5028.919041808279</v>
+        <v>5039.112116446927</v>
       </c>
       <c r="E13">
-        <v>-882.2760000000002</v>
+        <v>-826.9920000000002</v>
       </c>
       <c r="F13">
-        <v>608.1239999999999</v>
+        <v>663.4079999999999</v>
       </c>
       <c r="G13">
         <v>465.6</v>
@@ -2359,28 +2359,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M13">
-        <v>44.00232516761715</v>
+        <v>48.00253654649143</v>
       </c>
       <c r="N13">
-        <v>348.9119605466686</v>
+        <v>344.9117491677943</v>
       </c>
       <c r="O13">
-        <v>104.6735881640006</v>
+        <v>103.4735247503383</v>
       </c>
       <c r="P13">
-        <v>244.238372382668</v>
+        <v>241.438224417456</v>
       </c>
       <c r="Q13">
-        <v>282.038372382668</v>
+        <v>279.238224417456</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09740280104965673</v>
+        <v>0.0978272858754389</v>
       </c>
       <c r="T13">
-        <v>0.7508836313732683</v>
+        <v>0.7570604028074284</v>
       </c>
       <c r="U13">
         <v>0.07235748822216712</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.929398258332155</v>
+        <v>8.185281736804475</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09216604058104827</v>
+        <v>0.09214486163479518</v>
       </c>
       <c r="C14">
-        <v>4841.304116446927</v>
+        <v>4788.322919409606</v>
       </c>
       <c r="D14">
-        <v>5039.112116446927</v>
+        <v>5041.414919409605</v>
       </c>
       <c r="E14">
-        <v>-826.9920000000002</v>
+        <v>-771.7080000000001</v>
       </c>
       <c r="F14">
-        <v>663.4079999999999</v>
+        <v>718.692</v>
       </c>
       <c r="G14">
         <v>465.6</v>
@@ -2441,45 +2441,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M14">
-        <v>48.00253654649143</v>
+        <v>52.57770152536573</v>
       </c>
       <c r="N14">
-        <v>344.9117491677943</v>
+        <v>340.33658418892</v>
       </c>
       <c r="O14">
-        <v>103.4735247503383</v>
+        <v>102.100975256676</v>
       </c>
       <c r="P14">
-        <v>241.438224417456</v>
+        <v>238.235608932244</v>
       </c>
       <c r="Q14">
-        <v>279.238224417456</v>
+        <v>276.035608932244</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0978272858754389</v>
+        <v>0.09826152897307815</v>
       </c>
       <c r="T14">
-        <v>0.7570604028074284</v>
+        <v>0.7633791689872014</v>
       </c>
       <c r="U14">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.05065024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.185281736804475</v>
+        <v>7.473021343938496</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09214486163479518</v>
+        <v>0.09205648268854211</v>
       </c>
       <c r="C15">
-        <v>4788.322919409606</v>
+        <v>4742.671189575974</v>
       </c>
       <c r="D15">
-        <v>5041.414919409605</v>
+        <v>5051.047189575973</v>
       </c>
       <c r="E15">
-        <v>-771.7080000000001</v>
+        <v>-716.4240000000001</v>
       </c>
       <c r="F15">
-        <v>718.692</v>
+        <v>773.976</v>
       </c>
       <c r="G15">
         <v>465.6</v>
@@ -2523,28 +2523,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M15">
-        <v>52.57770152536573</v>
+        <v>56.62214010424001</v>
       </c>
       <c r="N15">
-        <v>340.33658418892</v>
+        <v>336.2921456100457</v>
       </c>
       <c r="O15">
-        <v>102.100975256676</v>
+        <v>100.8876436830137</v>
       </c>
       <c r="P15">
-        <v>238.235608932244</v>
+        <v>235.404501927032</v>
       </c>
       <c r="Q15">
-        <v>276.035608932244</v>
+        <v>273.204501927032</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09826152897307815</v>
+        <v>0.09870587074740667</v>
       </c>
       <c r="T15">
-        <v>0.7633791689872014</v>
+        <v>0.7698448832176666</v>
       </c>
       <c r="U15">
         <v>0.07315748822216711</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.473021343938496</v>
+        <v>6.939234105085746</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09205648268854211</v>
+        <v>0.09196810374228903</v>
       </c>
       <c r="C16">
-        <v>4742.671189575974</v>
+        <v>4697.056337578697</v>
       </c>
       <c r="D16">
-        <v>5051.047189575973</v>
+        <v>5060.716337578697</v>
       </c>
       <c r="E16">
-        <v>-716.4240000000001</v>
+        <v>-661.14</v>
       </c>
       <c r="F16">
-        <v>773.976</v>
+        <v>829.2600000000001</v>
       </c>
       <c r="G16">
         <v>465.6</v>
@@ -2605,28 +2605,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M16">
-        <v>56.62214010424001</v>
+        <v>60.66657868311431</v>
       </c>
       <c r="N16">
-        <v>336.2921456100457</v>
+        <v>332.2477070311714</v>
       </c>
       <c r="O16">
-        <v>100.8876436830137</v>
+        <v>99.67431210935142</v>
       </c>
       <c r="P16">
-        <v>235.404501927032</v>
+        <v>232.57339492182</v>
       </c>
       <c r="Q16">
-        <v>273.204501927032</v>
+        <v>270.37339492182</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09870587074740667</v>
+        <v>0.09916066762230763</v>
       </c>
       <c r="T16">
-        <v>0.7698448832176666</v>
+        <v>0.7764627319006137</v>
       </c>
       <c r="U16">
         <v>0.07315748822216711</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.939234105085746</v>
+        <v>6.476618498080029</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09196810374228903</v>
+        <v>0.09199172479603591</v>
       </c>
       <c r="C17">
-        <v>4697.056337578697</v>
+        <v>4639.1844400032</v>
       </c>
       <c r="D17">
-        <v>5060.716337578697</v>
+        <v>5058.128440003199</v>
       </c>
       <c r="E17">
-        <v>-661.1400000000002</v>
+        <v>-605.8560000000001</v>
       </c>
       <c r="F17">
-        <v>829.2599999999999</v>
+        <v>884.544</v>
       </c>
       <c r="G17">
         <v>465.6</v>
@@ -2687,45 +2687,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M17">
-        <v>60.66657868311429</v>
+        <v>65.59556126198858</v>
       </c>
       <c r="N17">
-        <v>332.2477070311714</v>
+        <v>327.3187244522971</v>
       </c>
       <c r="O17">
-        <v>99.67431210935143</v>
+        <v>98.19561733568914</v>
       </c>
       <c r="P17">
-        <v>232.57339492182</v>
+        <v>229.123107116608</v>
       </c>
       <c r="Q17">
-        <v>270.37339492182</v>
+        <v>266.923107116608</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09916066762230763</v>
+        <v>0.09962629299423001</v>
       </c>
       <c r="T17">
-        <v>0.7764627319006137</v>
+        <v>0.7832381484093449</v>
       </c>
       <c r="U17">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05121024175551697</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.476618498080032</v>
+        <v>5.989952340601015</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09199172479603591</v>
+        <v>0.09191034584978286</v>
       </c>
       <c r="C18">
-        <v>4639.1844400032</v>
+        <v>4592.827398907413</v>
       </c>
       <c r="D18">
-        <v>5058.128440003199</v>
+        <v>5067.055398907413</v>
       </c>
       <c r="E18">
-        <v>-605.8560000000001</v>
+        <v>-550.5720000000001</v>
       </c>
       <c r="F18">
-        <v>884.544</v>
+        <v>939.828</v>
       </c>
       <c r="G18">
         <v>465.6</v>
@@ -2769,28 +2769,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M18">
-        <v>65.59556126198858</v>
+        <v>69.69528384086287</v>
       </c>
       <c r="N18">
-        <v>327.3187244522971</v>
+        <v>323.2190018734228</v>
       </c>
       <c r="O18">
-        <v>98.19561733568914</v>
+        <v>96.96570056202684</v>
       </c>
       <c r="P18">
-        <v>229.123107116608</v>
+        <v>226.253301311396</v>
       </c>
       <c r="Q18">
-        <v>266.923107116608</v>
+        <v>264.053301311396</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09962629299423001</v>
+        <v>0.1001031382546325</v>
       </c>
       <c r="T18">
-        <v>0.7832381484093449</v>
+        <v>0.7901768279664796</v>
       </c>
       <c r="U18">
         <v>0.07415748822216711</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.989952340601015</v>
+        <v>5.637602202918601</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09191034584978286</v>
+        <v>0.09182896690352976</v>
       </c>
       <c r="C19">
-        <v>4592.827398907413</v>
+        <v>4546.501923434661</v>
       </c>
       <c r="D19">
-        <v>5067.055398907413</v>
+        <v>5076.013923434661</v>
       </c>
       <c r="E19">
-        <v>-550.5720000000001</v>
+        <v>-495.288</v>
       </c>
       <c r="F19">
-        <v>939.828</v>
+        <v>995.1120000000001</v>
       </c>
       <c r="G19">
         <v>465.6</v>
@@ -2851,28 +2851,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M19">
-        <v>69.69528384086287</v>
+        <v>73.79500641973716</v>
       </c>
       <c r="N19">
-        <v>323.2190018734228</v>
+        <v>319.1192792945486</v>
       </c>
       <c r="O19">
-        <v>96.96570056202684</v>
+        <v>95.73578378836457</v>
       </c>
       <c r="P19">
-        <v>226.253301311396</v>
+        <v>223.383495506184</v>
       </c>
       <c r="Q19">
-        <v>264.053301311396</v>
+        <v>261.183495506184</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1001031382546325</v>
+        <v>0.1005916138872399</v>
       </c>
       <c r="T19">
-        <v>0.7901768279664796</v>
+        <v>0.7972847436103734</v>
       </c>
       <c r="U19">
         <v>0.07415748822216711</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.637602202918601</v>
+        <v>5.324402080534234</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09182896690352978</v>
+        <v>0.09174758795727668</v>
       </c>
       <c r="C20">
-        <v>4546.50192343466</v>
+        <v>4500.20818130498</v>
       </c>
       <c r="D20">
-        <v>5076.01392343466</v>
+        <v>5085.004181304979</v>
       </c>
       <c r="E20">
-        <v>-495.2880000000002</v>
+        <v>-440.0040000000001</v>
       </c>
       <c r="F20">
-        <v>995.1119999999999</v>
+        <v>1050.396</v>
       </c>
       <c r="G20">
         <v>465.6</v>
@@ -2933,28 +2933,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M20">
-        <v>73.79500641973715</v>
+        <v>77.89472899861144</v>
       </c>
       <c r="N20">
-        <v>319.1192792945486</v>
+        <v>315.0195567156743</v>
       </c>
       <c r="O20">
-        <v>95.73578378836457</v>
+        <v>94.50586701470229</v>
       </c>
       <c r="P20">
-        <v>223.383495506184</v>
+        <v>220.513689700972</v>
       </c>
       <c r="Q20">
-        <v>261.183495506184</v>
+        <v>258.313689700972</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1005916138872399</v>
+        <v>0.1010921506465783</v>
       </c>
       <c r="T20">
-        <v>0.7972847436103734</v>
+        <v>0.80456816334424</v>
       </c>
       <c r="U20">
         <v>0.07415748822216711</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.324402080534235</v>
+        <v>5.044170392085065</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09174758795727668</v>
+        <v>0.0916662090110236</v>
       </c>
       <c r="C21">
-        <v>4500.20818130498</v>
+        <v>4453.946341428737</v>
       </c>
       <c r="D21">
-        <v>5085.004181304979</v>
+        <v>5094.026341428736</v>
       </c>
       <c r="E21">
-        <v>-440.0040000000001</v>
+        <v>-384.72</v>
       </c>
       <c r="F21">
-        <v>1050.396</v>
+        <v>1105.68</v>
       </c>
       <c r="G21">
         <v>465.6</v>
@@ -3015,28 +3015,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M21">
-        <v>77.89472899861144</v>
+        <v>81.99445157748573</v>
       </c>
       <c r="N21">
-        <v>315.0195567156743</v>
+        <v>310.9198341368</v>
       </c>
       <c r="O21">
-        <v>94.50586701470229</v>
+        <v>93.27595024103999</v>
       </c>
       <c r="P21">
-        <v>220.513689700972</v>
+        <v>217.64388389576</v>
       </c>
       <c r="Q21">
-        <v>258.313689700972</v>
+        <v>255.44388389576</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1010921506465783</v>
+        <v>0.1016052008249002</v>
       </c>
       <c r="T21">
-        <v>0.80456816334424</v>
+        <v>0.8120336685714533</v>
       </c>
       <c r="U21">
         <v>0.07415748822216711</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.044170392085065</v>
+        <v>4.791961872480811</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0916662090110236</v>
+        <v>0.09158483006477051</v>
       </c>
       <c r="C22">
-        <v>4453.946341428737</v>
+        <v>4407.716573917193</v>
       </c>
       <c r="D22">
-        <v>5094.026341428736</v>
+        <v>5103.080573917193</v>
       </c>
       <c r="E22">
-        <v>-384.72</v>
+        <v>-329.4360000000001</v>
       </c>
       <c r="F22">
-        <v>1105.68</v>
+        <v>1160.964</v>
       </c>
       <c r="G22">
         <v>465.6</v>
@@ -3097,28 +3097,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M22">
-        <v>81.99445157748573</v>
+        <v>86.09417415636001</v>
       </c>
       <c r="N22">
-        <v>310.9198341368</v>
+        <v>306.8201115579257</v>
       </c>
       <c r="O22">
-        <v>93.27595024103999</v>
+        <v>92.04603346737771</v>
       </c>
       <c r="P22">
-        <v>217.64388389576</v>
+        <v>214.774078090548</v>
       </c>
       <c r="Q22">
-        <v>255.44388389576</v>
+        <v>252.574078090548</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1016052008249002</v>
+        <v>0.1021312396153316</v>
       </c>
       <c r="T22">
-        <v>0.8120336685714533</v>
+        <v>0.8196881739310011</v>
       </c>
       <c r="U22">
         <v>0.07415748822216711</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.791961872480811</v>
+        <v>4.563773211886487</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0915848300647705</v>
+        <v>0.09188845111851743</v>
       </c>
       <c r="C23">
-        <v>4407.716573917194</v>
+        <v>4318.8145489325</v>
       </c>
       <c r="D23">
-        <v>5103.080573917194</v>
+        <v>5069.462548932499</v>
       </c>
       <c r="E23">
-        <v>-329.4360000000001</v>
+        <v>-274.1520000000003</v>
       </c>
       <c r="F23">
-        <v>1160.964</v>
+        <v>1216.248</v>
       </c>
       <c r="G23">
         <v>465.6</v>
@@ -3179,45 +3179,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M23">
-        <v>86.09417415636001</v>
+        <v>93.23451673523429</v>
       </c>
       <c r="N23">
-        <v>306.8201115579257</v>
+        <v>299.6797689790514</v>
       </c>
       <c r="O23">
-        <v>92.04603346737771</v>
+        <v>89.90393069371542</v>
       </c>
       <c r="P23">
-        <v>214.774078090548</v>
+        <v>209.775838285336</v>
       </c>
       <c r="Q23">
-        <v>252.574078090548</v>
+        <v>247.575838285336</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1021312396153316</v>
+        <v>0.1026707665798765</v>
       </c>
       <c r="T23">
-        <v>0.8196881739310009</v>
+        <v>0.8275389486587423</v>
       </c>
       <c r="U23">
-        <v>0.07415748822216711</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05191024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.563773211886487</v>
+        <v>4.214257760675444</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09188845111851743</v>
+        <v>0.09182457217226433</v>
       </c>
       <c r="C24">
-        <v>4318.8145489325</v>
+        <v>4270.566614894899</v>
       </c>
       <c r="D24">
-        <v>5069.462548932499</v>
+        <v>5076.498614894899</v>
       </c>
       <c r="E24">
-        <v>-274.1520000000003</v>
+        <v>-218.8680000000002</v>
       </c>
       <c r="F24">
-        <v>1216.248</v>
+        <v>1271.532</v>
       </c>
       <c r="G24">
         <v>465.6</v>
@@ -3261,28 +3261,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M24">
-        <v>93.23451673523429</v>
+        <v>97.47244931410859</v>
       </c>
       <c r="N24">
-        <v>299.6797689790514</v>
+        <v>295.4418364001771</v>
       </c>
       <c r="O24">
-        <v>89.90393069371542</v>
+        <v>88.63255092005313</v>
       </c>
       <c r="P24">
-        <v>209.775838285336</v>
+        <v>206.809285480124</v>
       </c>
       <c r="Q24">
-        <v>247.575838285336</v>
+        <v>244.609285480124</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1026707665798765</v>
+        <v>0.1032243072318122</v>
       </c>
       <c r="T24">
-        <v>0.8275389486587423</v>
+        <v>0.8355936396131781</v>
       </c>
       <c r="U24">
         <v>0.07665748822216711</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.214257760675444</v>
+        <v>4.031029162385208</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09182457217226433</v>
+        <v>0.09234869322601125</v>
       </c>
       <c r="C25">
-        <v>4270.566614894899</v>
+        <v>4158.123119772991</v>
       </c>
       <c r="D25">
-        <v>5076.498614894899</v>
+        <v>5019.339119772991</v>
       </c>
       <c r="E25">
-        <v>-218.8680000000002</v>
+        <v>-163.5840000000001</v>
       </c>
       <c r="F25">
-        <v>1271.532</v>
+        <v>1326.816</v>
       </c>
       <c r="G25">
         <v>465.6</v>
@@ -3343,45 +3343,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M25">
-        <v>97.47244931410859</v>
+        <v>106.3542378929829</v>
       </c>
       <c r="N25">
-        <v>295.4418364001771</v>
+        <v>286.5600478213028</v>
       </c>
       <c r="O25">
-        <v>88.63255092005313</v>
+        <v>85.96801434639085</v>
       </c>
       <c r="P25">
-        <v>206.809285480124</v>
+        <v>200.592033474912</v>
       </c>
       <c r="Q25">
-        <v>244.609285480124</v>
+        <v>238.392033474912</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1032243072318122</v>
+        <v>0.1037924147430094</v>
       </c>
       <c r="T25">
-        <v>0.8355936396131781</v>
+        <v>0.8438602961190467</v>
       </c>
       <c r="U25">
-        <v>0.07665748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05366024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.031029162385208</v>
+        <v>3.69439237681952</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09234869322601125</v>
+        <v>0.09230931427975815</v>
       </c>
       <c r="C26">
-        <v>4158.123119772991</v>
+        <v>4107.088941308408</v>
       </c>
       <c r="D26">
-        <v>5019.339119772991</v>
+        <v>5023.588941308408</v>
       </c>
       <c r="E26">
-        <v>-163.5840000000003</v>
+        <v>-108.3000000000002</v>
       </c>
       <c r="F26">
-        <v>1326.816</v>
+        <v>1382.1</v>
       </c>
       <c r="G26">
         <v>465.6</v>
@@ -3425,28 +3425,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M26">
-        <v>106.3542378929829</v>
+        <v>110.7856644718572</v>
       </c>
       <c r="N26">
-        <v>286.5600478213029</v>
+        <v>282.1286212424286</v>
       </c>
       <c r="O26">
-        <v>85.96801434639086</v>
+        <v>84.63858637272857</v>
       </c>
       <c r="P26">
-        <v>200.592033474912</v>
+        <v>197.4900348697</v>
       </c>
       <c r="Q26">
-        <v>238.392033474912</v>
+        <v>235.2900348697</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1037924147430094</v>
+        <v>0.1043756717878385</v>
       </c>
       <c r="T26">
-        <v>0.8438602961190467</v>
+        <v>0.8523473967984049</v>
       </c>
       <c r="U26">
         <v>0.08015748822216712</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.694392376819521</v>
+        <v>3.54661668174674</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09230931427975815</v>
+        <v>0.09277953533350507</v>
       </c>
       <c r="C27">
-        <v>4107.088941308408</v>
+        <v>4001.523531141102</v>
       </c>
       <c r="D27">
-        <v>5023.588941308408</v>
+        <v>4973.307531141102</v>
       </c>
       <c r="E27">
-        <v>-108.3000000000002</v>
+        <v>-53.01600000000008</v>
       </c>
       <c r="F27">
-        <v>1382.1</v>
+        <v>1437.384</v>
       </c>
       <c r="G27">
         <v>465.6</v>
@@ -3507,45 +3507,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M27">
-        <v>110.7856644718572</v>
+        <v>119.2417662507315</v>
       </c>
       <c r="N27">
-        <v>282.1286212424286</v>
+        <v>273.6725194635542</v>
       </c>
       <c r="O27">
-        <v>84.63858637272857</v>
+        <v>82.10175583906627</v>
       </c>
       <c r="P27">
-        <v>197.4900348697</v>
+        <v>191.570763624488</v>
       </c>
       <c r="Q27">
-        <v>235.2900348697</v>
+        <v>229.370763624488</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1043756717878385</v>
+        <v>0.104974692536582</v>
       </c>
       <c r="T27">
-        <v>0.8523473967984049</v>
+        <v>0.8610638785772051</v>
       </c>
       <c r="U27">
-        <v>0.08015748822216712</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.05611024175551698</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.54661668174674</v>
+        <v>3.295106220484012</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09277953533350507</v>
+        <v>0.09275975638725199</v>
       </c>
       <c r="C28">
-        <v>4001.523531141102</v>
+        <v>3948.3342349881</v>
       </c>
       <c r="D28">
-        <v>4973.307531141102</v>
+        <v>4975.4022349881</v>
       </c>
       <c r="E28">
-        <v>-53.01600000000008</v>
+        <v>2.267999999999802</v>
       </c>
       <c r="F28">
-        <v>1437.384</v>
+        <v>1492.668</v>
       </c>
       <c r="G28">
         <v>465.6</v>
@@ -3589,28 +3589,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M28">
-        <v>119.2417662507315</v>
+        <v>123.8279880296057</v>
       </c>
       <c r="N28">
-        <v>273.6725194635542</v>
+        <v>269.0862976846799</v>
       </c>
       <c r="O28">
-        <v>82.10175583906627</v>
+        <v>80.72588930540398</v>
       </c>
       <c r="P28">
-        <v>191.570763624488</v>
+        <v>188.360408379276</v>
       </c>
       <c r="Q28">
-        <v>229.370763624488</v>
+        <v>226.160408379276</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.104974692536582</v>
+        <v>0.1055901248126882</v>
       </c>
       <c r="T28">
-        <v>0.8610638785772051</v>
+        <v>0.8700191680759727</v>
       </c>
       <c r="U28">
         <v>0.08295748822216711</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.295106220484012</v>
+        <v>3.173065249354974</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09275975638725199</v>
+        <v>0.09273997744099889</v>
       </c>
       <c r="C29">
-        <v>3948.3342349881</v>
+        <v>3895.146704112251</v>
       </c>
       <c r="D29">
-        <v>4975.4022349881</v>
+        <v>4977.49870411225</v>
       </c>
       <c r="E29">
-        <v>2.267999999999802</v>
+        <v>57.55199999999991</v>
       </c>
       <c r="F29">
-        <v>1492.668</v>
+        <v>1547.952</v>
       </c>
       <c r="G29">
         <v>465.6</v>
@@ -3671,28 +3671,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M29">
-        <v>123.8279880296057</v>
+        <v>128.41420980848</v>
       </c>
       <c r="N29">
-        <v>269.0862976846799</v>
+        <v>264.5000759058057</v>
       </c>
       <c r="O29">
-        <v>80.72588930540398</v>
+        <v>79.35002277174171</v>
       </c>
       <c r="P29">
-        <v>188.360408379276</v>
+        <v>185.150053134064</v>
       </c>
       <c r="Q29">
-        <v>226.160408379276</v>
+        <v>222.950053134064</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1055901248126882</v>
+        <v>0.1062226524297974</v>
       </c>
       <c r="T29">
-        <v>0.8700191680759727</v>
+        <v>0.8792232156163725</v>
       </c>
       <c r="U29">
         <v>0.08295748822216711</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.173065249354974</v>
+        <v>3.05974149044944</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09273997744099889</v>
+        <v>0.09430359849474582</v>
       </c>
       <c r="C30">
-        <v>3895.146704112251</v>
+        <v>3679.401995829111</v>
       </c>
       <c r="D30">
-        <v>4977.49870411225</v>
+        <v>4817.037995829111</v>
       </c>
       <c r="E30">
-        <v>57.55199999999991</v>
+        <v>112.836</v>
       </c>
       <c r="F30">
-        <v>1547.952</v>
+        <v>1603.236</v>
       </c>
       <c r="G30">
         <v>465.6</v>
@@ -3753,45 +3753,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M30">
-        <v>128.41420980848</v>
+        <v>145.5056723873543</v>
       </c>
       <c r="N30">
-        <v>264.5000759058057</v>
+        <v>247.4086133269314</v>
       </c>
       <c r="O30">
-        <v>79.35002277174171</v>
+        <v>74.22258399807941</v>
       </c>
       <c r="P30">
-        <v>185.150053134064</v>
+        <v>173.186029328852</v>
       </c>
       <c r="Q30">
-        <v>222.950053134064</v>
+        <v>210.986029328852</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1062226524297974</v>
+        <v>0.1068729977262618</v>
       </c>
       <c r="T30">
-        <v>0.8792232156163725</v>
+        <v>0.8886865321015726</v>
       </c>
       <c r="U30">
-        <v>0.08295748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.05807024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.05974149044944</v>
+        <v>2.700336552298103</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09430359849474582</v>
+        <v>0.09433841954849273</v>
       </c>
       <c r="C31">
-        <v>3679.401995829111</v>
+        <v>3620.662293304927</v>
       </c>
       <c r="D31">
-        <v>4817.037995829111</v>
+        <v>4813.582293304926</v>
       </c>
       <c r="E31">
-        <v>112.8359999999998</v>
+        <v>168.1199999999997</v>
       </c>
       <c r="F31">
-        <v>1603.236</v>
+        <v>1658.52</v>
       </c>
       <c r="G31">
         <v>465.6</v>
@@ -3835,28 +3835,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M31">
-        <v>145.5056723873543</v>
+        <v>150.5231093662286</v>
       </c>
       <c r="N31">
-        <v>247.4086133269314</v>
+        <v>242.3911763480571</v>
       </c>
       <c r="O31">
-        <v>74.22258399807941</v>
+        <v>72.71735290441713</v>
       </c>
       <c r="P31">
-        <v>173.186029328852</v>
+        <v>169.67382344364</v>
       </c>
       <c r="Q31">
-        <v>210.986029328852</v>
+        <v>207.47382344364</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1068729977262618</v>
+        <v>0.1075419243169109</v>
       </c>
       <c r="T31">
-        <v>0.8886865321015726</v>
+        <v>0.8984202290577781</v>
       </c>
       <c r="U31">
         <v>0.09075748822216712</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.700336552298103</v>
+        <v>2.610325333888167</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09433841954849273</v>
+        <v>0.09437324060223963</v>
       </c>
       <c r="C32">
-        <v>3620.662293304927</v>
+        <v>3561.927545410156</v>
       </c>
       <c r="D32">
-        <v>4813.582293304926</v>
+        <v>4810.131545410156</v>
       </c>
       <c r="E32">
-        <v>168.1199999999997</v>
+        <v>223.4039999999998</v>
       </c>
       <c r="F32">
-        <v>1658.52</v>
+        <v>1713.804</v>
       </c>
       <c r="G32">
         <v>465.6</v>
@@ -3917,28 +3917,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M32">
-        <v>150.5231093662286</v>
+        <v>155.5405463451029</v>
       </c>
       <c r="N32">
-        <v>242.3911763480571</v>
+        <v>237.3737393691828</v>
       </c>
       <c r="O32">
-        <v>72.71735290441713</v>
+        <v>71.21212181075485</v>
       </c>
       <c r="P32">
-        <v>169.67382344364</v>
+        <v>166.161617558428</v>
       </c>
       <c r="Q32">
-        <v>207.47382344364</v>
+        <v>203.961617558428</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1075419243169109</v>
+        <v>0.1082302400841005</v>
       </c>
       <c r="T32">
-        <v>0.8984202290577781</v>
+        <v>0.9084360621576417</v>
       </c>
       <c r="U32">
         <v>0.09075748822216712</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.610325333888167</v>
+        <v>2.526121290859516</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09437324060223963</v>
+        <v>0.09528166165598655</v>
       </c>
       <c r="C33">
-        <v>3561.927545410156</v>
+        <v>3418.335581996925</v>
       </c>
       <c r="D33">
-        <v>4810.131545410156</v>
+        <v>4721.823581996924</v>
       </c>
       <c r="E33">
-        <v>223.4039999999998</v>
+        <v>278.6879999999999</v>
       </c>
       <c r="F33">
-        <v>1713.804</v>
+        <v>1769.088</v>
       </c>
       <c r="G33">
         <v>465.6</v>
@@ -3999,45 +3999,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M33">
-        <v>155.5405463451029</v>
+        <v>167.4574265239772</v>
       </c>
       <c r="N33">
-        <v>237.3737393691828</v>
+        <v>225.4568591903085</v>
       </c>
       <c r="O33">
-        <v>71.21212181075485</v>
+        <v>67.63705775709256</v>
       </c>
       <c r="P33">
-        <v>166.161617558428</v>
+        <v>157.819801433216</v>
       </c>
       <c r="Q33">
-        <v>203.961617558428</v>
+        <v>195.619801433216</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1082302400841005</v>
+        <v>0.1089388004326781</v>
       </c>
       <c r="T33">
-        <v>0.9084360621576417</v>
+        <v>0.9187464785839721</v>
       </c>
       <c r="U33">
-        <v>0.09075748822216712</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.06353024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.526121290859516</v>
+        <v>2.346353302270693</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09528166165598655</v>
+        <v>0.09534378270973345</v>
       </c>
       <c r="C34">
-        <v>3418.335581996925</v>
+        <v>3357.131068049914</v>
       </c>
       <c r="D34">
-        <v>4721.823581996924</v>
+        <v>4715.903068049914</v>
       </c>
       <c r="E34">
-        <v>278.6879999999999</v>
+        <v>333.972</v>
       </c>
       <c r="F34">
-        <v>1769.088</v>
+        <v>1824.372</v>
       </c>
       <c r="G34">
         <v>465.6</v>
@@ -4081,28 +4081,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M34">
-        <v>167.4574265239772</v>
+        <v>172.6904711028515</v>
       </c>
       <c r="N34">
-        <v>225.4568591903085</v>
+        <v>220.2238146114342</v>
       </c>
       <c r="O34">
-        <v>67.63705775709256</v>
+        <v>66.06714438343027</v>
       </c>
       <c r="P34">
-        <v>157.819801433216</v>
+        <v>154.156670228004</v>
       </c>
       <c r="Q34">
-        <v>195.619801433216</v>
+        <v>191.956670228004</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1089388004326781</v>
+        <v>0.1096685118364371</v>
       </c>
       <c r="T34">
-        <v>0.9187464785839721</v>
+        <v>0.9293646686349691</v>
       </c>
       <c r="U34">
         <v>0.09465748822216712</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.346353302270693</v>
+        <v>2.275251687050369</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09534378270973345</v>
+        <v>0.09540590376348038</v>
       </c>
       <c r="C35">
-        <v>3357.131068049914</v>
+        <v>3295.941382521989</v>
       </c>
       <c r="D35">
-        <v>4715.903068049914</v>
+        <v>4709.997382521989</v>
       </c>
       <c r="E35">
-        <v>333.972</v>
+        <v>389.2559999999999</v>
       </c>
       <c r="F35">
-        <v>1824.372</v>
+        <v>1879.656</v>
       </c>
       <c r="G35">
         <v>465.6</v>
@@ -4163,28 +4163,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M35">
-        <v>172.6904711028515</v>
+        <v>177.9235156817257</v>
       </c>
       <c r="N35">
-        <v>220.2238146114342</v>
+        <v>214.99077003256</v>
       </c>
       <c r="O35">
-        <v>66.06714438343027</v>
+        <v>64.49723100976799</v>
       </c>
       <c r="P35">
-        <v>154.156670228004</v>
+        <v>150.493539022792</v>
       </c>
       <c r="Q35">
-        <v>191.956670228004</v>
+        <v>188.293539022792</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1096685118364371</v>
+        <v>0.1104203357069767</v>
       </c>
       <c r="T35">
-        <v>0.9293646686349691</v>
+        <v>0.9403046220208446</v>
       </c>
       <c r="U35">
         <v>0.09465748822216712</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.275251687050369</v>
+        <v>2.208332519784181</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09540590376348038</v>
+        <v>0.09546802481722727</v>
       </c>
       <c r="C36">
-        <v>3295.941382521989</v>
+        <v>3234.76646977432</v>
       </c>
       <c r="D36">
-        <v>4709.997382521989</v>
+        <v>4704.10646977432</v>
       </c>
       <c r="E36">
-        <v>389.2559999999999</v>
+        <v>444.54</v>
       </c>
       <c r="F36">
-        <v>1879.656</v>
+        <v>1934.94</v>
       </c>
       <c r="G36">
         <v>465.6</v>
@@ -4245,28 +4245,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M36">
-        <v>177.9235156817257</v>
+        <v>183.1565602606</v>
       </c>
       <c r="N36">
-        <v>214.99077003256</v>
+        <v>209.7577254536857</v>
       </c>
       <c r="O36">
-        <v>64.49723100976799</v>
+        <v>62.9273176361057</v>
       </c>
       <c r="P36">
-        <v>150.493539022792</v>
+        <v>146.83040781758</v>
       </c>
       <c r="Q36">
-        <v>188.293539022792</v>
+        <v>184.63040781758</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1104203357069767</v>
+        <v>0.1111952926196867</v>
       </c>
       <c r="T36">
-        <v>0.9403046220208446</v>
+        <v>0.9515811893570548</v>
       </c>
       <c r="U36">
         <v>0.09465748822216712</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.208332519784181</v>
+        <v>2.145237304933205</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09546802481722727</v>
+        <v>0.09553014587097422</v>
       </c>
       <c r="C37">
-        <v>3234.76646977432</v>
+        <v>3173.60627444607</v>
       </c>
       <c r="D37">
-        <v>4704.10646977432</v>
+        <v>4698.230274446069</v>
       </c>
       <c r="E37">
-        <v>444.54</v>
+        <v>499.8240000000001</v>
       </c>
       <c r="F37">
-        <v>1934.94</v>
+        <v>1990.224</v>
       </c>
       <c r="G37">
         <v>465.6</v>
@@ -4327,28 +4327,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M37">
-        <v>183.1565602606</v>
+        <v>188.3896048394743</v>
       </c>
       <c r="N37">
-        <v>209.7577254536857</v>
+        <v>204.5246808748114</v>
       </c>
       <c r="O37">
-        <v>62.9273176361057</v>
+        <v>61.35740426244341</v>
       </c>
       <c r="P37">
-        <v>146.83040781758</v>
+        <v>143.167276612368</v>
       </c>
       <c r="Q37">
-        <v>184.63040781758</v>
+        <v>180.967276612368</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1111952926196867</v>
+        <v>0.1119944669359189</v>
       </c>
       <c r="T37">
-        <v>0.9515811893570548</v>
+        <v>0.9632101494225217</v>
       </c>
       <c r="U37">
         <v>0.09465748822216712</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.145237304933205</v>
+        <v>2.085647379796171</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09553014587097422</v>
+        <v>0.09559226692472111</v>
       </c>
       <c r="C38">
-        <v>3173.60627444607</v>
+        <v>3112.460741452695</v>
       </c>
       <c r="D38">
-        <v>4698.230274446069</v>
+        <v>4692.368741452695</v>
       </c>
       <c r="E38">
-        <v>499.8239999999996</v>
+        <v>555.1079999999997</v>
       </c>
       <c r="F38">
-        <v>1990.224</v>
+        <v>2045.508</v>
       </c>
       <c r="G38">
         <v>465.6</v>
@@ -4409,28 +4409,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M38">
-        <v>188.3896048394743</v>
+        <v>193.6226494183486</v>
       </c>
       <c r="N38">
-        <v>204.5246808748114</v>
+        <v>199.2916362959371</v>
       </c>
       <c r="O38">
-        <v>61.35740426244342</v>
+        <v>59.78749088878113</v>
       </c>
       <c r="P38">
-        <v>143.167276612368</v>
+        <v>139.504145407156</v>
       </c>
       <c r="Q38">
-        <v>180.967276612368</v>
+        <v>177.304145407156</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1119944669359189</v>
+        <v>0.1128190118653648</v>
       </c>
       <c r="T38">
-        <v>0.9632101494225217</v>
+        <v>0.9752082828234</v>
       </c>
       <c r="U38">
         <v>0.09465748822216712</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.085647379796172</v>
+        <v>2.029278531693572</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09559226692472111</v>
+        <v>0.09943158797846804</v>
       </c>
       <c r="C39">
-        <v>3112.460741452695</v>
+        <v>2721.26444088393</v>
       </c>
       <c r="D39">
-        <v>4692.368741452695</v>
+        <v>4356.45644088393</v>
       </c>
       <c r="E39">
-        <v>555.1079999999997</v>
+        <v>610.3919999999998</v>
       </c>
       <c r="F39">
-        <v>2045.508</v>
+        <v>2100.792</v>
       </c>
       <c r="G39">
         <v>465.6</v>
@@ -4491,45 +4491,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M39">
-        <v>193.6226494183486</v>
+        <v>228.6869403972229</v>
       </c>
       <c r="N39">
-        <v>199.2916362959371</v>
+        <v>164.2273453170628</v>
       </c>
       <c r="O39">
-        <v>59.78749088878113</v>
+        <v>49.26820359511884</v>
       </c>
       <c r="P39">
-        <v>139.504145407156</v>
+        <v>114.959141721944</v>
       </c>
       <c r="Q39">
-        <v>177.304145407156</v>
+        <v>152.759141721944</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1128190118653648</v>
+        <v>0.1136701550183413</v>
       </c>
       <c r="T39">
-        <v>0.9752082828234</v>
+        <v>0.9875934527855972</v>
       </c>
       <c r="U39">
-        <v>0.09465748822216712</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.06626024175551698</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.029278531693572</v>
+        <v>1.718131717673971</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09943158797846804</v>
+        <v>0.09959310903221497</v>
       </c>
       <c r="C40">
-        <v>2721.26444088393</v>
+        <v>2652.899593771846</v>
       </c>
       <c r="D40">
-        <v>4356.45644088393</v>
+        <v>4343.375593771845</v>
       </c>
       <c r="E40">
-        <v>610.3919999999998</v>
+        <v>665.6759999999999</v>
       </c>
       <c r="F40">
-        <v>2100.792</v>
+        <v>2156.076</v>
       </c>
       <c r="G40">
         <v>465.6</v>
@@ -4573,28 +4573,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M40">
-        <v>228.6869403972229</v>
+        <v>234.7050177760972</v>
       </c>
       <c r="N40">
-        <v>164.2273453170628</v>
+        <v>158.2092679381885</v>
       </c>
       <c r="O40">
-        <v>49.26820359511884</v>
+        <v>47.46278038145655</v>
       </c>
       <c r="P40">
-        <v>114.959141721944</v>
+        <v>110.7464875567319</v>
       </c>
       <c r="Q40">
-        <v>152.759141721944</v>
+        <v>148.546487556732</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1136701550183413</v>
+        <v>0.1145492045042022</v>
       </c>
       <c r="T40">
-        <v>0.9875934527855972</v>
+        <v>1.000384693894096</v>
       </c>
       <c r="U40">
         <v>0.1088574882221671</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.718131717673971</v>
+        <v>1.674077058246433</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09959310903221497</v>
+        <v>0.09975463008596187</v>
       </c>
       <c r="C41">
-        <v>2652.899593771846</v>
+        <v>2584.613065506766</v>
       </c>
       <c r="D41">
-        <v>4343.375593771845</v>
+        <v>4330.373065506766</v>
       </c>
       <c r="E41">
-        <v>665.6759999999999</v>
+        <v>720.96</v>
       </c>
       <c r="F41">
-        <v>2156.076</v>
+        <v>2211.36</v>
       </c>
       <c r="G41">
         <v>465.6</v>
@@ -4655,28 +4655,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M41">
-        <v>234.7050177760972</v>
+        <v>240.7230951549715</v>
       </c>
       <c r="N41">
-        <v>158.2092679381885</v>
+        <v>152.1911905593142</v>
       </c>
       <c r="O41">
-        <v>47.46278038145655</v>
+        <v>45.65735716779426</v>
       </c>
       <c r="P41">
-        <v>110.7464875567319</v>
+        <v>106.5338333915199</v>
       </c>
       <c r="Q41">
-        <v>148.546487556732</v>
+        <v>144.33383339152</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1145492045042022</v>
+        <v>0.1154575556395918</v>
       </c>
       <c r="T41">
-        <v>1.000384693894096</v>
+        <v>1.013602309706211</v>
       </c>
       <c r="U41">
         <v>0.1088574882221671</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.674077058246433</v>
+        <v>1.632225131790273</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09975463008596187</v>
+        <v>0.09991615113970878</v>
       </c>
       <c r="C42">
-        <v>2584.613065506766</v>
+        <v>2516.404154811396</v>
       </c>
       <c r="D42">
-        <v>4330.373065506766</v>
+        <v>4317.448154811395</v>
       </c>
       <c r="E42">
-        <v>720.96</v>
+        <v>776.2440000000001</v>
       </c>
       <c r="F42">
-        <v>2211.36</v>
+        <v>2266.644</v>
       </c>
       <c r="G42">
         <v>465.6</v>
@@ -4737,28 +4737,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M42">
-        <v>240.7230951549715</v>
+        <v>246.7411725338458</v>
       </c>
       <c r="N42">
-        <v>152.1911905593142</v>
+        <v>146.1731131804399</v>
       </c>
       <c r="O42">
-        <v>45.65735716779426</v>
+        <v>43.85193395413197</v>
       </c>
       <c r="P42">
-        <v>106.5338333915199</v>
+        <v>102.3211792263079</v>
       </c>
       <c r="Q42">
-        <v>144.33383339152</v>
+        <v>140.121179226308</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1154575556395918</v>
+        <v>0.1163966983388929</v>
       </c>
       <c r="T42">
-        <v>1.013602309706211</v>
+        <v>1.027267980291618</v>
       </c>
       <c r="U42">
         <v>0.1088574882221671</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.632225131790273</v>
+        <v>1.592414762722217</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09991615113970878</v>
+        <v>0.1000776721934557</v>
       </c>
       <c r="C43">
-        <v>2516.404154811396</v>
+        <v>2448.272168755964</v>
       </c>
       <c r="D43">
-        <v>4317.448154811395</v>
+        <v>4304.600168755964</v>
       </c>
       <c r="E43">
-        <v>776.2440000000001</v>
+        <v>831.5279999999998</v>
       </c>
       <c r="F43">
-        <v>2266.644</v>
+        <v>2321.928</v>
       </c>
       <c r="G43">
         <v>465.6</v>
@@ -4819,28 +4819,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M43">
-        <v>246.7411725338458</v>
+        <v>252.75924991272</v>
       </c>
       <c r="N43">
-        <v>146.1731131804399</v>
+        <v>140.1550358015657</v>
       </c>
       <c r="O43">
-        <v>43.85193395413197</v>
+        <v>42.0465107404697</v>
       </c>
       <c r="P43">
-        <v>102.3211792263079</v>
+        <v>98.10852506109597</v>
       </c>
       <c r="Q43">
-        <v>140.121179226308</v>
+        <v>135.908525061096</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1163966983388929</v>
+        <v>0.1173682252692044</v>
       </c>
       <c r="T43">
-        <v>1.027267980291618</v>
+        <v>1.041404880897212</v>
       </c>
       <c r="U43">
         <v>0.1088574882221671</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.592414762722217</v>
+        <v>1.554500125514546</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1000776721934557</v>
+        <v>0.1002391932472026</v>
       </c>
       <c r="C44">
-        <v>2448.272168755964</v>
+        <v>2380.216422634389</v>
       </c>
       <c r="D44">
-        <v>4304.600168755964</v>
+        <v>4291.828422634389</v>
       </c>
       <c r="E44">
-        <v>831.5279999999998</v>
+        <v>886.8119999999999</v>
       </c>
       <c r="F44">
-        <v>2321.928</v>
+        <v>2377.212</v>
       </c>
       <c r="G44">
         <v>465.6</v>
@@ -4901,28 +4901,28 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M44">
-        <v>252.75924991272</v>
+        <v>258.7773272915944</v>
       </c>
       <c r="N44">
-        <v>140.1550358015657</v>
+        <v>134.1369584226914</v>
       </c>
       <c r="O44">
-        <v>42.0465107404697</v>
+        <v>40.24108752680741</v>
       </c>
       <c r="P44">
-        <v>98.10852506109597</v>
+        <v>93.89587089588395</v>
       </c>
       <c r="Q44">
-        <v>135.908525061096</v>
+        <v>131.695870895884</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1173682252692044</v>
+        <v>0.1183738408637374</v>
       </c>
       <c r="T44">
-        <v>1.041404880897212</v>
+        <v>1.056037813103002</v>
       </c>
       <c r="U44">
         <v>0.1088574882221671</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.554500125514546</v>
+        <v>1.518348959804905</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1002391932472026</v>
+        <v>0.1185966186773166</v>
       </c>
       <c r="C45">
-        <v>2380.216422634389</v>
+        <v>1242.644238665419</v>
       </c>
       <c r="D45">
-        <v>4291.828422634389</v>
+        <v>3209.540238665419</v>
       </c>
       <c r="E45">
-        <v>886.8119999999999</v>
+        <v>942.0959999999995</v>
       </c>
       <c r="F45">
-        <v>2377.212</v>
+        <v>2432.496</v>
       </c>
       <c r="G45">
         <v>465.6</v>
@@ -4983,45 +4983,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M45">
-        <v>258.7773272915944</v>
+        <v>402.9611774704686</v>
       </c>
       <c r="N45">
-        <v>134.1369584226914</v>
+        <v>-10.0468917561829</v>
       </c>
       <c r="O45">
-        <v>40.24108752680741</v>
+        <v>-3.01406752685487</v>
       </c>
       <c r="P45">
-        <v>93.89587089588395</v>
+        <v>-7.032824229328032</v>
       </c>
       <c r="Q45">
-        <v>131.695870895884</v>
+        <v>30.76717577067198</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1183738408637374</v>
+        <v>0.1196944914763165</v>
       </c>
       <c r="T45">
-        <v>1.056037813103002</v>
+        <v>1.075254888679859</v>
       </c>
       <c r="U45">
-        <v>0.1088574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V45">
-        <v>0.3</v>
+        <v>0.2925202036936281</v>
       </c>
       <c r="W45">
-        <v>0.07620024175551698</v>
+        <v>0.117199326024044</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.518348959804905</v>
+        <v>0.9750673456454271</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1185966186773166</v>
+        <v>0.1197951935595383</v>
       </c>
       <c r="C46">
-        <v>1242.644238665419</v>
+        <v>1135.372073914573</v>
       </c>
       <c r="D46">
-        <v>3209.540238665419</v>
+        <v>3157.552073914573</v>
       </c>
       <c r="E46">
-        <v>942.0959999999995</v>
+        <v>997.3799999999997</v>
       </c>
       <c r="F46">
-        <v>2432.496</v>
+        <v>2487.78</v>
       </c>
       <c r="G46">
         <v>465.6</v>
@@ -5065,37 +5065,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M46">
-        <v>402.9611774704686</v>
+        <v>412.1193860493429</v>
       </c>
       <c r="N46">
-        <v>-10.0468917561829</v>
+        <v>-19.20510033505718</v>
       </c>
       <c r="O46">
-        <v>-3.01406752685487</v>
+        <v>-5.761530100517154</v>
       </c>
       <c r="P46">
-        <v>-7.032824229328032</v>
+        <v>-13.44357023454003</v>
       </c>
       <c r="Q46">
-        <v>30.76717577067198</v>
+        <v>24.35642976545999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1196944914763165</v>
+        <v>0.1210380276849768</v>
       </c>
       <c r="T46">
-        <v>1.075254888679859</v>
+        <v>1.094804977564947</v>
       </c>
       <c r="U46">
         <v>0.1656574882221671</v>
       </c>
       <c r="V46">
-        <v>0.2925202036936281</v>
+        <v>0.2860197547226586</v>
       </c>
       <c r="W46">
-        <v>0.117199326024044</v>
+        <v>0.1182761740728912</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9750673456454271</v>
+        <v>0.9533991824088621</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1197951935595383</v>
+        <v>0.1209937684417599</v>
       </c>
       <c r="C47">
-        <v>1135.372073914573</v>
+        <v>1029.757272791974</v>
       </c>
       <c r="D47">
-        <v>3157.552073914573</v>
+        <v>3107.221272791974</v>
       </c>
       <c r="E47">
-        <v>997.3799999999997</v>
+        <v>1052.664</v>
       </c>
       <c r="F47">
-        <v>2487.78</v>
+        <v>2543.064</v>
       </c>
       <c r="G47">
         <v>465.6</v>
@@ -5147,37 +5147,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M47">
-        <v>412.1193860493429</v>
+        <v>421.2775946282172</v>
       </c>
       <c r="N47">
-        <v>-19.20510033505718</v>
+        <v>-28.36330891393152</v>
       </c>
       <c r="O47">
-        <v>-5.761530100517154</v>
+        <v>-8.508992674179455</v>
       </c>
       <c r="P47">
-        <v>-13.44357023454003</v>
+        <v>-19.85431623975207</v>
       </c>
       <c r="Q47">
-        <v>24.35642976545999</v>
+        <v>17.94568376024795</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1210380276849768</v>
+        <v>0.1224313244939578</v>
       </c>
       <c r="T47">
-        <v>1.094804977564947</v>
+        <v>1.11507914381615</v>
       </c>
       <c r="U47">
         <v>0.1656574882221671</v>
       </c>
       <c r="V47">
-        <v>0.2860197547226586</v>
+        <v>0.2798019339678182</v>
       </c>
       <c r="W47">
-        <v>0.1182761740728912</v>
+        <v>0.1193062026413537</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9533991824088621</v>
+        <v>0.9326731132260606</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1209937684417599</v>
+        <v>0.1221923433239816</v>
       </c>
       <c r="C48">
-        <v>1029.757272791974</v>
+        <v>925.7218245574468</v>
       </c>
       <c r="D48">
-        <v>3107.221272791974</v>
+        <v>3058.469824557447</v>
       </c>
       <c r="E48">
-        <v>1052.664</v>
+        <v>1107.948</v>
       </c>
       <c r="F48">
-        <v>2543.064</v>
+        <v>2598.348</v>
       </c>
       <c r="G48">
         <v>465.6</v>
@@ -5229,37 +5229,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M48">
-        <v>421.2775946282172</v>
+        <v>430.4358032070915</v>
       </c>
       <c r="N48">
-        <v>-28.36330891393152</v>
+        <v>-37.5215174928058</v>
       </c>
       <c r="O48">
-        <v>-8.508992674179455</v>
+        <v>-11.25645524784174</v>
       </c>
       <c r="P48">
-        <v>-19.85431623975207</v>
+        <v>-26.26506224496406</v>
       </c>
       <c r="Q48">
-        <v>17.94568376024795</v>
+        <v>11.53493775503595</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1224313244939578</v>
+        <v>0.1238771985410136</v>
       </c>
       <c r="T48">
-        <v>1.11507914381615</v>
+        <v>1.136118372944756</v>
       </c>
       <c r="U48">
         <v>0.1656574882221671</v>
       </c>
       <c r="V48">
-        <v>0.2798019339678182</v>
+        <v>0.2738487013302051</v>
       </c>
       <c r="W48">
-        <v>0.1193062026413537</v>
+        <v>0.1202924002069029</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9326731132260606</v>
+        <v>0.9128290044340168</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1221923433239816</v>
+        <v>0.1233909182062033</v>
       </c>
       <c r="C49">
-        <v>925.7218245574468</v>
+        <v>823.1925387109068</v>
       </c>
       <c r="D49">
-        <v>3058.469824557447</v>
+        <v>3011.224538710907</v>
       </c>
       <c r="E49">
-        <v>1107.948</v>
+        <v>1163.232</v>
       </c>
       <c r="F49">
-        <v>2598.348</v>
+        <v>2653.632</v>
       </c>
       <c r="G49">
         <v>465.6</v>
@@ -5311,37 +5311,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M49">
-        <v>430.4358032070915</v>
+        <v>439.5940117859658</v>
       </c>
       <c r="N49">
-        <v>-37.5215174928058</v>
+        <v>-46.67972607168014</v>
       </c>
       <c r="O49">
-        <v>-11.25645524784174</v>
+        <v>-14.00391782150404</v>
       </c>
       <c r="P49">
-        <v>-26.26506224496406</v>
+        <v>-32.6758082501761</v>
       </c>
       <c r="Q49">
-        <v>11.53493775503595</v>
+        <v>5.124191749823915</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1238771985410136</v>
+        <v>0.1253786831283408</v>
       </c>
       <c r="T49">
-        <v>1.136118372944756</v>
+        <v>1.157966803193694</v>
       </c>
       <c r="U49">
         <v>0.1656574882221671</v>
       </c>
       <c r="V49">
-        <v>0.2738487013302051</v>
+        <v>0.2681435200524924</v>
       </c>
       <c r="W49">
-        <v>0.1202924002069029</v>
+        <v>0.1212375062072209</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.9128290044340168</v>
+        <v>0.893811733508308</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1233909182062033</v>
+        <v>0.1245894930884249</v>
       </c>
       <c r="C50">
-        <v>823.1925387109086</v>
+        <v>722.1006783560019</v>
       </c>
       <c r="D50">
-        <v>3011.224538710908</v>
+        <v>2965.416678356002</v>
       </c>
       <c r="E50">
-        <v>1163.232</v>
+        <v>1218.516</v>
       </c>
       <c r="F50">
-        <v>2653.632</v>
+        <v>2708.916</v>
       </c>
       <c r="G50">
         <v>465.6</v>
@@ -5393,37 +5393,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M50">
-        <v>439.5940117859657</v>
+        <v>448.7522203648401</v>
       </c>
       <c r="N50">
-        <v>-46.67972607168002</v>
+        <v>-55.83793465055436</v>
       </c>
       <c r="O50">
-        <v>-14.00391782150401</v>
+        <v>-16.75138039516631</v>
       </c>
       <c r="P50">
-        <v>-32.67580825017602</v>
+        <v>-39.08655425538805</v>
       </c>
       <c r="Q50">
-        <v>5.124191749823993</v>
+        <v>-1.28655425538804</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1253786831283408</v>
+        <v>0.1269390494641906</v>
       </c>
       <c r="T50">
-        <v>1.157966803193694</v>
+        <v>1.180672034628864</v>
       </c>
       <c r="U50">
         <v>0.1656574882221671</v>
       </c>
       <c r="V50">
-        <v>0.2681435200524925</v>
+        <v>0.2626712033167273</v>
       </c>
       <c r="W50">
-        <v>0.1212375062072209</v>
+        <v>0.1221440364524239</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8938117335083082</v>
+        <v>0.8755706777224243</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1245894930884249</v>
+        <v>0.1257880679706466</v>
       </c>
       <c r="C51">
-        <v>722.1006783560019</v>
+        <v>622.3816265267333</v>
       </c>
       <c r="D51">
-        <v>2965.416678356002</v>
+        <v>2920.981626526733</v>
       </c>
       <c r="E51">
-        <v>1218.516</v>
+        <v>1273.8</v>
       </c>
       <c r="F51">
-        <v>2708.916</v>
+        <v>2764.2</v>
       </c>
       <c r="G51">
         <v>465.6</v>
@@ -5475,37 +5475,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M51">
-        <v>448.7522203648401</v>
+        <v>457.9104289437144</v>
       </c>
       <c r="N51">
-        <v>-55.83793465055436</v>
+        <v>-64.99614322942864</v>
       </c>
       <c r="O51">
-        <v>-16.75138039516631</v>
+        <v>-19.49884296882859</v>
       </c>
       <c r="P51">
-        <v>-39.08655425538805</v>
+        <v>-45.49730026060005</v>
       </c>
       <c r="Q51">
-        <v>-1.28655425538804</v>
+        <v>-7.697300260600038</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1269390494641906</v>
+        <v>0.1285618304534745</v>
       </c>
       <c r="T51">
-        <v>1.180672034628864</v>
+        <v>1.204285475321441</v>
       </c>
       <c r="U51">
         <v>0.1656574882221671</v>
       </c>
       <c r="V51">
-        <v>0.2626712033167273</v>
+        <v>0.2574177792503927</v>
       </c>
       <c r="W51">
-        <v>0.1221440364524239</v>
+        <v>0.1230143054878188</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8755706777224243</v>
+        <v>0.8580592641679758</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1257880679706466</v>
+        <v>0.1269866428528683</v>
       </c>
       <c r="C52">
-        <v>622.3816265267333</v>
+        <v>523.9745820706298</v>
       </c>
       <c r="D52">
-        <v>2920.981626526733</v>
+        <v>2877.85858207063</v>
       </c>
       <c r="E52">
-        <v>1273.8</v>
+        <v>1329.084</v>
       </c>
       <c r="F52">
-        <v>2764.2</v>
+        <v>2819.484</v>
       </c>
       <c r="G52">
         <v>465.6</v>
@@ -5557,37 +5557,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M52">
-        <v>457.9104289437144</v>
+        <v>467.0686375225887</v>
       </c>
       <c r="N52">
-        <v>-64.99614322942864</v>
+        <v>-74.15435180830298</v>
       </c>
       <c r="O52">
-        <v>-19.49884296882859</v>
+        <v>-22.24630554249089</v>
       </c>
       <c r="P52">
-        <v>-45.49730026060005</v>
+        <v>-51.90804626581209</v>
       </c>
       <c r="Q52">
-        <v>-7.697300260600038</v>
+        <v>-14.10804626581208</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1285618304534745</v>
+        <v>0.1302508474015046</v>
       </c>
       <c r="T52">
-        <v>1.204285475321441</v>
+        <v>1.228862729919838</v>
       </c>
       <c r="U52">
         <v>0.1656574882221671</v>
       </c>
       <c r="V52">
-        <v>0.2574177792503927</v>
+        <v>0.2523703718141105</v>
       </c>
       <c r="W52">
-        <v>0.1230143054878188</v>
+        <v>0.1238504463257472</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8580592641679758</v>
+        <v>0.8412345727137017</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1269866428528683</v>
+        <v>0.12818521773509</v>
       </c>
       <c r="C53">
-        <v>523.9745820706298</v>
+        <v>426.8222820784254</v>
       </c>
       <c r="D53">
-        <v>2877.85858207063</v>
+        <v>2835.990282078425</v>
       </c>
       <c r="E53">
-        <v>1329.084</v>
+        <v>1384.368</v>
       </c>
       <c r="F53">
-        <v>2819.484</v>
+        <v>2874.768</v>
       </c>
       <c r="G53">
         <v>465.6</v>
@@ -5639,37 +5639,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M53">
-        <v>467.0686375225887</v>
+        <v>476.226846101463</v>
       </c>
       <c r="N53">
-        <v>-74.15435180830298</v>
+        <v>-83.31256038717726</v>
       </c>
       <c r="O53">
-        <v>-22.24630554249089</v>
+        <v>-24.99376811615318</v>
       </c>
       <c r="P53">
-        <v>-51.90804626581209</v>
+        <v>-58.31879227102408</v>
       </c>
       <c r="Q53">
-        <v>-14.10804626581208</v>
+        <v>-20.51879227102407</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1302508474015046</v>
+        <v>0.1320102400557026</v>
       </c>
       <c r="T53">
-        <v>1.228862729919838</v>
+        <v>1.254464036793168</v>
       </c>
       <c r="U53">
         <v>0.1656574882221671</v>
       </c>
       <c r="V53">
-        <v>0.2523703718141105</v>
+        <v>0.2475170954330699</v>
       </c>
       <c r="W53">
-        <v>0.1238504463257472</v>
+        <v>0.1246544279006783</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8412345727137017</v>
+        <v>0.8250569847768998</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.12818521773509</v>
+        <v>0.1293837926173116</v>
       </c>
       <c r="C54">
-        <v>426.8222820784254</v>
+        <v>330.8707481955466</v>
       </c>
       <c r="D54">
-        <v>2835.990282078425</v>
+        <v>2795.322748195547</v>
       </c>
       <c r="E54">
-        <v>1384.368</v>
+        <v>1439.652</v>
       </c>
       <c r="F54">
-        <v>2874.768</v>
+        <v>2930.052</v>
       </c>
       <c r="G54">
         <v>465.6</v>
@@ -5721,37 +5721,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M54">
-        <v>476.226846101463</v>
+        <v>485.3850546803373</v>
       </c>
       <c r="N54">
-        <v>-83.31256038717726</v>
+        <v>-92.47076896605159</v>
       </c>
       <c r="O54">
-        <v>-24.99376811615318</v>
+        <v>-27.74123068981548</v>
       </c>
       <c r="P54">
-        <v>-58.31879227102408</v>
+        <v>-64.72953827623611</v>
       </c>
       <c r="Q54">
-        <v>-20.51879227102407</v>
+        <v>-26.9295382762361</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1320102400557026</v>
+        <v>0.1338445004824196</v>
       </c>
       <c r="T54">
-        <v>1.254464036793168</v>
+        <v>1.281154760980257</v>
       </c>
       <c r="U54">
         <v>0.1656574882221671</v>
       </c>
       <c r="V54">
-        <v>0.2475170954330699</v>
+        <v>0.2428469615569742</v>
       </c>
       <c r="W54">
-        <v>0.1246544279006783</v>
+        <v>0.1254280705482536</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8250569847768998</v>
+        <v>0.8094898718565808</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1293837926173116</v>
+        <v>0.1612451395150766</v>
       </c>
       <c r="C55">
-        <v>330.8707481955466</v>
+        <v>-495.8857290830724</v>
       </c>
       <c r="D55">
-        <v>2795.322748195547</v>
+        <v>2023.850270916927</v>
       </c>
       <c r="E55">
-        <v>1439.652</v>
+        <v>1494.936</v>
       </c>
       <c r="F55">
-        <v>2930.052</v>
+        <v>2985.336</v>
       </c>
       <c r="G55">
         <v>465.6</v>
@@ -5803,45 +5803,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M55">
-        <v>485.3850546803373</v>
+        <v>655.7514072592115</v>
       </c>
       <c r="N55">
-        <v>-92.47076896605159</v>
+        <v>-262.8371215449258</v>
       </c>
       <c r="O55">
-        <v>-27.74123068981548</v>
+        <v>-78.85113646347774</v>
       </c>
       <c r="P55">
-        <v>-64.72953827623611</v>
+        <v>-183.9859850814481</v>
       </c>
       <c r="Q55">
-        <v>-26.9295382762361</v>
+        <v>-146.1859850814481</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1338445004824196</v>
+        <v>0.1390254070484359</v>
       </c>
       <c r="T55">
-        <v>1.281154760980257</v>
+        <v>1.356543264258447</v>
       </c>
       <c r="U55">
-        <v>0.1656574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V55">
-        <v>0.2428469615569742</v>
+        <v>0.1797545295509999</v>
       </c>
       <c r="W55">
-        <v>0.1254280705482536</v>
+        <v>0.1801730597644372</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8094898718565808</v>
+        <v>0.5991817651699997</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1612451395150766</v>
+        <v>0.1629837143972983</v>
       </c>
       <c r="C56">
-        <v>-495.8857290830724</v>
+        <v>-581.1962158222127</v>
       </c>
       <c r="D56">
-        <v>2023.850270916927</v>
+        <v>1993.823784177787</v>
       </c>
       <c r="E56">
-        <v>1494.936</v>
+        <v>1550.22</v>
       </c>
       <c r="F56">
-        <v>2985.336</v>
+        <v>3040.62</v>
       </c>
       <c r="G56">
         <v>465.6</v>
@@ -5885,37 +5885,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M56">
-        <v>655.7514072592115</v>
+        <v>667.8949518380858</v>
       </c>
       <c r="N56">
-        <v>-262.8371215449258</v>
+        <v>-274.9806661238001</v>
       </c>
       <c r="O56">
-        <v>-78.85113646347774</v>
+        <v>-82.49419983714003</v>
       </c>
       <c r="P56">
-        <v>-183.9859850814481</v>
+        <v>-192.4864662866601</v>
       </c>
       <c r="Q56">
-        <v>-146.1859850814481</v>
+        <v>-154.6864662866601</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1390254070484359</v>
+        <v>0.1410970827606233</v>
       </c>
       <c r="T56">
-        <v>1.356543264258447</v>
+        <v>1.386688670130857</v>
       </c>
       <c r="U56">
         <v>0.2196574882221671</v>
       </c>
       <c r="V56">
-        <v>0.1797545295509999</v>
+        <v>0.1764862653773454</v>
       </c>
       <c r="W56">
-        <v>0.1801730597644372</v>
+        <v>0.1808909584636686</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5991817651699997</v>
+        <v>0.5882875512578178</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1629837143972983</v>
+        <v>0.1647222892795199</v>
       </c>
       <c r="C57">
-        <v>-581.1962158222127</v>
+        <v>-665.6287629259446</v>
       </c>
       <c r="D57">
-        <v>1993.823784177787</v>
+        <v>1964.675237074056</v>
       </c>
       <c r="E57">
-        <v>1550.22</v>
+        <v>1605.504</v>
       </c>
       <c r="F57">
-        <v>3040.62</v>
+        <v>3095.904</v>
       </c>
       <c r="G57">
         <v>465.6</v>
@@ -5967,37 +5967,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M57">
-        <v>667.8949518380858</v>
+        <v>680.0384964169601</v>
       </c>
       <c r="N57">
-        <v>-274.9806661238001</v>
+        <v>-287.1242107026744</v>
       </c>
       <c r="O57">
-        <v>-82.49419983714003</v>
+        <v>-86.13726321080232</v>
       </c>
       <c r="P57">
-        <v>-192.4864662866601</v>
+        <v>-200.9869474918721</v>
       </c>
       <c r="Q57">
-        <v>-154.6864662866601</v>
+        <v>-163.1869474918721</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1410970827606233</v>
+        <v>0.1432629255506375</v>
       </c>
       <c r="T57">
-        <v>1.386688670130857</v>
+        <v>1.418204321724741</v>
       </c>
       <c r="U57">
         <v>0.2196574882221671</v>
       </c>
       <c r="V57">
-        <v>0.1764862653773454</v>
+        <v>0.1733347249241785</v>
       </c>
       <c r="W57">
-        <v>0.1808909584636686</v>
+        <v>0.1815832179236418</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5882875512578178</v>
+        <v>0.5777824164139282</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1647222892795199</v>
+        <v>0.1664608641617416</v>
       </c>
       <c r="C58">
-        <v>-665.6287629259446</v>
+        <v>-749.2213204904019</v>
       </c>
       <c r="D58">
-        <v>1964.675237074056</v>
+        <v>1936.366679509598</v>
       </c>
       <c r="E58">
-        <v>1605.504</v>
+        <v>1660.788</v>
       </c>
       <c r="F58">
-        <v>3095.904</v>
+        <v>3151.188</v>
       </c>
       <c r="G58">
         <v>465.6</v>
@@ -6049,37 +6049,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M58">
-        <v>680.0384964169601</v>
+        <v>692.1820409958344</v>
       </c>
       <c r="N58">
-        <v>-287.1242107026744</v>
+        <v>-299.2677552815487</v>
       </c>
       <c r="O58">
-        <v>-86.13726321080232</v>
+        <v>-89.78032658446462</v>
       </c>
       <c r="P58">
-        <v>-200.9869474918721</v>
+        <v>-209.4874286970841</v>
       </c>
       <c r="Q58">
-        <v>-163.1869474918721</v>
+        <v>-171.6874286970841</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1432629255506375</v>
+        <v>0.1455295052146058</v>
       </c>
       <c r="T58">
-        <v>1.418204321724741</v>
+        <v>1.451185817578805</v>
       </c>
       <c r="U58">
         <v>0.2196574882221671</v>
       </c>
       <c r="V58">
-        <v>0.1733347249241785</v>
+        <v>0.1702937648377894</v>
       </c>
       <c r="W58">
-        <v>0.1815832179236418</v>
+        <v>0.1822511875780019</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5777824164139282</v>
+        <v>0.5676458827926312</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1664608641617416</v>
+        <v>0.1681994390439633</v>
       </c>
       <c r="C59">
-        <v>-749.2213204904019</v>
+        <v>-832.0096824226266</v>
       </c>
       <c r="D59">
-        <v>1936.366679509598</v>
+        <v>1908.862317577374</v>
       </c>
       <c r="E59">
-        <v>1660.788</v>
+        <v>1716.072</v>
       </c>
       <c r="F59">
-        <v>3151.188</v>
+        <v>3206.472</v>
       </c>
       <c r="G59">
         <v>465.6</v>
@@ -6131,37 +6131,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M59">
-        <v>692.1820409958344</v>
+        <v>704.3255855747087</v>
       </c>
       <c r="N59">
-        <v>-299.2677552815487</v>
+        <v>-311.411299860423</v>
       </c>
       <c r="O59">
-        <v>-89.78032658446462</v>
+        <v>-93.4233899581269</v>
       </c>
       <c r="P59">
-        <v>-209.4874286970841</v>
+        <v>-217.9879099022961</v>
       </c>
       <c r="Q59">
-        <v>-171.6874286970841</v>
+        <v>-180.1879099022961</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1455295052146058</v>
+        <v>0.147904017243525</v>
       </c>
       <c r="T59">
-        <v>1.451185817578805</v>
+        <v>1.48573786085449</v>
       </c>
       <c r="U59">
         <v>0.2196574882221671</v>
       </c>
       <c r="V59">
-        <v>0.1702937648377894</v>
+        <v>0.1673576654440344</v>
       </c>
       <c r="W59">
-        <v>0.1822511875780019</v>
+        <v>0.1828961237960048</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5676458827926312</v>
+        <v>0.557858884813448</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1681994390439632</v>
+        <v>0.1699380139261849</v>
       </c>
       <c r="C60">
-        <v>-832.0096824226248</v>
+        <v>-914.0276374296132</v>
       </c>
       <c r="D60">
-        <v>1908.862317577375</v>
+        <v>1882.128362570386</v>
       </c>
       <c r="E60">
-        <v>1716.072</v>
+        <v>1771.355999999999</v>
       </c>
       <c r="F60">
-        <v>3206.472</v>
+        <v>3261.755999999999</v>
       </c>
       <c r="G60">
         <v>465.6</v>
@@ -6213,37 +6213,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M60">
-        <v>704.3255855747086</v>
+        <v>716.4691301535828</v>
       </c>
       <c r="N60">
-        <v>-311.4112998604229</v>
+        <v>-323.5548444392971</v>
       </c>
       <c r="O60">
-        <v>-93.42338995812686</v>
+        <v>-97.06645333178912</v>
       </c>
       <c r="P60">
-        <v>-217.9879099022961</v>
+        <v>-226.488391107508</v>
       </c>
       <c r="Q60">
-        <v>-180.187909902296</v>
+        <v>-188.688391107508</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1479040172435249</v>
+        <v>0.1503943591275134</v>
       </c>
       <c r="T60">
-        <v>1.48573786085449</v>
+        <v>1.521975369655819</v>
       </c>
       <c r="U60">
         <v>0.2196574882221671</v>
       </c>
       <c r="V60">
-        <v>0.1673576654440344</v>
+        <v>0.1645210948432881</v>
       </c>
       <c r="W60">
-        <v>0.1828961237960048</v>
+        <v>0.1835191977693295</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.557858884813448</v>
+        <v>0.548403649477627</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1699380139261849</v>
+        <v>0.1716765888084066</v>
       </c>
       <c r="C61">
-        <v>-914.0276374296132</v>
+        <v>-995.3071074948402</v>
       </c>
       <c r="D61">
-        <v>1882.128362570386</v>
+        <v>1856.132892505159</v>
       </c>
       <c r="E61">
-        <v>1771.355999999999</v>
+        <v>1826.639999999999</v>
       </c>
       <c r="F61">
-        <v>3261.755999999999</v>
+        <v>3317.04</v>
       </c>
       <c r="G61">
         <v>465.6</v>
@@ -6295,37 +6295,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M61">
-        <v>716.4691301535828</v>
+        <v>728.6126747324571</v>
       </c>
       <c r="N61">
-        <v>-323.5548444392971</v>
+        <v>-335.6983890181714</v>
       </c>
       <c r="O61">
-        <v>-97.06645333178912</v>
+        <v>-100.7095167054514</v>
       </c>
       <c r="P61">
-        <v>-226.488391107508</v>
+        <v>-234.98887231272</v>
       </c>
       <c r="Q61">
-        <v>-188.688391107508</v>
+        <v>-197.18887231272</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1503943591275134</v>
+        <v>0.1530092181057012</v>
       </c>
       <c r="T61">
-        <v>1.521975369655819</v>
+        <v>1.560024753897214</v>
       </c>
       <c r="U61">
         <v>0.2196574882221671</v>
       </c>
       <c r="V61">
-        <v>0.1645210948432881</v>
+        <v>0.1617790765958999</v>
       </c>
       <c r="W61">
-        <v>0.1835191977693295</v>
+        <v>0.1841215026102102</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.548403649477627</v>
+        <v>0.5392635886529998</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1716765888084066</v>
+        <v>0.1734151636906283</v>
       </c>
       <c r="C62">
-        <v>-995.3071074948402</v>
+        <v>-1075.87827503551</v>
       </c>
       <c r="D62">
-        <v>1856.132892505159</v>
+        <v>1830.845724964489</v>
       </c>
       <c r="E62">
-        <v>1826.639999999999</v>
+        <v>1881.924</v>
       </c>
       <c r="F62">
-        <v>3317.04</v>
+        <v>3372.324</v>
       </c>
       <c r="G62">
         <v>465.6</v>
@@ -6377,37 +6377,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M62">
-        <v>728.6126747324571</v>
+        <v>740.7562193113315</v>
       </c>
       <c r="N62">
-        <v>-335.6983890181714</v>
+        <v>-347.8419335970458</v>
       </c>
       <c r="O62">
-        <v>-100.7095167054514</v>
+        <v>-104.3525800791137</v>
       </c>
       <c r="P62">
-        <v>-234.98887231272</v>
+        <v>-243.489353517932</v>
       </c>
       <c r="Q62">
-        <v>-197.18887231272</v>
+        <v>-205.689353517932</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1530092181057012</v>
+        <v>0.1557581724161038</v>
       </c>
       <c r="T62">
-        <v>1.560024753897214</v>
+        <v>1.600025388612528</v>
       </c>
       <c r="U62">
         <v>0.2196574882221671</v>
       </c>
       <c r="V62">
-        <v>0.1617790765958999</v>
+        <v>0.1591269605861311</v>
       </c>
       <c r="W62">
-        <v>0.1841215026102102</v>
+        <v>0.1847040597513898</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5392635886529998</v>
+        <v>0.5304232019537702</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1734151636906283</v>
+        <v>0.1751537385728499</v>
       </c>
       <c r="C63">
-        <v>-1075.87827503551</v>
+        <v>-1155.769699805484</v>
       </c>
       <c r="D63">
-        <v>1830.845724964489</v>
+        <v>1806.238300194516</v>
       </c>
       <c r="E63">
-        <v>1881.924</v>
+        <v>1937.208</v>
       </c>
       <c r="F63">
-        <v>3372.324</v>
+        <v>3427.608</v>
       </c>
       <c r="G63">
         <v>465.6</v>
@@ -6459,37 +6459,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M63">
-        <v>740.7562193113315</v>
+        <v>752.8997638902058</v>
       </c>
       <c r="N63">
-        <v>-347.8419335970458</v>
+        <v>-359.9854781759201</v>
       </c>
       <c r="O63">
-        <v>-104.3525800791137</v>
+        <v>-107.995643452776</v>
       </c>
       <c r="P63">
-        <v>-243.489353517932</v>
+        <v>-251.9898347231441</v>
       </c>
       <c r="Q63">
-        <v>-205.689353517932</v>
+        <v>-214.1898347231441</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1557581724161038</v>
+        <v>0.1586518085323171</v>
       </c>
       <c r="T63">
-        <v>1.600025388612528</v>
+        <v>1.642131319891805</v>
       </c>
       <c r="U63">
         <v>0.2196574882221671</v>
       </c>
       <c r="V63">
-        <v>0.1591269605861311</v>
+        <v>0.1565603967057096</v>
       </c>
       <c r="W63">
-        <v>0.1847040597513898</v>
+        <v>0.1852678247267249</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5304232019537702</v>
+        <v>0.5218679890190321</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1751537385728499</v>
+        <v>0.1768923134550716</v>
       </c>
       <c r="C64">
-        <v>-1155.769699805484</v>
+        <v>-1235.008426495857</v>
       </c>
       <c r="D64">
-        <v>1806.238300194516</v>
+        <v>1782.283573504142</v>
       </c>
       <c r="E64">
-        <v>1937.208</v>
+        <v>1992.492</v>
       </c>
       <c r="F64">
-        <v>3427.608</v>
+        <v>3482.892</v>
       </c>
       <c r="G64">
         <v>465.6</v>
@@ -6541,37 +6541,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M64">
-        <v>752.8997638902058</v>
+        <v>765.0433084690801</v>
       </c>
       <c r="N64">
-        <v>-359.9854781759201</v>
+        <v>-372.1290227547944</v>
       </c>
       <c r="O64">
-        <v>-107.995643452776</v>
+        <v>-111.6387068264383</v>
       </c>
       <c r="P64">
-        <v>-251.9898347231441</v>
+        <v>-260.4903159283561</v>
       </c>
       <c r="Q64">
-        <v>-214.1898347231441</v>
+        <v>-222.6903159283561</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1586518085323171</v>
+        <v>0.1617018574115689</v>
       </c>
       <c r="T64">
-        <v>1.642131319891805</v>
+        <v>1.686513247456448</v>
       </c>
       <c r="U64">
         <v>0.2196574882221671</v>
       </c>
       <c r="V64">
-        <v>0.1565603967057096</v>
+        <v>0.1540753110437142</v>
       </c>
       <c r="W64">
-        <v>0.1852678247267249</v>
+        <v>0.1858136924012558</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5218679890190321</v>
+        <v>0.513584370145714</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1768923134550716</v>
+        <v>0.1786308883372933</v>
       </c>
       <c r="C65">
-        <v>-1235.008426495857</v>
+        <v>-1313.620083885472</v>
       </c>
       <c r="D65">
-        <v>1782.283573504142</v>
+        <v>1758.955916114528</v>
       </c>
       <c r="E65">
-        <v>1992.492</v>
+        <v>2047.776</v>
       </c>
       <c r="F65">
-        <v>3482.892</v>
+        <v>3538.176</v>
       </c>
       <c r="G65">
         <v>465.6</v>
@@ -6623,37 +6623,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M65">
-        <v>765.0433084690801</v>
+        <v>777.1868530479544</v>
       </c>
       <c r="N65">
-        <v>-372.1290227547944</v>
+        <v>-384.2725673336687</v>
       </c>
       <c r="O65">
-        <v>-111.6387068264383</v>
+        <v>-115.2817702001006</v>
       </c>
       <c r="P65">
-        <v>-260.4903159283561</v>
+        <v>-268.9907971335681</v>
       </c>
       <c r="Q65">
-        <v>-222.6903159283561</v>
+        <v>-231.1907971335681</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1617018574115689</v>
+        <v>0.1649213534507792</v>
       </c>
       <c r="T65">
-        <v>1.686513247456448</v>
+        <v>1.733360837663572</v>
       </c>
       <c r="U65">
         <v>0.2196574882221671</v>
       </c>
       <c r="V65">
-        <v>0.1540753110437142</v>
+        <v>0.1516678843086562</v>
       </c>
       <c r="W65">
-        <v>0.1858136924012558</v>
+        <v>0.1863425017109575</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.513584370145714</v>
+        <v>0.5055596143621872</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1786308883372933</v>
+        <v>0.2037530731926974</v>
       </c>
       <c r="C66">
-        <v>-1313.620083885472</v>
+        <v>-1648.663222368502</v>
       </c>
       <c r="D66">
-        <v>1758.955916114528</v>
+        <v>1479.196777631498</v>
       </c>
       <c r="E66">
-        <v>2047.776</v>
+        <v>2103.06</v>
       </c>
       <c r="F66">
-        <v>3538.176</v>
+        <v>3593.46</v>
       </c>
       <c r="G66">
         <v>465.6</v>
@@ -6705,45 +6705,45 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M66">
-        <v>777.1868530479544</v>
+        <v>915.1014976268286</v>
       </c>
       <c r="N66">
-        <v>-384.2725673336687</v>
+        <v>-522.1872119125429</v>
       </c>
       <c r="O66">
-        <v>-115.2817702001006</v>
+        <v>-156.6561635737629</v>
       </c>
       <c r="P66">
-        <v>-268.9907971335681</v>
+        <v>-365.53104833878</v>
       </c>
       <c r="Q66">
-        <v>-231.1907971335681</v>
+        <v>-327.73104833878</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1649213534507792</v>
+        <v>0.1701351349013228</v>
       </c>
       <c r="T66">
-        <v>1.733360837663572</v>
+        <v>1.809227710568466</v>
       </c>
       <c r="U66">
-        <v>0.2196574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V66">
-        <v>0.1516678843086562</v>
+        <v>0.1288100675389277</v>
       </c>
       <c r="W66">
-        <v>0.1863425017109575</v>
+        <v>0.221855039964976</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.5055596143621872</v>
+        <v>0.4293668917964257</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2037530731926974</v>
+        <v>0.2058416480749191</v>
       </c>
       <c r="C67">
-        <v>-1648.663222368502</v>
+        <v>-1723.251030300911</v>
       </c>
       <c r="D67">
-        <v>1479.196777631498</v>
+        <v>1459.892969699089</v>
       </c>
       <c r="E67">
-        <v>2103.06</v>
+        <v>2158.344</v>
       </c>
       <c r="F67">
-        <v>3593.46</v>
+        <v>3648.744</v>
       </c>
       <c r="G67">
         <v>465.6</v>
@@ -6787,37 +6787,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M67">
-        <v>915.1014976268286</v>
+        <v>929.1799822057029</v>
       </c>
       <c r="N67">
-        <v>-522.1872119125429</v>
+        <v>-536.2656964914172</v>
       </c>
       <c r="O67">
-        <v>-156.6561635737629</v>
+        <v>-160.8797089474251</v>
       </c>
       <c r="P67">
-        <v>-365.53104833878</v>
+        <v>-375.3859875439921</v>
       </c>
       <c r="Q67">
-        <v>-327.73104833878</v>
+        <v>-337.5859875439921</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1701351349013228</v>
+        <v>0.1737920506337147</v>
       </c>
       <c r="T67">
-        <v>1.809227710568466</v>
+        <v>1.862440290291067</v>
       </c>
       <c r="U67">
         <v>0.2546574882221671</v>
       </c>
       <c r="V67">
-        <v>0.1288100675389277</v>
+        <v>0.126858399848944</v>
       </c>
       <c r="W67">
-        <v>0.221855039964976</v>
+        <v>0.2223520467567517</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4293668917964257</v>
+        <v>0.4228613328298133</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2058416480749191</v>
+        <v>0.2079302229571408</v>
       </c>
       <c r="C68">
-        <v>-1723.251030300911</v>
+        <v>-1797.341491746729</v>
       </c>
       <c r="D68">
-        <v>1459.892969699089</v>
+        <v>1441.08650825327</v>
       </c>
       <c r="E68">
-        <v>2158.344</v>
+        <v>2213.628</v>
       </c>
       <c r="F68">
-        <v>3648.744</v>
+        <v>3704.028</v>
       </c>
       <c r="G68">
         <v>465.6</v>
@@ -6869,37 +6869,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M68">
-        <v>929.1799822057029</v>
+        <v>943.2584667845771</v>
       </c>
       <c r="N68">
-        <v>-536.2656964914172</v>
+        <v>-550.3441810702914</v>
       </c>
       <c r="O68">
-        <v>-160.8797089474251</v>
+        <v>-165.1032543210874</v>
       </c>
       <c r="P68">
-        <v>-375.3859875439921</v>
+        <v>-385.2409267492039</v>
       </c>
       <c r="Q68">
-        <v>-337.5859875439921</v>
+        <v>-347.4409267492039</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1737920506337147</v>
+        <v>0.1776705976226151</v>
       </c>
       <c r="T68">
-        <v>1.862440290291067</v>
+        <v>1.918877874845342</v>
       </c>
       <c r="U68">
         <v>0.2546574882221671</v>
       </c>
       <c r="V68">
-        <v>0.126858399848944</v>
+        <v>0.1249649908959747</v>
       </c>
       <c r="W68">
-        <v>0.2223520467567517</v>
+        <v>0.2228342175248922</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4228613328298133</v>
+        <v>0.416549969653249</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2079302229571408</v>
+        <v>0.2100187978393624</v>
       </c>
       <c r="C69">
-        <v>-1797.341491746729</v>
+        <v>-1870.953582829155</v>
       </c>
       <c r="D69">
-        <v>1441.08650825327</v>
+        <v>1422.758417170845</v>
       </c>
       <c r="E69">
-        <v>2213.628</v>
+        <v>2268.912</v>
       </c>
       <c r="F69">
-        <v>3704.028</v>
+        <v>3759.312</v>
       </c>
       <c r="G69">
         <v>465.6</v>
@@ -6951,37 +6951,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M69">
-        <v>943.2584667845771</v>
+        <v>957.3369513634515</v>
       </c>
       <c r="N69">
-        <v>-550.3441810702914</v>
+        <v>-564.4226656491658</v>
       </c>
       <c r="O69">
-        <v>-165.1032543210874</v>
+        <v>-169.3267996947497</v>
       </c>
       <c r="P69">
-        <v>-385.2409267492039</v>
+        <v>-395.095865954416</v>
       </c>
       <c r="Q69">
-        <v>-347.4409267492039</v>
+        <v>-357.295865954416</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1776705976226151</v>
+        <v>0.1817915537983218</v>
       </c>
       <c r="T69">
-        <v>1.918877874845342</v>
+        <v>1.978842808434259</v>
       </c>
       <c r="U69">
         <v>0.2546574882221671</v>
       </c>
       <c r="V69">
-        <v>0.1249649908959747</v>
+        <v>0.1231272704416221</v>
       </c>
       <c r="W69">
-        <v>0.2228342175248922</v>
+        <v>0.2233022067998521</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.416549969653249</v>
+        <v>0.410424234805407</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2100187978393624</v>
+        <v>0.2121073727215841</v>
       </c>
       <c r="C70">
-        <v>-1870.953582829155</v>
+        <v>-1944.105326423104</v>
       </c>
       <c r="D70">
-        <v>1422.758417170845</v>
+        <v>1404.890673576896</v>
       </c>
       <c r="E70">
-        <v>2268.912</v>
+        <v>2324.196</v>
       </c>
       <c r="F70">
-        <v>3759.312</v>
+        <v>3814.596</v>
       </c>
       <c r="G70">
         <v>465.6</v>
@@ -7033,37 +7033,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M70">
-        <v>957.3369513634515</v>
+        <v>971.4154359423258</v>
       </c>
       <c r="N70">
-        <v>-564.4226656491658</v>
+        <v>-578.50115022804</v>
       </c>
       <c r="O70">
-        <v>-169.3267996947497</v>
+        <v>-173.550345068412</v>
       </c>
       <c r="P70">
-        <v>-395.095865954416</v>
+        <v>-404.950805159628</v>
       </c>
       <c r="Q70">
-        <v>-357.295865954416</v>
+        <v>-367.150805159628</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1817915537983218</v>
+        <v>0.1861783781143968</v>
       </c>
       <c r="T70">
-        <v>1.978842808434259</v>
+        <v>2.04267644741601</v>
       </c>
       <c r="U70">
         <v>0.2546574882221671</v>
       </c>
       <c r="V70">
-        <v>0.1231272704416221</v>
+        <v>0.121342817246816</v>
       </c>
       <c r="W70">
-        <v>0.2233022067998521</v>
+        <v>0.2237566311682915</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.410424234805407</v>
+        <v>0.4044760574893866</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2121073727215841</v>
+        <v>0.2141959476038058</v>
       </c>
       <c r="C71">
-        <v>-1944.105326423104</v>
+        <v>-2016.813851269769</v>
       </c>
       <c r="D71">
-        <v>1404.890673576896</v>
+        <v>1387.466148730231</v>
       </c>
       <c r="E71">
-        <v>2324.196</v>
+        <v>2379.48</v>
       </c>
       <c r="F71">
-        <v>3814.596</v>
+        <v>3869.88</v>
       </c>
       <c r="G71">
         <v>465.6</v>
@@ -7115,37 +7115,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M71">
-        <v>971.4154359423258</v>
+        <v>985.4939205212</v>
       </c>
       <c r="N71">
-        <v>-578.50115022804</v>
+        <v>-592.5796348069143</v>
       </c>
       <c r="O71">
-        <v>-173.550345068412</v>
+        <v>-177.7738904420743</v>
       </c>
       <c r="P71">
-        <v>-404.950805159628</v>
+        <v>-414.8057443648401</v>
       </c>
       <c r="Q71">
-        <v>-367.150805159628</v>
+        <v>-377.00574436484</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1861783781143968</v>
+        <v>0.1908576573848766</v>
       </c>
       <c r="T71">
-        <v>2.04267644741601</v>
+        <v>2.110765662329877</v>
       </c>
       <c r="U71">
         <v>0.2546574882221671</v>
       </c>
       <c r="V71">
-        <v>0.121342817246816</v>
+        <v>0.1196093484290043</v>
       </c>
       <c r="W71">
-        <v>0.2237566311682915</v>
+        <v>0.2241980719833469</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4044760574893866</v>
+        <v>0.3986978280966811</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2141959476038058</v>
+        <v>0.2162845224860275</v>
       </c>
       <c r="C72">
-        <v>-2016.813851269769</v>
+        <v>-2089.09544674597</v>
       </c>
       <c r="D72">
-        <v>1387.466148730231</v>
+        <v>1370.46855325403</v>
       </c>
       <c r="E72">
-        <v>2379.48</v>
+        <v>2434.764</v>
       </c>
       <c r="F72">
-        <v>3869.88</v>
+        <v>3925.164</v>
       </c>
       <c r="G72">
         <v>465.6</v>
@@ -7197,37 +7197,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M72">
-        <v>985.4939205212</v>
+        <v>999.5724051000744</v>
       </c>
       <c r="N72">
-        <v>-592.5796348069143</v>
+        <v>-606.6581193857887</v>
       </c>
       <c r="O72">
-        <v>-177.7738904420743</v>
+        <v>-181.9974358157366</v>
       </c>
       <c r="P72">
-        <v>-414.8057443648401</v>
+        <v>-424.6606835700521</v>
       </c>
       <c r="Q72">
-        <v>-377.00574436484</v>
+        <v>-386.8606835700521</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1908576573848766</v>
+        <v>0.1958596455705621</v>
       </c>
       <c r="T72">
-        <v>2.110765662329877</v>
+        <v>2.183550685168838</v>
       </c>
       <c r="U72">
         <v>0.2546574882221671</v>
       </c>
       <c r="V72">
-        <v>0.1196093484290043</v>
+        <v>0.1179247097187366</v>
       </c>
       <c r="W72">
-        <v>0.2241980719833469</v>
+        <v>0.2246270778458655</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3986978280966811</v>
+        <v>0.3930823657291221</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2162845224860275</v>
+        <v>0.2183730973682491</v>
       </c>
       <c r="C73">
-        <v>-2089.09544674597</v>
+        <v>-2160.965613656407</v>
       </c>
       <c r="D73">
-        <v>1370.46855325403</v>
+        <v>1353.882386343593</v>
       </c>
       <c r="E73">
-        <v>2434.764</v>
+        <v>2490.047999999999</v>
       </c>
       <c r="F73">
-        <v>3925.164</v>
+        <v>3980.447999999999</v>
       </c>
       <c r="G73">
         <v>465.6</v>
@@ -7279,37 +7279,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M73">
-        <v>999.5724051000742</v>
+        <v>1013.650889678948</v>
       </c>
       <c r="N73">
-        <v>-606.6581193857885</v>
+        <v>-620.7366039646628</v>
       </c>
       <c r="O73">
-        <v>-181.9974358157365</v>
+        <v>-186.2209811893988</v>
       </c>
       <c r="P73">
-        <v>-424.660683570052</v>
+        <v>-434.515622775264</v>
       </c>
       <c r="Q73">
-        <v>-386.8606835700519</v>
+        <v>-396.715622775264</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.195859645570562</v>
+        <v>0.2012189186266535</v>
       </c>
       <c r="T73">
-        <v>2.183550685168837</v>
+        <v>2.261534638210581</v>
       </c>
       <c r="U73">
         <v>0.2546574882221671</v>
       </c>
       <c r="V73">
-        <v>0.1179247097187367</v>
+        <v>0.1162868665281987</v>
       </c>
       <c r="W73">
-        <v>0.2246270778458654</v>
+        <v>0.2250441668788696</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3930823657291223</v>
+        <v>0.3876228884273288</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2183730973682491</v>
+        <v>0.2204616722504708</v>
       </c>
       <c r="C74">
-        <v>-2160.965613656407</v>
+        <v>-2232.439111381727</v>
       </c>
       <c r="D74">
-        <v>1353.882386343593</v>
+        <v>1337.692888618272</v>
       </c>
       <c r="E74">
-        <v>2490.047999999999</v>
+        <v>2545.331999999999</v>
       </c>
       <c r="F74">
-        <v>3980.447999999999</v>
+        <v>4035.732</v>
       </c>
       <c r="G74">
         <v>465.6</v>
@@ -7361,37 +7361,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M74">
-        <v>1013.650889678948</v>
+        <v>1027.729374257823</v>
       </c>
       <c r="N74">
-        <v>-620.7366039646628</v>
+        <v>-634.8150885435372</v>
       </c>
       <c r="O74">
-        <v>-186.2209811893988</v>
+        <v>-190.4445265630611</v>
       </c>
       <c r="P74">
-        <v>-434.515622775264</v>
+        <v>-444.3705619804761</v>
       </c>
       <c r="Q74">
-        <v>-396.715622775264</v>
+        <v>-406.570561980476</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2012189186266535</v>
+        <v>0.2069751748720851</v>
       </c>
       <c r="T74">
-        <v>2.261534638210581</v>
+        <v>2.345295180366529</v>
       </c>
       <c r="U74">
         <v>0.2546574882221671</v>
       </c>
       <c r="V74">
-        <v>0.1162868665281987</v>
+        <v>0.1146938957538398</v>
       </c>
       <c r="W74">
-        <v>0.2250441668788696</v>
+        <v>0.2254498288150792</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3876228884273288</v>
+        <v>0.3823129858461326</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2204616722504708</v>
+        <v>0.2225502471326925</v>
       </c>
       <c r="C75">
-        <v>-2232.439111381727</v>
+        <v>-2303.530001683823</v>
       </c>
       <c r="D75">
-        <v>1337.692888618272</v>
+        <v>1321.885998316177</v>
       </c>
       <c r="E75">
-        <v>2545.331999999999</v>
+        <v>2600.616</v>
       </c>
       <c r="F75">
-        <v>4035.732</v>
+        <v>4091.016</v>
       </c>
       <c r="G75">
         <v>465.6</v>
@@ -7443,37 +7443,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M75">
-        <v>1027.729374257823</v>
+        <v>1041.807858836697</v>
       </c>
       <c r="N75">
-        <v>-634.8150885435372</v>
+        <v>-648.8935731224113</v>
       </c>
       <c r="O75">
-        <v>-190.4445265630611</v>
+        <v>-194.6680719367234</v>
       </c>
       <c r="P75">
-        <v>-444.3705619804761</v>
+        <v>-454.2255011856879</v>
       </c>
       <c r="Q75">
-        <v>-406.570561980476</v>
+        <v>-416.4255011856879</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2069751748720851</v>
+        <v>0.213174220059473</v>
       </c>
       <c r="T75">
-        <v>2.345295180366529</v>
+        <v>2.435498841149857</v>
       </c>
       <c r="U75">
         <v>0.2546574882221671</v>
       </c>
       <c r="V75">
-        <v>0.1146938957538398</v>
+        <v>0.1131439782436527</v>
       </c>
       <c r="W75">
-        <v>0.2254498288150792</v>
+        <v>0.225844526915175</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3823129858461326</v>
+        <v>0.3771465941455092</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2225502471326925</v>
+        <v>0.2246388220149141</v>
       </c>
       <c r="C76">
-        <v>-2303.530001683823</v>
+        <v>-2374.251689441648</v>
       </c>
       <c r="D76">
-        <v>1321.885998316177</v>
+        <v>1306.448310558352</v>
       </c>
       <c r="E76">
-        <v>2600.616</v>
+        <v>2655.899999999999</v>
       </c>
       <c r="F76">
-        <v>4091.016</v>
+        <v>4146.299999999999</v>
       </c>
       <c r="G76">
         <v>465.6</v>
@@ -7525,37 +7525,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M76">
-        <v>1041.807858836697</v>
+        <v>1055.886343415571</v>
       </c>
       <c r="N76">
-        <v>-648.8935731224113</v>
+        <v>-662.9720577012855</v>
       </c>
       <c r="O76">
-        <v>-194.6680719367234</v>
+        <v>-198.8916173103856</v>
       </c>
       <c r="P76">
-        <v>-454.2255011856879</v>
+        <v>-464.0804403908999</v>
       </c>
       <c r="Q76">
-        <v>-416.4255011856879</v>
+        <v>-426.2804403908999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.213174220059473</v>
+        <v>0.2198691888618519</v>
       </c>
       <c r="T76">
-        <v>2.435498841149857</v>
+        <v>2.532918794795851</v>
       </c>
       <c r="U76">
         <v>0.2546574882221671</v>
       </c>
       <c r="V76">
-        <v>0.1131439782436527</v>
+        <v>0.1116353918670707</v>
       </c>
       <c r="W76">
-        <v>0.225844526915175</v>
+        <v>0.2262286997326015</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3771465941455092</v>
+        <v>0.3721179728902357</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2246388220149141</v>
+        <v>0.2267273968971358</v>
       </c>
       <c r="C77">
-        <v>-2374.251689441648</v>
+        <v>-2444.616960565581</v>
       </c>
       <c r="D77">
-        <v>1306.448310558352</v>
+        <v>1291.367039434419</v>
       </c>
       <c r="E77">
-        <v>2655.899999999999</v>
+        <v>2711.184</v>
       </c>
       <c r="F77">
-        <v>4146.299999999999</v>
+        <v>4201.584</v>
       </c>
       <c r="G77">
         <v>465.6</v>
@@ -7607,37 +7607,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M77">
-        <v>1055.886343415571</v>
+        <v>1069.964827994446</v>
       </c>
       <c r="N77">
-        <v>-662.9720577012855</v>
+        <v>-677.0505422801599</v>
       </c>
       <c r="O77">
-        <v>-198.8916173103856</v>
+        <v>-203.115162684048</v>
       </c>
       <c r="P77">
-        <v>-464.0804403908999</v>
+        <v>-473.9353795961119</v>
       </c>
       <c r="Q77">
-        <v>-426.2804403908999</v>
+        <v>-436.1353795961119</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2198691888618519</v>
+        <v>0.2271220717310958</v>
       </c>
       <c r="T77">
-        <v>2.532918794795851</v>
+        <v>2.638457077912345</v>
       </c>
       <c r="U77">
         <v>0.2546574882221671</v>
       </c>
       <c r="V77">
-        <v>0.1116353918670707</v>
+        <v>0.1101665051319777</v>
       </c>
       <c r="W77">
-        <v>0.2262286997326015</v>
+        <v>0.2266027627390432</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3721179728902357</v>
+        <v>0.3672216837732589</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2267273968971358</v>
+        <v>0.2288159717793575</v>
       </c>
       <c r="C78">
-        <v>-2444.616960565581</v>
+        <v>-2514.638017315706</v>
       </c>
       <c r="D78">
-        <v>1291.367039434419</v>
+        <v>1276.629982684294</v>
       </c>
       <c r="E78">
-        <v>2711.184</v>
+        <v>2766.467999999999</v>
       </c>
       <c r="F78">
-        <v>4201.584</v>
+        <v>4256.867999999999</v>
       </c>
       <c r="G78">
         <v>465.6</v>
@@ -7689,37 +7689,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M78">
-        <v>1069.964827994446</v>
+        <v>1084.04331257332</v>
       </c>
       <c r="N78">
-        <v>-677.0505422801599</v>
+        <v>-691.1290268590343</v>
       </c>
       <c r="O78">
-        <v>-203.115162684048</v>
+        <v>-207.3387080577103</v>
       </c>
       <c r="P78">
-        <v>-473.9353795961119</v>
+        <v>-483.790318801324</v>
       </c>
       <c r="Q78">
-        <v>-436.1353795961119</v>
+        <v>-445.990318801324</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2271220717310958</v>
+        <v>0.2350056400672304</v>
       </c>
       <c r="T78">
-        <v>2.638457077912345</v>
+        <v>2.753172603038969</v>
       </c>
       <c r="U78">
         <v>0.2546574882221671</v>
       </c>
       <c r="V78">
-        <v>0.1101665051319777</v>
+        <v>0.1087357712990948</v>
       </c>
       <c r="W78">
-        <v>0.2266027627390432</v>
+        <v>0.2269671098232396</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3672216837732589</v>
+        <v>0.3624525709969828</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2288159717793575</v>
+        <v>0.2309045466615791</v>
       </c>
       <c r="C79">
-        <v>-2514.638017315706</v>
+        <v>-2584.326511229086</v>
       </c>
       <c r="D79">
-        <v>1276.629982684294</v>
+        <v>1262.225488770915</v>
       </c>
       <c r="E79">
-        <v>2766.467999999999</v>
+        <v>2821.752</v>
       </c>
       <c r="F79">
-        <v>4256.867999999999</v>
+        <v>4312.152</v>
       </c>
       <c r="G79">
         <v>465.6</v>
@@ -7771,37 +7771,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M79">
-        <v>1084.04331257332</v>
+        <v>1098.121797152194</v>
       </c>
       <c r="N79">
-        <v>-691.1290268590343</v>
+        <v>-705.2075114379087</v>
       </c>
       <c r="O79">
-        <v>-207.3387080577103</v>
+        <v>-211.5622534313726</v>
       </c>
       <c r="P79">
-        <v>-483.790318801324</v>
+        <v>-493.6452580065361</v>
       </c>
       <c r="Q79">
-        <v>-445.990318801324</v>
+        <v>-455.8452580065361</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2350056400672304</v>
+        <v>0.2436058964339227</v>
       </c>
       <c r="T79">
-        <v>2.753172603038969</v>
+        <v>2.878316812268013</v>
       </c>
       <c r="U79">
         <v>0.2546574882221671</v>
       </c>
       <c r="V79">
-        <v>0.1087357712990948</v>
+        <v>0.1073417229491064</v>
       </c>
       <c r="W79">
-        <v>0.2269671098232396</v>
+        <v>0.2273221146745079</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3624525709969828</v>
+        <v>0.3578057431636882</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2309045466615791</v>
+        <v>0.2329931215438008</v>
       </c>
       <c r="C80">
-        <v>-2584.326511229086</v>
+        <v>-2653.693573842741</v>
       </c>
       <c r="D80">
-        <v>1262.225488770915</v>
+        <v>1248.142426157259</v>
       </c>
       <c r="E80">
-        <v>2821.752</v>
+        <v>2877.036</v>
       </c>
       <c r="F80">
-        <v>4312.152</v>
+        <v>4367.436</v>
       </c>
       <c r="G80">
         <v>465.6</v>
@@ -7853,37 +7853,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M80">
-        <v>1098.121797152194</v>
+        <v>1112.200281731069</v>
       </c>
       <c r="N80">
-        <v>-705.2075114379087</v>
+        <v>-719.2859960167829</v>
       </c>
       <c r="O80">
-        <v>-211.5622534313726</v>
+        <v>-215.7857988050349</v>
       </c>
       <c r="P80">
-        <v>-493.6452580065361</v>
+        <v>-503.500197211748</v>
       </c>
       <c r="Q80">
-        <v>-455.8452580065361</v>
+        <v>-465.700197211748</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2436058964339227</v>
+        <v>0.253025224835538</v>
       </c>
       <c r="T80">
-        <v>2.878316812268013</v>
+        <v>3.015379517614109</v>
       </c>
       <c r="U80">
         <v>0.2546574882221671</v>
       </c>
       <c r="V80">
-        <v>0.1073417229491064</v>
+        <v>0.1059829669624089</v>
       </c>
       <c r="W80">
-        <v>0.2273221146745079</v>
+        <v>0.2276681320611871</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3578057431636882</v>
+        <v>0.353276556541363</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2329931215438008</v>
+        <v>0.2350816964260225</v>
       </c>
       <c r="C81">
-        <v>-2653.693573842741</v>
+        <v>-2722.749845382615</v>
       </c>
       <c r="D81">
-        <v>1248.142426157259</v>
+        <v>1234.370154617385</v>
       </c>
       <c r="E81">
-        <v>2877.036</v>
+        <v>2932.32</v>
       </c>
       <c r="F81">
-        <v>4367.436</v>
+        <v>4422.72</v>
       </c>
       <c r="G81">
         <v>465.6</v>
@@ -7935,37 +7935,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M81">
-        <v>1112.200281731069</v>
+        <v>1126.278766309943</v>
       </c>
       <c r="N81">
-        <v>-719.2859960167829</v>
+        <v>-733.3644805956573</v>
       </c>
       <c r="O81">
-        <v>-215.7857988050349</v>
+        <v>-220.0093441786972</v>
       </c>
       <c r="P81">
-        <v>-503.500197211748</v>
+        <v>-513.35513641696</v>
       </c>
       <c r="Q81">
-        <v>-465.700197211748</v>
+        <v>-475.55513641696</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.253025224835538</v>
+        <v>0.263386486077315</v>
       </c>
       <c r="T81">
-        <v>3.015379517614109</v>
+        <v>3.166148493494815</v>
       </c>
       <c r="U81">
         <v>0.2546574882221671</v>
       </c>
       <c r="V81">
-        <v>0.1059829669624089</v>
+        <v>0.1046581798753788</v>
       </c>
       <c r="W81">
-        <v>0.2276681320611871</v>
+        <v>0.2280054990131994</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.353276556541363</v>
+        <v>0.3488605995845959</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2350816964260225</v>
+        <v>0.2371702713082442</v>
       </c>
       <c r="C82">
-        <v>-2722.749845382615</v>
+        <v>-2791.505501573903</v>
       </c>
       <c r="D82">
-        <v>1234.370154617385</v>
+        <v>1220.898498426097</v>
       </c>
       <c r="E82">
-        <v>2932.32</v>
+        <v>2987.604</v>
       </c>
       <c r="F82">
-        <v>4422.72</v>
+        <v>4478.004</v>
       </c>
       <c r="G82">
         <v>465.6</v>
@@ -8017,37 +8017,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M82">
-        <v>1126.278766309943</v>
+        <v>1140.357250888817</v>
       </c>
       <c r="N82">
-        <v>-733.3644805956573</v>
+        <v>-747.4429651745314</v>
       </c>
       <c r="O82">
-        <v>-220.0093441786972</v>
+        <v>-224.2328895523594</v>
       </c>
       <c r="P82">
-        <v>-513.35513641696</v>
+        <v>-523.210075622172</v>
       </c>
       <c r="Q82">
-        <v>-475.55513641696</v>
+        <v>-485.410075622172</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.263386486077315</v>
+        <v>0.2748384063971736</v>
       </c>
       <c r="T82">
-        <v>3.166148493494815</v>
+        <v>3.332787887889279</v>
       </c>
       <c r="U82">
         <v>0.2546574882221671</v>
       </c>
       <c r="V82">
-        <v>0.1046581798753788</v>
+        <v>0.103366103580621</v>
       </c>
       <c r="W82">
-        <v>0.2280054990131994</v>
+        <v>0.2283345359170138</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3488605995845959</v>
+        <v>0.3445536786020701</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2371702713082442</v>
+        <v>0.2392588461904658</v>
       </c>
       <c r="C83">
-        <v>-2791.505501573903</v>
+        <v>-2859.970278714713</v>
       </c>
       <c r="D83">
-        <v>1220.898498426097</v>
+        <v>1207.717721285287</v>
       </c>
       <c r="E83">
-        <v>2987.604</v>
+        <v>3042.888</v>
       </c>
       <c r="F83">
-        <v>4478.004</v>
+        <v>4533.288</v>
       </c>
       <c r="G83">
         <v>465.6</v>
@@ -8099,37 +8099,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M83">
-        <v>1140.357250888817</v>
+        <v>1154.435735467692</v>
       </c>
       <c r="N83">
-        <v>-747.4429651745314</v>
+        <v>-761.5214497534058</v>
       </c>
       <c r="O83">
-        <v>-224.2328895523594</v>
+        <v>-228.4564349260217</v>
       </c>
       <c r="P83">
-        <v>-523.210075622172</v>
+        <v>-533.0650148273841</v>
       </c>
       <c r="Q83">
-        <v>-485.410075622172</v>
+        <v>-495.2650148273841</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2748384063971736</v>
+        <v>0.2875627623081278</v>
       </c>
       <c r="T83">
-        <v>3.332787887889279</v>
+        <v>3.517942770549795</v>
       </c>
       <c r="U83">
         <v>0.2546574882221671</v>
       </c>
       <c r="V83">
-        <v>0.103366103580621</v>
+        <v>0.102105541341833</v>
       </c>
       <c r="W83">
-        <v>0.2283345359170138</v>
+        <v>0.2286555475304913</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3445536786020701</v>
+        <v>0.3403518044727766</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2392588461904658</v>
+        <v>0.2413474210726875</v>
       </c>
       <c r="C84">
-        <v>-2859.970278714713</v>
+        <v>-2928.153497142926</v>
       </c>
       <c r="D84">
-        <v>1207.717721285287</v>
+        <v>1194.818502857074</v>
       </c>
       <c r="E84">
-        <v>3042.888</v>
+        <v>3098.172</v>
       </c>
       <c r="F84">
-        <v>4533.288</v>
+        <v>4588.572</v>
       </c>
       <c r="G84">
         <v>465.6</v>
@@ -8181,37 +8181,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M84">
-        <v>1154.435735467692</v>
+        <v>1168.514220046566</v>
       </c>
       <c r="N84">
-        <v>-761.5214497534058</v>
+        <v>-775.59993433228</v>
       </c>
       <c r="O84">
-        <v>-228.4564349260217</v>
+        <v>-232.679980299684</v>
       </c>
       <c r="P84">
-        <v>-533.0650148273841</v>
+        <v>-542.919954032596</v>
       </c>
       <c r="Q84">
-        <v>-495.2650148273841</v>
+        <v>-505.119954032596</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2875627623081278</v>
+        <v>0.3017841012674294</v>
       </c>
       <c r="T84">
-        <v>3.517942770549795</v>
+        <v>3.724880580582136</v>
       </c>
       <c r="U84">
         <v>0.2546574882221671</v>
       </c>
       <c r="V84">
-        <v>0.102105541341833</v>
+        <v>0.1008753540967506</v>
       </c>
       <c r="W84">
-        <v>0.2286555475304913</v>
+        <v>0.2289688239243669</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3403518044727766</v>
+        <v>0.3362511803225021</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2413474210726875</v>
+        <v>0.2434359959549092</v>
       </c>
       <c r="C85">
-        <v>-2928.153497142926</v>
+        <v>-2996.064083215083</v>
       </c>
       <c r="D85">
-        <v>1194.818502857074</v>
+        <v>1182.191916784916</v>
       </c>
       <c r="E85">
-        <v>3098.172</v>
+        <v>3153.456</v>
       </c>
       <c r="F85">
-        <v>4588.572</v>
+        <v>4643.856</v>
       </c>
       <c r="G85">
         <v>465.6</v>
@@ -8263,37 +8263,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M85">
-        <v>1168.514220046566</v>
+        <v>1182.59270462544</v>
       </c>
       <c r="N85">
-        <v>-775.59993433228</v>
+        <v>-789.6784189111544</v>
       </c>
       <c r="O85">
-        <v>-232.679980299684</v>
+        <v>-236.9035256733463</v>
       </c>
       <c r="P85">
-        <v>-542.919954032596</v>
+        <v>-552.7748932378081</v>
       </c>
       <c r="Q85">
-        <v>-505.119954032596</v>
+        <v>-514.9748932378081</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3017841012674294</v>
+        <v>0.3177831075966439</v>
       </c>
       <c r="T85">
-        <v>3.724880580582136</v>
+        <v>3.95768561686852</v>
       </c>
       <c r="U85">
         <v>0.2546574882221671</v>
       </c>
       <c r="V85">
-        <v>0.1008753540967506</v>
+        <v>0.09967445702417026</v>
       </c>
       <c r="W85">
-        <v>0.2289688239243669</v>
+        <v>0.2292746413564836</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3362511803225021</v>
+        <v>0.3322481900805676</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2434359959549092</v>
+        <v>0.2455245708371309</v>
       </c>
       <c r="C86">
-        <v>-2996.064083215082</v>
+        <v>-3063.710589906239</v>
       </c>
       <c r="D86">
-        <v>1182.191916784918</v>
+        <v>1169.829410093761</v>
       </c>
       <c r="E86">
-        <v>3153.456</v>
+        <v>3208.739999999999</v>
       </c>
       <c r="F86">
-        <v>4643.856</v>
+        <v>4699.139999999999</v>
       </c>
       <c r="G86">
         <v>465.6</v>
@@ -8345,37 +8345,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M86">
-        <v>1182.59270462544</v>
+        <v>1196.671189204314</v>
       </c>
       <c r="N86">
-        <v>-789.6784189111544</v>
+        <v>-803.7569034900285</v>
       </c>
       <c r="O86">
-        <v>-236.9035256733463</v>
+        <v>-241.1270710470085</v>
       </c>
       <c r="P86">
-        <v>-552.7748932378081</v>
+        <v>-562.62983244302</v>
       </c>
       <c r="Q86">
-        <v>-514.9748932378081</v>
+        <v>-524.82983244302</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3177831075966436</v>
+        <v>0.3359153147697532</v>
       </c>
       <c r="T86">
-        <v>3.957685616868518</v>
+        <v>4.221531324659752</v>
       </c>
       <c r="U86">
         <v>0.2546574882221671</v>
       </c>
       <c r="V86">
-        <v>0.09967445702417026</v>
+        <v>0.09850181635329769</v>
       </c>
       <c r="W86">
-        <v>0.2292746413564836</v>
+        <v>0.2295732630843151</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3322481900805676</v>
+        <v>0.3283393878443256</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2455245708371309</v>
+        <v>0.2476131457193525</v>
       </c>
       <c r="C87">
-        <v>-3063.710589906239</v>
+        <v>-3131.101216130697</v>
       </c>
       <c r="D87">
-        <v>1169.829410093761</v>
+        <v>1157.722783869303</v>
       </c>
       <c r="E87">
-        <v>3208.739999999999</v>
+        <v>3264.024</v>
       </c>
       <c r="F87">
-        <v>4699.139999999999</v>
+        <v>4754.424</v>
       </c>
       <c r="G87">
         <v>465.6</v>
@@ -8427,37 +8427,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M87">
-        <v>1196.671189204314</v>
+        <v>1210.749673783189</v>
       </c>
       <c r="N87">
-        <v>-803.7569034900285</v>
+        <v>-817.8353880689029</v>
       </c>
       <c r="O87">
-        <v>-241.1270710470085</v>
+        <v>-245.3506164206709</v>
       </c>
       <c r="P87">
-        <v>-562.62983244302</v>
+        <v>-572.484771648232</v>
       </c>
       <c r="Q87">
-        <v>-524.82983244302</v>
+        <v>-534.6847716482321</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3359153147697532</v>
+        <v>0.3566378372533071</v>
       </c>
       <c r="T87">
-        <v>4.221531324659752</v>
+        <v>4.523069276421164</v>
       </c>
       <c r="U87">
         <v>0.2546574882221671</v>
       </c>
       <c r="V87">
-        <v>0.09850181635329769</v>
+        <v>0.09735644639570119</v>
       </c>
       <c r="W87">
-        <v>0.2295732630843151</v>
+        <v>0.2298649401208018</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3283393878443256</v>
+        <v>0.3245214879856706</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2476131457193525</v>
+        <v>0.2497017206015742</v>
       </c>
       <c r="C88">
-        <v>-3131.101216130697</v>
+        <v>-3198.243824875297</v>
       </c>
       <c r="D88">
-        <v>1157.722783869303</v>
+        <v>1145.864175124702</v>
       </c>
       <c r="E88">
-        <v>3264.024</v>
+        <v>3319.308</v>
       </c>
       <c r="F88">
-        <v>4754.424</v>
+        <v>4809.708</v>
       </c>
       <c r="G88">
         <v>465.6</v>
@@ -8509,37 +8509,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M88">
-        <v>1210.749673783189</v>
+        <v>1224.828158362063</v>
       </c>
       <c r="N88">
-        <v>-817.8353880689029</v>
+        <v>-831.9138726477771</v>
       </c>
       <c r="O88">
-        <v>-245.3506164206709</v>
+        <v>-249.5741617943331</v>
       </c>
       <c r="P88">
-        <v>-572.484771648232</v>
+        <v>-582.339710853444</v>
       </c>
       <c r="Q88">
-        <v>-534.6847716482321</v>
+        <v>-544.5397108534439</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3566378372533071</v>
+        <v>0.380548440118946</v>
       </c>
       <c r="T88">
-        <v>4.523069276421164</v>
+        <v>4.870997682299714</v>
       </c>
       <c r="U88">
         <v>0.2546574882221671</v>
       </c>
       <c r="V88">
-        <v>0.09735644639570119</v>
+        <v>0.09623740678195751</v>
       </c>
       <c r="W88">
-        <v>0.2298649401208018</v>
+        <v>0.2301499119380589</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3245214879856706</v>
+        <v>0.3207913559398584</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2497017206015742</v>
+        <v>0.2517902954837959</v>
       </c>
       <c r="C89">
-        <v>-3198.243824875297</v>
+        <v>-3265.145960229598</v>
       </c>
       <c r="D89">
-        <v>1145.864175124702</v>
+        <v>1134.246039770402</v>
       </c>
       <c r="E89">
-        <v>3319.308</v>
+        <v>3374.591999999999</v>
       </c>
       <c r="F89">
-        <v>4809.708</v>
+        <v>4864.991999999999</v>
       </c>
       <c r="G89">
         <v>465.6</v>
@@ -8591,37 +8591,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M89">
-        <v>1224.828158362063</v>
+        <v>1238.906642940937</v>
       </c>
       <c r="N89">
-        <v>-831.9138726477771</v>
+        <v>-845.9923572266513</v>
       </c>
       <c r="O89">
-        <v>-249.5741617943331</v>
+        <v>-253.7977071679954</v>
       </c>
       <c r="P89">
-        <v>-582.339710853444</v>
+        <v>-592.194650058656</v>
       </c>
       <c r="Q89">
-        <v>-544.5397108534439</v>
+        <v>-554.394650058656</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.380548440118946</v>
+        <v>0.4084441434621915</v>
       </c>
       <c r="T89">
-        <v>4.870997682299714</v>
+        <v>5.276914155824691</v>
       </c>
       <c r="U89">
         <v>0.2546574882221671</v>
       </c>
       <c r="V89">
-        <v>0.09623740678195751</v>
+        <v>0.095143799886708</v>
       </c>
       <c r="W89">
-        <v>0.2301499119380589</v>
+        <v>0.2304284071231056</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3207913559398584</v>
+        <v>0.31714599962236</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2517902954837959</v>
+        <v>0.2538788703660175</v>
       </c>
       <c r="C90">
-        <v>-3265.145960229598</v>
+        <v>-3331.814863390389</v>
       </c>
       <c r="D90">
-        <v>1134.246039770402</v>
+        <v>1122.861136609611</v>
       </c>
       <c r="E90">
-        <v>3374.591999999999</v>
+        <v>3429.876</v>
       </c>
       <c r="F90">
-        <v>4864.991999999999</v>
+        <v>4920.276</v>
       </c>
       <c r="G90">
         <v>465.6</v>
@@ -8673,37 +8673,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M90">
-        <v>1238.906642940937</v>
+        <v>1252.985127519811</v>
       </c>
       <c r="N90">
-        <v>-845.9923572266513</v>
+        <v>-860.0708418055257</v>
       </c>
       <c r="O90">
-        <v>-253.7977071679954</v>
+        <v>-258.0212525416577</v>
       </c>
       <c r="P90">
-        <v>-592.194650058656</v>
+        <v>-602.049589263868</v>
       </c>
       <c r="Q90">
-        <v>-554.394650058656</v>
+        <v>-564.2495892638681</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4084441434621915</v>
+        <v>0.4414117928678453</v>
       </c>
       <c r="T90">
-        <v>5.276914155824691</v>
+        <v>5.756633624536026</v>
       </c>
       <c r="U90">
         <v>0.2546574882221671</v>
       </c>
       <c r="V90">
-        <v>0.095143799886708</v>
+        <v>0.09407476842730678</v>
       </c>
       <c r="W90">
-        <v>0.2304284071231056</v>
+        <v>0.2307006439893871</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.31714599962236</v>
+        <v>0.3135825614243559</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2538788703660175</v>
+        <v>0.2559674452482392</v>
       </c>
       <c r="C91">
-        <v>-3331.814863390389</v>
+        <v>-3398.257487711942</v>
       </c>
       <c r="D91">
-        <v>1122.861136609611</v>
+        <v>1111.702512288058</v>
       </c>
       <c r="E91">
-        <v>3429.876</v>
+        <v>3485.159999999999</v>
       </c>
       <c r="F91">
-        <v>4920.276</v>
+        <v>4975.559999999999</v>
       </c>
       <c r="G91">
         <v>465.6</v>
@@ -8755,37 +8755,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M91">
-        <v>1252.985127519811</v>
+        <v>1267.063612098686</v>
       </c>
       <c r="N91">
-        <v>-860.0708418055257</v>
+        <v>-874.1493263843998</v>
       </c>
       <c r="O91">
-        <v>-258.0212525416577</v>
+        <v>-262.24479791532</v>
       </c>
       <c r="P91">
-        <v>-602.049589263868</v>
+        <v>-611.9045284690799</v>
       </c>
       <c r="Q91">
-        <v>-564.2495892638681</v>
+        <v>-574.1045284690799</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4414117928678453</v>
+        <v>0.48097297215463</v>
       </c>
       <c r="T91">
-        <v>5.756633624536026</v>
+        <v>6.33229698698963</v>
       </c>
       <c r="U91">
         <v>0.2546574882221671</v>
       </c>
       <c r="V91">
-        <v>0.09407476842730678</v>
+        <v>0.09302949322255893</v>
       </c>
       <c r="W91">
-        <v>0.2307006439893871</v>
+        <v>0.2309668311475291</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3135825614243559</v>
+        <v>0.3100983107418631</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2559674452482392</v>
+        <v>0.2580560201304609</v>
       </c>
       <c r="C92">
-        <v>-3398.257487711942</v>
+        <v>-3464.480512867698</v>
       </c>
       <c r="D92">
-        <v>1111.702512288058</v>
+        <v>1100.763487132302</v>
       </c>
       <c r="E92">
-        <v>3485.159999999999</v>
+        <v>3540.444</v>
       </c>
       <c r="F92">
-        <v>4975.559999999999</v>
+        <v>5030.844</v>
       </c>
       <c r="G92">
         <v>465.6</v>
@@ -8837,37 +8837,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M92">
-        <v>1267.063612098686</v>
+        <v>1281.14209667756</v>
       </c>
       <c r="N92">
-        <v>-874.1493263843998</v>
+        <v>-888.2278109632745</v>
       </c>
       <c r="O92">
-        <v>-262.24479791532</v>
+        <v>-266.4683432889823</v>
       </c>
       <c r="P92">
-        <v>-611.9045284690799</v>
+        <v>-621.7594676742922</v>
       </c>
       <c r="Q92">
-        <v>-574.1045284690799</v>
+        <v>-583.9594676742922</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.48097297215463</v>
+        <v>0.5293255246162555</v>
       </c>
       <c r="T92">
-        <v>6.33229698698963</v>
+        <v>7.03588554109959</v>
       </c>
       <c r="U92">
         <v>0.2546574882221671</v>
       </c>
       <c r="V92">
-        <v>0.09302949322255893</v>
+        <v>0.0920071910992341</v>
       </c>
       <c r="W92">
-        <v>0.2309668311475291</v>
+        <v>0.2312271680384592</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3100983107418631</v>
+        <v>0.3066906369974469</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2580560201304609</v>
+        <v>0.2601445950126826</v>
       </c>
       <c r="C93">
-        <v>-3464.480512867698</v>
+        <v>-3530.490358183999</v>
       </c>
       <c r="D93">
-        <v>1100.763487132302</v>
+        <v>1090.037641816001</v>
       </c>
       <c r="E93">
-        <v>3540.444</v>
+        <v>3595.728</v>
       </c>
       <c r="F93">
-        <v>5030.844</v>
+        <v>5086.128</v>
       </c>
       <c r="G93">
         <v>465.6</v>
@@ -8919,37 +8919,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M93">
-        <v>1281.14209667756</v>
+        <v>1295.220581256434</v>
       </c>
       <c r="N93">
-        <v>-888.2278109632745</v>
+        <v>-902.3062955421486</v>
       </c>
       <c r="O93">
-        <v>-266.4683432889823</v>
+        <v>-270.6918886626446</v>
       </c>
       <c r="P93">
-        <v>-621.7594676742922</v>
+        <v>-631.614406879504</v>
       </c>
       <c r="Q93">
-        <v>-583.9594676742922</v>
+        <v>-593.8144068795041</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5293255246162555</v>
+        <v>0.5897662151932876</v>
       </c>
       <c r="T93">
-        <v>7.03588554109959</v>
+        <v>7.915371233737041</v>
       </c>
       <c r="U93">
         <v>0.2546574882221671</v>
       </c>
       <c r="V93">
-        <v>0.0920071910992341</v>
+        <v>0.09100711293511199</v>
       </c>
       <c r="W93">
-        <v>0.2312271680384592</v>
+        <v>0.2314818454317604</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3066906369974469</v>
+        <v>0.3033570431170399</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2601445950126826</v>
+        <v>0.2622331698949042</v>
       </c>
       <c r="C94">
-        <v>-3530.490358183999</v>
+        <v>-3596.293195201812</v>
       </c>
       <c r="D94">
-        <v>1090.037641816001</v>
+        <v>1079.518804798188</v>
       </c>
       <c r="E94">
-        <v>3595.728</v>
+        <v>3651.012</v>
       </c>
       <c r="F94">
-        <v>5086.128</v>
+        <v>5141.412</v>
       </c>
       <c r="G94">
         <v>465.6</v>
@@ -9001,37 +9001,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M94">
-        <v>1295.220581256434</v>
+        <v>1309.299065835309</v>
       </c>
       <c r="N94">
-        <v>-902.3062955421486</v>
+        <v>-916.384780121023</v>
       </c>
       <c r="O94">
-        <v>-270.6918886626446</v>
+        <v>-274.9154340363069</v>
       </c>
       <c r="P94">
-        <v>-631.614406879504</v>
+        <v>-641.4693460847161</v>
       </c>
       <c r="Q94">
-        <v>-593.8144068795041</v>
+        <v>-603.6693460847162</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5897662151932876</v>
+        <v>0.6674756745066145</v>
       </c>
       <c r="T94">
-        <v>7.915371233737041</v>
+        <v>9.046138552842333</v>
       </c>
       <c r="U94">
         <v>0.2546574882221671</v>
       </c>
       <c r="V94">
-        <v>0.09100711293511199</v>
+        <v>0.09002854182828282</v>
       </c>
       <c r="W94">
-        <v>0.2314818454317604</v>
+        <v>0.2317310458918723</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3033570431170399</v>
+        <v>0.3000951394276093</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2622331698949042</v>
+        <v>0.2643217447771259</v>
       </c>
       <c r="C95">
-        <v>-3596.293195201812</v>
+        <v>-3661.894959518067</v>
       </c>
       <c r="D95">
-        <v>1079.518804798188</v>
+        <v>1069.201040481933</v>
       </c>
       <c r="E95">
-        <v>3651.012</v>
+        <v>3706.296</v>
       </c>
       <c r="F95">
-        <v>5141.412</v>
+        <v>5196.696</v>
       </c>
       <c r="G95">
         <v>465.6</v>
@@ -9083,37 +9083,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M95">
-        <v>1309.299065835309</v>
+        <v>1323.377550414183</v>
       </c>
       <c r="N95">
-        <v>-916.384780121023</v>
+        <v>-930.4632646998972</v>
       </c>
       <c r="O95">
-        <v>-274.9154340363069</v>
+        <v>-279.1389794099691</v>
       </c>
       <c r="P95">
-        <v>-641.4693460847161</v>
+        <v>-651.3242852899281</v>
       </c>
       <c r="Q95">
-        <v>-603.6693460847162</v>
+        <v>-613.524285289928</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6674756745066145</v>
+        <v>0.7710882869243837</v>
       </c>
       <c r="T95">
-        <v>9.046138552842333</v>
+        <v>10.55382831164939</v>
       </c>
       <c r="U95">
         <v>0.2546574882221671</v>
       </c>
       <c r="V95">
-        <v>0.09002854182828282</v>
+        <v>0.08907079138330108</v>
       </c>
       <c r="W95">
-        <v>0.2317310458918723</v>
+        <v>0.231974944214535</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3000951394276093</v>
+        <v>0.296902637944337</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2643217447771259</v>
+        <v>0.2664103196593476</v>
       </c>
       <c r="C96">
-        <v>-3661.894959518067</v>
+        <v>-3727.301361954382</v>
       </c>
       <c r="D96">
-        <v>1069.201040481933</v>
+        <v>1059.078638045618</v>
       </c>
       <c r="E96">
-        <v>3706.296</v>
+        <v>3761.58</v>
       </c>
       <c r="F96">
-        <v>5196.696</v>
+        <v>5251.98</v>
       </c>
       <c r="G96">
         <v>465.6</v>
@@ -9165,37 +9165,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M96">
-        <v>1323.377550414183</v>
+        <v>1337.456034993057</v>
       </c>
       <c r="N96">
-        <v>-930.4632646998972</v>
+        <v>-944.5417492787716</v>
       </c>
       <c r="O96">
-        <v>-279.1389794099691</v>
+        <v>-283.3625247836314</v>
       </c>
       <c r="P96">
-        <v>-651.3242852899281</v>
+        <v>-661.1792244951401</v>
       </c>
       <c r="Q96">
-        <v>-613.524285289928</v>
+        <v>-623.3792244951401</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7710882869243837</v>
+        <v>0.9161459443092608</v>
       </c>
       <c r="T96">
-        <v>10.55382831164939</v>
+        <v>12.66459397397927</v>
       </c>
       <c r="U96">
         <v>0.2546574882221671</v>
       </c>
       <c r="V96">
-        <v>0.08907079138330108</v>
+        <v>0.08813320410558212</v>
       </c>
       <c r="W96">
-        <v>0.231974944214535</v>
+        <v>0.232213707835668</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.296902637944337</v>
+        <v>0.2937773470186071</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2664103196593476</v>
+        <v>0.2684988945415693</v>
       </c>
       <c r="C97">
-        <v>-3727.301361954382</v>
+        <v>-3792.517899097295</v>
       </c>
       <c r="D97">
-        <v>1059.078638045618</v>
+        <v>1049.146100902706</v>
       </c>
       <c r="E97">
-        <v>3761.58</v>
+        <v>3816.864</v>
       </c>
       <c r="F97">
-        <v>5251.98</v>
+        <v>5307.264</v>
       </c>
       <c r="G97">
         <v>465.6</v>
@@ -9247,37 +9247,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M97">
-        <v>1337.456034993057</v>
+        <v>1351.534519571931</v>
       </c>
       <c r="N97">
-        <v>-944.5417492787716</v>
+        <v>-958.6202338576458</v>
       </c>
       <c r="O97">
-        <v>-283.3625247836314</v>
+        <v>-287.5860701572937</v>
       </c>
       <c r="P97">
-        <v>-661.1792244951401</v>
+        <v>-671.0341637003521</v>
       </c>
       <c r="Q97">
-        <v>-623.3792244951401</v>
+        <v>-633.2341637003522</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9161459443092608</v>
+        <v>1.133732430386577</v>
       </c>
       <c r="T97">
-        <v>12.66459397397927</v>
+        <v>15.8307424674741</v>
       </c>
       <c r="U97">
         <v>0.2546574882221671</v>
       </c>
       <c r="V97">
-        <v>0.08813320410558212</v>
+        <v>0.08721514989614899</v>
       </c>
       <c r="W97">
-        <v>0.232213707835668</v>
+        <v>0.232447497214694</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2937773470186071</v>
+        <v>0.2907171663204966</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2684988945415693</v>
+        <v>0.2705874694237909</v>
       </c>
       <c r="C98">
-        <v>-3792.517899097294</v>
+        <v>-3857.549863250914</v>
       </c>
       <c r="D98">
-        <v>1049.146100902706</v>
+        <v>1039.398136749085</v>
       </c>
       <c r="E98">
-        <v>3816.863999999999</v>
+        <v>3872.148</v>
       </c>
       <c r="F98">
-        <v>5307.263999999999</v>
+        <v>5362.548</v>
       </c>
       <c r="G98">
         <v>465.6</v>
@@ -9329,37 +9329,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M98">
-        <v>1351.534519571931</v>
+        <v>1365.613004150806</v>
       </c>
       <c r="N98">
-        <v>-958.6202338576455</v>
+        <v>-972.6987184365199</v>
       </c>
       <c r="O98">
-        <v>-287.5860701572936</v>
+        <v>-291.809615530956</v>
       </c>
       <c r="P98">
-        <v>-671.0341637003519</v>
+        <v>-680.889102905564</v>
       </c>
       <c r="Q98">
-        <v>-633.2341637003519</v>
+        <v>-643.089102905564</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.133732430386574</v>
+        <v>1.496376573848765</v>
       </c>
       <c r="T98">
-        <v>15.83074246747406</v>
+        <v>21.10765662329875</v>
       </c>
       <c r="U98">
         <v>0.2546574882221671</v>
       </c>
       <c r="V98">
-        <v>0.08721514989614899</v>
+        <v>0.08631602463948766</v>
       </c>
       <c r="W98">
-        <v>0.232447497214694</v>
+        <v>0.2326764661941525</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2907171663204967</v>
+        <v>0.2877200821316256</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2705874694237909</v>
+        <v>0.2726760443060126</v>
       </c>
       <c r="C99">
-        <v>-3857.549863250914</v>
+        <v>-3922.402351839837</v>
       </c>
       <c r="D99">
-        <v>1039.398136749085</v>
+        <v>1029.829648160163</v>
       </c>
       <c r="E99">
-        <v>3872.148</v>
+        <v>3927.431999999999</v>
       </c>
       <c r="F99">
-        <v>5362.548</v>
+        <v>5417.831999999999</v>
       </c>
       <c r="G99">
         <v>465.6</v>
@@ -9411,37 +9411,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M99">
-        <v>1365.613004150806</v>
+        <v>1379.69148872968</v>
       </c>
       <c r="N99">
-        <v>-972.6987184365199</v>
+        <v>-986.7772030153941</v>
       </c>
       <c r="O99">
-        <v>-291.809615530956</v>
+        <v>-296.0331609046182</v>
       </c>
       <c r="P99">
-        <v>-680.889102905564</v>
+        <v>-690.7440421107758</v>
       </c>
       <c r="Q99">
-        <v>-643.089102905564</v>
+        <v>-652.9440421107759</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.496376573848765</v>
+        <v>2.221664860773148</v>
       </c>
       <c r="T99">
-        <v>21.10765662329875</v>
+        <v>31.66148493494812</v>
       </c>
       <c r="U99">
         <v>0.2546574882221671</v>
       </c>
       <c r="V99">
-        <v>0.08631602463948766</v>
+        <v>0.08543524887786025</v>
       </c>
       <c r="W99">
-        <v>0.2326764661941525</v>
+        <v>0.2329007623372955</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2877200821316256</v>
+        <v>0.2847841629262008</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2726760443060126</v>
+        <v>0.2747646191882342</v>
       </c>
       <c r="C100">
-        <v>-3922.402351839837</v>
+        <v>-3987.080276297425</v>
       </c>
       <c r="D100">
-        <v>1029.829648160163</v>
+        <v>1020.435723702575</v>
       </c>
       <c r="E100">
-        <v>3927.431999999999</v>
+        <v>3982.716</v>
       </c>
       <c r="F100">
-        <v>5417.831999999999</v>
+        <v>5473.116</v>
       </c>
       <c r="G100">
         <v>465.6</v>
@@ -9493,37 +9493,37 @@
         <v>392.9142857142857</v>
       </c>
       <c r="M100">
-        <v>1379.69148872968</v>
+        <v>1393.769973308554</v>
       </c>
       <c r="N100">
-        <v>-986.7772030153941</v>
+        <v>-1000.855687594269</v>
       </c>
       <c r="O100">
-        <v>-296.0331609046182</v>
+        <v>-300.2567062782806</v>
       </c>
       <c r="P100">
-        <v>-690.7440421107758</v>
+        <v>-700.5989813159881</v>
       </c>
       <c r="Q100">
-        <v>-652.9440421107759</v>
+        <v>-662.7989813159882</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.221664860773148</v>
+        <v>4.397529721546295</v>
       </c>
       <c r="T100">
-        <v>31.66148493494812</v>
+        <v>63.32296986989623</v>
       </c>
       <c r="U100">
         <v>0.2546574882221671</v>
       </c>
       <c r="V100">
-        <v>0.08543524887786025</v>
+        <v>0.08457226656596264</v>
       </c>
       <c r="W100">
-        <v>0.2329007623372955</v>
+        <v>0.2331205272452235</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2847841629262008</v>
+        <v>0.2819075552198755</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2747646191882342</v>
-      </c>
-      <c r="C101">
-        <v>-3987.080276297425</v>
-      </c>
-      <c r="D101">
-        <v>1020.435723702575</v>
-      </c>
-      <c r="E101">
-        <v>3982.716</v>
-      </c>
-      <c r="F101">
-        <v>5473.116</v>
-      </c>
-      <c r="G101">
-        <v>465.6</v>
-      </c>
-      <c r="H101">
-        <v>4038</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>430.7142857142857</v>
-      </c>
-      <c r="K101">
-        <v>37.80000000000001</v>
-      </c>
-      <c r="L101">
-        <v>392.9142857142857</v>
-      </c>
-      <c r="M101">
-        <v>1393.769973308554</v>
-      </c>
-      <c r="N101">
-        <v>-1000.855687594269</v>
-      </c>
-      <c r="O101">
-        <v>-300.2567062782806</v>
-      </c>
-      <c r="P101">
-        <v>-700.5989813159881</v>
-      </c>
-      <c r="Q101">
-        <v>-662.7989813159882</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.397529721546295</v>
-      </c>
-      <c r="T101">
-        <v>63.32296986989623</v>
-      </c>
-      <c r="U101">
-        <v>0.2546574882221671</v>
-      </c>
-      <c r="V101">
-        <v>0.08457226656596264</v>
-      </c>
-      <c r="W101">
-        <v>0.2331205272452235</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2819075552198755</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
